--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -6394,7 +6394,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121346074</v>
+        <v>121343178</v>
       </c>
       <c r="B53" t="n">
         <v>78598</v>
@@ -6430,14 +6430,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518583</v>
+        <v>518814</v>
       </c>
       <c r="R53" t="n">
-        <v>6995023</v>
+        <v>6994717</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6506,7 +6506,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121343178</v>
+        <v>121346074</v>
       </c>
       <c r="B54" t="n">
         <v>78598</v>
@@ -6542,14 +6542,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518814</v>
+        <v>518583</v>
       </c>
       <c r="R54" t="n">
-        <v>6994717</v>
+        <v>6995023</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,10 +6618,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121345954</v>
+        <v>121343022</v>
       </c>
       <c r="B55" t="n">
-        <v>79679</v>
+        <v>78598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6634,37 +6634,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518428</v>
+        <v>518814</v>
       </c>
       <c r="R55" t="n">
-        <v>6995142</v>
+        <v>6994676</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121343022</v>
+        <v>121345954</v>
       </c>
       <c r="B56" t="n">
-        <v>78598</v>
+        <v>79679</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6746,37 +6746,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518814</v>
+        <v>518428</v>
       </c>
       <c r="R56" t="n">
-        <v>6994676</v>
+        <v>6995142</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346613</v>
+        <v>121343196</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518770</v>
+        <v>518797</v>
       </c>
       <c r="R3" t="n">
-        <v>6994702</v>
+        <v>6994707</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346053</v>
+        <v>121346005</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518560</v>
+        <v>518483</v>
       </c>
       <c r="R4" t="n">
-        <v>6995039</v>
+        <v>6995124</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346620</v>
+        <v>121344456</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,17 +1050,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518774</v>
+        <v>518727</v>
       </c>
       <c r="R5" t="n">
-        <v>6994685</v>
+        <v>6994987</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346560</v>
+        <v>121343207</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>91259</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,41 +1138,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518787</v>
+        <v>518808</v>
       </c>
       <c r="R6" t="n">
-        <v>6994752</v>
+        <v>6994725</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,6 +1223,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343137</v>
+        <v>121345116</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,34 +1258,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518823</v>
+        <v>518559</v>
       </c>
       <c r="R7" t="n">
-        <v>6994691</v>
+        <v>6994969</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1313,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,6 +1339,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1350,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346586</v>
+        <v>121344731</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,14 +1394,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518787</v>
+        <v>518652</v>
       </c>
       <c r="R8" t="n">
-        <v>6994738</v>
+        <v>6994988</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343303</v>
+        <v>121345946</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,14 +1506,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518809</v>
+        <v>518414</v>
       </c>
       <c r="R9" t="n">
-        <v>6994765</v>
+        <v>6995151</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1555,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343196</v>
+        <v>121346126</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,14 +1618,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518797</v>
+        <v>518627</v>
       </c>
       <c r="R10" t="n">
-        <v>6994707</v>
+        <v>6994984</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1649,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343959</v>
+        <v>121343797</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518825</v>
+        <v>518812</v>
       </c>
       <c r="R11" t="n">
-        <v>6994907</v>
+        <v>6994875</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1761,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1779,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345085</v>
+        <v>121343229</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,14 +1842,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518559</v>
+        <v>518808</v>
       </c>
       <c r="R12" t="n">
-        <v>6995004</v>
+        <v>6994725</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1873,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1891,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121344818</v>
+        <v>121346613</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,17 +1954,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518624</v>
+        <v>518770</v>
       </c>
       <c r="R13" t="n">
-        <v>6995059</v>
+        <v>6994702</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345122</v>
+        <v>121346092</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,13 +2070,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518552</v>
+        <v>518610</v>
       </c>
       <c r="R14" t="n">
-        <v>6994973</v>
+        <v>6995000</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2115,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121344213</v>
+        <v>121343305</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,17 +2178,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518792</v>
+        <v>518812</v>
       </c>
       <c r="R15" t="n">
-        <v>6994973</v>
+        <v>6994779</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,7 +2217,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2227,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121343093</v>
+        <v>121344999</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,17 +2290,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518801</v>
+        <v>518659</v>
       </c>
       <c r="R16" t="n">
-        <v>6994670</v>
+        <v>6995028</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2321,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346289</v>
+        <v>121345053</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2374,34 +2382,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518618</v>
+        <v>518563</v>
       </c>
       <c r="R17" t="n">
-        <v>6994929</v>
+        <v>6995042</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2433,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121343478</v>
+        <v>121346074</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,14 +2514,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518834</v>
+        <v>518583</v>
       </c>
       <c r="R18" t="n">
-        <v>6994815</v>
+        <v>6995023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2555,7 +2563,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121345073</v>
+        <v>121343959</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2618,17 +2626,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518555</v>
+        <v>518825</v>
       </c>
       <c r="R19" t="n">
-        <v>6995010</v>
+        <v>6994907</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2667,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,7 +2705,7 @@
         <v>121346635</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343524</v>
+        <v>121346430</v>
       </c>
       <c r="B21" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,17 +2850,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518815</v>
+        <v>518614</v>
       </c>
       <c r="R21" t="n">
-        <v>6994807</v>
+        <v>6994902</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2881,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2891,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343253</v>
+        <v>121345064</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2954,17 +2962,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518799</v>
+        <v>518566</v>
       </c>
       <c r="R22" t="n">
-        <v>6994749</v>
+        <v>6995030</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2993,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3003,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121344999</v>
+        <v>121344796</v>
       </c>
       <c r="B23" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3070,13 +3078,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518659</v>
+        <v>518665</v>
       </c>
       <c r="R23" t="n">
-        <v>6995028</v>
+        <v>6995040</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3105,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3115,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121344380</v>
+        <v>121346232</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3182,13 +3190,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518768</v>
+        <v>518626</v>
       </c>
       <c r="R24" t="n">
-        <v>6994994</v>
+        <v>6994964</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3217,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3227,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,10 +3262,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121343160</v>
+        <v>121344308</v>
       </c>
       <c r="B25" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3270,37 +3278,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518815</v>
+        <v>518783</v>
       </c>
       <c r="R25" t="n">
-        <v>6994704</v>
+        <v>6994979</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121345116</v>
+        <v>121346595</v>
       </c>
       <c r="B26" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3382,40 +3390,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518559</v>
+        <v>518786</v>
       </c>
       <c r="R26" t="n">
-        <v>6994969</v>
+        <v>6994717</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3444,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3454,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,7 +3468,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3482,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346038</v>
+        <v>121343920</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3518,17 +3522,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518544</v>
+        <v>518807</v>
       </c>
       <c r="R27" t="n">
-        <v>6995061</v>
+        <v>6994899</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3557,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,10 +3598,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346232</v>
+        <v>121343092</v>
       </c>
       <c r="B28" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3630,17 +3634,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518626</v>
+        <v>518811</v>
       </c>
       <c r="R28" t="n">
-        <v>6994964</v>
+        <v>6994686</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3669,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,10 +3710,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343732</v>
+        <v>121344384</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3722,21 +3726,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3746,13 +3750,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518817</v>
+        <v>518741</v>
       </c>
       <c r="R29" t="n">
-        <v>6994855</v>
+        <v>6994995</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3791,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,10 +3822,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121346005</v>
+        <v>121344380</v>
       </c>
       <c r="B30" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3854,17 +3858,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518483</v>
+        <v>518768</v>
       </c>
       <c r="R30" t="n">
-        <v>6995124</v>
+        <v>6994994</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346126</v>
+        <v>121344818</v>
       </c>
       <c r="B31" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,13 +3974,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518627</v>
+        <v>518624</v>
       </c>
       <c r="R31" t="n">
-        <v>6994984</v>
+        <v>6995059</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4005,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121343249</v>
+        <v>121343160</v>
       </c>
       <c r="B32" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4058,21 +4062,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4082,13 +4086,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518808</v>
+        <v>518815</v>
       </c>
       <c r="R32" t="n">
-        <v>6994740</v>
+        <v>6994704</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121344731</v>
+        <v>121343625</v>
       </c>
       <c r="B33" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,17 +4194,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518652</v>
+        <v>518819</v>
       </c>
       <c r="R33" t="n">
-        <v>6994988</v>
+        <v>6994817</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4229,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,10 +4270,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121345972</v>
+        <v>121345085</v>
       </c>
       <c r="B34" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4302,14 +4306,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518465</v>
+        <v>518559</v>
       </c>
       <c r="R34" t="n">
-        <v>6995120</v>
+        <v>6995004</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4341,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121343797</v>
+        <v>121346053</v>
       </c>
       <c r="B35" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,14 +4418,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518812</v>
+        <v>518560</v>
       </c>
       <c r="R35" t="n">
-        <v>6994875</v>
+        <v>6995039</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4453,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121345946</v>
+        <v>121346533</v>
       </c>
       <c r="B36" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4526,14 +4530,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518414</v>
+        <v>518703</v>
       </c>
       <c r="R36" t="n">
-        <v>6995151</v>
+        <v>6994800</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4565,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,10 +4606,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121343018</v>
+        <v>121344213</v>
       </c>
       <c r="B37" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,17 +4642,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518813</v>
+        <v>518792</v>
       </c>
       <c r="R37" t="n">
-        <v>6994667</v>
+        <v>6994973</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4677,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,10 +4718,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121343920</v>
+        <v>121343303</v>
       </c>
       <c r="B38" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4750,17 +4754,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518807</v>
+        <v>518809</v>
       </c>
       <c r="R38" t="n">
-        <v>6994899</v>
+        <v>6994765</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4789,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4799,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4826,10 +4830,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121344456</v>
+        <v>121343289</v>
       </c>
       <c r="B39" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4862,14 +4866,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518727</v>
+        <v>518814</v>
       </c>
       <c r="R39" t="n">
-        <v>6994987</v>
+        <v>6994762</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4901,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4911,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4938,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121343092</v>
+        <v>121343285</v>
       </c>
       <c r="B40" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4978,10 +4982,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518811</v>
+        <v>518804</v>
       </c>
       <c r="R40" t="n">
-        <v>6994686</v>
+        <v>6994760</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5013,7 +5017,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5027,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5050,10 +5054,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121343625</v>
+        <v>121343732</v>
       </c>
       <c r="B41" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5086,17 +5090,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518819</v>
+        <v>518817</v>
       </c>
       <c r="R41" t="n">
-        <v>6994817</v>
+        <v>6994855</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,7 +5129,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5139,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5162,10 +5166,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121343305</v>
+        <v>121343472</v>
       </c>
       <c r="B42" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5202,10 +5206,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518812</v>
+        <v>518814</v>
       </c>
       <c r="R42" t="n">
-        <v>6994779</v>
+        <v>6994800</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5237,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5247,7 +5251,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5274,10 +5278,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121344796</v>
+        <v>121343178</v>
       </c>
       <c r="B43" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5310,14 +5314,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518665</v>
+        <v>518814</v>
       </c>
       <c r="R43" t="n">
-        <v>6995040</v>
+        <v>6994717</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5349,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5359,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5386,10 +5390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121343468</v>
+        <v>121344193</v>
       </c>
       <c r="B44" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5422,17 +5426,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518814</v>
+        <v>518808</v>
       </c>
       <c r="R44" t="n">
-        <v>6994789</v>
+        <v>6994956</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5461,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5498,10 +5502,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121344384</v>
+        <v>121343249</v>
       </c>
       <c r="B45" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5514,37 +5518,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518741</v>
+        <v>518808</v>
       </c>
       <c r="R45" t="n">
-        <v>6994995</v>
+        <v>6994740</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5573,7 +5577,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5583,7 +5587,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5610,10 +5614,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121343289</v>
+        <v>121346025</v>
       </c>
       <c r="B46" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5646,17 +5650,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518814</v>
+        <v>518519</v>
       </c>
       <c r="R46" t="n">
-        <v>6994762</v>
+        <v>6995085</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5685,7 +5689,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5695,7 +5699,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,10 +5726,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121345938</v>
+        <v>121346560</v>
       </c>
       <c r="B47" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5758,14 +5762,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518387</v>
+        <v>518787</v>
       </c>
       <c r="R47" t="n">
-        <v>6995152</v>
+        <v>6994752</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5797,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5807,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5834,10 +5838,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121346092</v>
+        <v>121343524</v>
       </c>
       <c r="B48" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5870,14 +5874,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518610</v>
+        <v>518815</v>
       </c>
       <c r="R48" t="n">
-        <v>6995000</v>
+        <v>6994807</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5909,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5946,10 +5950,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121343809</v>
+        <v>121345122</v>
       </c>
       <c r="B49" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5986,10 +5990,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518808</v>
+        <v>518552</v>
       </c>
       <c r="R49" t="n">
-        <v>6994892</v>
+        <v>6994973</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6021,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6031,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6058,10 +6062,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121344193</v>
+        <v>121345954</v>
       </c>
       <c r="B50" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6074,37 +6078,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518808</v>
+        <v>518428</v>
       </c>
       <c r="R50" t="n">
-        <v>6994956</v>
+        <v>6995142</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6147,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6170,10 +6174,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121345053</v>
+        <v>121343298</v>
       </c>
       <c r="B51" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6186,37 +6190,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518563</v>
+        <v>518812</v>
       </c>
       <c r="R51" t="n">
-        <v>6995042</v>
+        <v>6994775</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6245,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6255,7 +6259,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6282,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121346025</v>
+        <v>121345938</v>
       </c>
       <c r="B52" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6322,10 +6326,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518519</v>
+        <v>518387</v>
       </c>
       <c r="R52" t="n">
-        <v>6995085</v>
+        <v>6995152</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6367,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6394,10 +6398,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121343178</v>
+        <v>121346289</v>
       </c>
       <c r="B53" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6430,17 +6434,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518814</v>
+        <v>518618</v>
       </c>
       <c r="R53" t="n">
-        <v>6994717</v>
+        <v>6994929</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6469,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6479,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6506,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121346074</v>
+        <v>121346620</v>
       </c>
       <c r="B54" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6542,14 +6546,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518583</v>
+        <v>518774</v>
       </c>
       <c r="R54" t="n">
-        <v>6995023</v>
+        <v>6994685</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6581,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6591,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,10 +6622,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121343022</v>
+        <v>121345918</v>
       </c>
       <c r="B55" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6654,14 +6658,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518814</v>
+        <v>518360</v>
       </c>
       <c r="R55" t="n">
-        <v>6994676</v>
+        <v>6995099</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6693,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6703,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6730,10 +6734,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121345954</v>
+        <v>121343137</v>
       </c>
       <c r="B56" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6746,37 +6750,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518428</v>
+        <v>518823</v>
       </c>
       <c r="R56" t="n">
-        <v>6995142</v>
+        <v>6994691</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6805,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6815,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121345064</v>
+        <v>121343478</v>
       </c>
       <c r="B57" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6878,14 +6882,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518566</v>
+        <v>518834</v>
       </c>
       <c r="R57" t="n">
-        <v>6995030</v>
+        <v>6994815</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6917,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6927,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6954,10 +6958,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121346533</v>
+        <v>121346586</v>
       </c>
       <c r="B58" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6994,10 +6998,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518703</v>
+        <v>518787</v>
       </c>
       <c r="R58" t="n">
-        <v>6994800</v>
+        <v>6994738</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7029,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7039,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7066,10 +7070,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121343207</v>
+        <v>121343809</v>
       </c>
       <c r="B59" t="n">
-        <v>91249</v>
+        <v>78601</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7078,44 +7082,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
         <v>518808</v>
       </c>
       <c r="R59" t="n">
-        <v>6994725</v>
+        <v>6994892</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7144,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7154,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7163,7 +7164,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7182,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121345960</v>
+        <v>121343022</v>
       </c>
       <c r="B60" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7198,34 +7198,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518444</v>
+        <v>518814</v>
       </c>
       <c r="R60" t="n">
-        <v>6995141</v>
+        <v>6994676</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,10 +7294,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121345918</v>
+        <v>121345972</v>
       </c>
       <c r="B61" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518360</v>
+        <v>518465</v>
       </c>
       <c r="R61" t="n">
-        <v>6995099</v>
+        <v>6995120</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121343298</v>
+        <v>121343468</v>
       </c>
       <c r="B62" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518812</v>
+        <v>518814</v>
       </c>
       <c r="R62" t="n">
-        <v>6994775</v>
+        <v>6994789</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121346595</v>
+        <v>121345960</v>
       </c>
       <c r="B63" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7534,37 +7534,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518786</v>
+        <v>518444</v>
       </c>
       <c r="R63" t="n">
-        <v>6994717</v>
+        <v>6995141</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,10 +7630,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121344308</v>
+        <v>121345073</v>
       </c>
       <c r="B64" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7666,14 +7666,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518783</v>
+        <v>518555</v>
       </c>
       <c r="R64" t="n">
-        <v>6994979</v>
+        <v>6995010</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121343285</v>
+        <v>121343093</v>
       </c>
       <c r="B65" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7782,13 +7782,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518804</v>
+        <v>518801</v>
       </c>
       <c r="R65" t="n">
-        <v>6994760</v>
+        <v>6994670</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,10 +7854,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121343472</v>
+        <v>121343253</v>
       </c>
       <c r="B66" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518814</v>
+        <v>518799</v>
       </c>
       <c r="R66" t="n">
-        <v>6994800</v>
+        <v>6994749</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121346430</v>
+        <v>121346038</v>
       </c>
       <c r="B67" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,14 +8002,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518614</v>
+        <v>518544</v>
       </c>
       <c r="R67" t="n">
-        <v>6994902</v>
+        <v>6995061</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,10 +8078,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343229</v>
+        <v>121343018</v>
       </c>
       <c r="B68" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518808</v>
+        <v>518813</v>
       </c>
       <c r="R68" t="n">
-        <v>6994725</v>
+        <v>6994667</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -1918,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346613</v>
+        <v>121346092</v>
       </c>
       <c r="B13" t="n">
         <v>78601</v>
@@ -1954,14 +1954,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518770</v>
+        <v>518610</v>
       </c>
       <c r="R13" t="n">
-        <v>6994702</v>
+        <v>6995000</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346092</v>
+        <v>121346613</v>
       </c>
       <c r="B14" t="n">
         <v>78601</v>
@@ -2066,14 +2066,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518610</v>
+        <v>518770</v>
       </c>
       <c r="R14" t="n">
-        <v>6995000</v>
+        <v>6994702</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346232</v>
+        <v>121346595</v>
       </c>
       <c r="B24" t="n">
         <v>78601</v>
@@ -3186,14 +3186,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518626</v>
+        <v>518786</v>
       </c>
       <c r="R24" t="n">
-        <v>6994964</v>
+        <v>6994717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,7 +3262,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121344308</v>
+        <v>121346232</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518783</v>
+        <v>518626</v>
       </c>
       <c r="R25" t="n">
-        <v>6994979</v>
+        <v>6994964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,7 +3374,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346595</v>
+        <v>121344308</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3410,14 +3410,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518786</v>
+        <v>518783</v>
       </c>
       <c r="R26" t="n">
-        <v>6994717</v>
+        <v>6994979</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121343160</v>
+        <v>121343625</v>
       </c>
       <c r="B32" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518815</v>
+        <v>518819</v>
       </c>
       <c r="R32" t="n">
-        <v>6994704</v>
+        <v>6994817</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,7 +4158,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121343625</v>
+        <v>121345085</v>
       </c>
       <c r="B33" t="n">
         <v>78601</v>
@@ -4194,14 +4194,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518819</v>
+        <v>518559</v>
       </c>
       <c r="R33" t="n">
-        <v>6994817</v>
+        <v>6995004</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,7 +4270,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121345085</v>
+        <v>121346053</v>
       </c>
       <c r="B34" t="n">
         <v>78601</v>
@@ -4306,14 +4306,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518559</v>
+        <v>518560</v>
       </c>
       <c r="R34" t="n">
-        <v>6995004</v>
+        <v>6995039</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346053</v>
+        <v>121343160</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4398,34 +4398,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518560</v>
+        <v>518815</v>
       </c>
       <c r="R35" t="n">
-        <v>6995039</v>
+        <v>6994704</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346533</v>
+        <v>121344213</v>
       </c>
       <c r="B36" t="n">
         <v>78601</v>
@@ -4530,14 +4530,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518703</v>
+        <v>518792</v>
       </c>
       <c r="R36" t="n">
-        <v>6994800</v>
+        <v>6994973</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121344213</v>
+        <v>121346533</v>
       </c>
       <c r="B37" t="n">
         <v>78601</v>
@@ -4642,14 +4642,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518792</v>
+        <v>518703</v>
       </c>
       <c r="R37" t="n">
-        <v>6994973</v>
+        <v>6994800</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121345960</v>
+        <v>121345073</v>
       </c>
       <c r="B63" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7534,21 +7534,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7558,13 +7558,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518444</v>
+        <v>518555</v>
       </c>
       <c r="R63" t="n">
-        <v>6995141</v>
+        <v>6995010</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121345073</v>
+        <v>121343093</v>
       </c>
       <c r="B64" t="n">
         <v>78601</v>
@@ -7666,17 +7666,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518555</v>
+        <v>518801</v>
       </c>
       <c r="R64" t="n">
-        <v>6995010</v>
+        <v>6994670</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121343093</v>
+        <v>121345960</v>
       </c>
       <c r="B65" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7758,37 +7758,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518801</v>
+        <v>518444</v>
       </c>
       <c r="R65" t="n">
-        <v>6994670</v>
+        <v>6995141</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,7 +7854,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121343253</v>
+        <v>121343018</v>
       </c>
       <c r="B66" t="n">
         <v>78601</v>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518799</v>
+        <v>518813</v>
       </c>
       <c r="R66" t="n">
-        <v>6994749</v>
+        <v>6994667</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121346038</v>
+        <v>121343253</v>
       </c>
       <c r="B67" t="n">
         <v>78601</v>
@@ -8002,17 +8002,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518544</v>
+        <v>518799</v>
       </c>
       <c r="R67" t="n">
-        <v>6995061</v>
+        <v>6994749</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343018</v>
+        <v>121346038</v>
       </c>
       <c r="B68" t="n">
         <v>78601</v>
@@ -8114,17 +8114,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518813</v>
+        <v>518544</v>
       </c>
       <c r="R68" t="n">
-        <v>6994667</v>
+        <v>6995061</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343207</v>
+        <v>121345116</v>
       </c>
       <c r="B6" t="n">
-        <v>91259</v>
+        <v>90697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,25 +1138,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,14 +1165,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518808</v>
+        <v>518559</v>
       </c>
       <c r="R6" t="n">
-        <v>6994725</v>
+        <v>6994969</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345116</v>
+        <v>121345946</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,40 +1258,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518559</v>
+        <v>518414</v>
       </c>
       <c r="R7" t="n">
-        <v>6994969</v>
+        <v>6995151</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,7 +1336,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1358,7 +1354,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121344731</v>
+        <v>121346126</v>
       </c>
       <c r="B8" t="n">
         <v>78601</v>
@@ -1398,13 +1394,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518652</v>
+        <v>518627</v>
       </c>
       <c r="R8" t="n">
-        <v>6994988</v>
+        <v>6994984</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345946</v>
+        <v>121343207</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>91259</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,41 +1478,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518414</v>
+        <v>518808</v>
       </c>
       <c r="R9" t="n">
-        <v>6995151</v>
+        <v>6994725</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,6 +1563,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346126</v>
+        <v>121344731</v>
       </c>
       <c r="B10" t="n">
         <v>78601</v>
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518627</v>
+        <v>518652</v>
       </c>
       <c r="R10" t="n">
-        <v>6994984</v>
+        <v>6994988</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346092</v>
+        <v>121346613</v>
       </c>
       <c r="B13" t="n">
         <v>78601</v>
@@ -1954,14 +1954,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518610</v>
+        <v>518770</v>
       </c>
       <c r="R13" t="n">
-        <v>6995000</v>
+        <v>6994702</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346613</v>
+        <v>121346092</v>
       </c>
       <c r="B14" t="n">
         <v>78601</v>
@@ -2066,14 +2066,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518770</v>
+        <v>518610</v>
       </c>
       <c r="R14" t="n">
-        <v>6994702</v>
+        <v>6995000</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121343305</v>
+        <v>121345053</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,34 +2158,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518812</v>
+        <v>518563</v>
       </c>
       <c r="R15" t="n">
-        <v>6994779</v>
+        <v>6995042</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,7 +2254,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121344999</v>
+        <v>121343305</v>
       </c>
       <c r="B16" t="n">
         <v>78601</v>
@@ -2290,14 +2290,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518659</v>
+        <v>518812</v>
       </c>
       <c r="R16" t="n">
-        <v>6995028</v>
+        <v>6994779</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345053</v>
+        <v>121344999</v>
       </c>
       <c r="B17" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,34 +2382,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518563</v>
+        <v>518659</v>
       </c>
       <c r="R17" t="n">
-        <v>6995042</v>
+        <v>6995028</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346595</v>
+        <v>121346232</v>
       </c>
       <c r="B24" t="n">
         <v>78601</v>
@@ -3186,14 +3186,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518786</v>
+        <v>518626</v>
       </c>
       <c r="R24" t="n">
-        <v>6994717</v>
+        <v>6994964</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,7 +3262,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346232</v>
+        <v>121344308</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518626</v>
+        <v>518783</v>
       </c>
       <c r="R25" t="n">
-        <v>6994964</v>
+        <v>6994979</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,7 +3374,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121344308</v>
+        <v>121346595</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3410,14 +3410,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518783</v>
+        <v>518786</v>
       </c>
       <c r="R26" t="n">
-        <v>6994979</v>
+        <v>6994717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121343625</v>
+        <v>121343160</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518819</v>
+        <v>518815</v>
       </c>
       <c r="R32" t="n">
-        <v>6994817</v>
+        <v>6994704</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,7 +4158,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121345085</v>
+        <v>121343625</v>
       </c>
       <c r="B33" t="n">
         <v>78601</v>
@@ -4194,14 +4194,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518559</v>
+        <v>518819</v>
       </c>
       <c r="R33" t="n">
-        <v>6995004</v>
+        <v>6994817</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,7 +4270,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121346053</v>
+        <v>121345085</v>
       </c>
       <c r="B34" t="n">
         <v>78601</v>
@@ -4306,14 +4306,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518560</v>
+        <v>518559</v>
       </c>
       <c r="R34" t="n">
-        <v>6995039</v>
+        <v>6995004</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121343160</v>
+        <v>121346053</v>
       </c>
       <c r="B35" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4398,34 +4398,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518815</v>
+        <v>518560</v>
       </c>
       <c r="R35" t="n">
-        <v>6994704</v>
+        <v>6995039</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121344213</v>
+        <v>121346533</v>
       </c>
       <c r="B36" t="n">
         <v>78601</v>
@@ -4530,14 +4530,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518792</v>
+        <v>518703</v>
       </c>
       <c r="R36" t="n">
-        <v>6994973</v>
+        <v>6994800</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346533</v>
+        <v>121344213</v>
       </c>
       <c r="B37" t="n">
         <v>78601</v>
@@ -4642,14 +4642,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518703</v>
+        <v>518792</v>
       </c>
       <c r="R37" t="n">
-        <v>6994800</v>
+        <v>6994973</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5614,7 +5614,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121346025</v>
+        <v>121346560</v>
       </c>
       <c r="B46" t="n">
         <v>78601</v>
@@ -5650,14 +5650,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518519</v>
+        <v>518787</v>
       </c>
       <c r="R46" t="n">
-        <v>6995085</v>
+        <v>6994752</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,7 +5726,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121346560</v>
+        <v>121345122</v>
       </c>
       <c r="B47" t="n">
         <v>78601</v>
@@ -5762,14 +5762,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518787</v>
+        <v>518552</v>
       </c>
       <c r="R47" t="n">
-        <v>6994752</v>
+        <v>6994973</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,7 +5838,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121343524</v>
+        <v>121346025</v>
       </c>
       <c r="B48" t="n">
         <v>78601</v>
@@ -5874,17 +5874,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518815</v>
+        <v>518519</v>
       </c>
       <c r="R48" t="n">
-        <v>6994807</v>
+        <v>6995085</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,7 +5950,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121345122</v>
+        <v>121343524</v>
       </c>
       <c r="B49" t="n">
         <v>78601</v>
@@ -5986,17 +5986,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518552</v>
+        <v>518815</v>
       </c>
       <c r="R49" t="n">
-        <v>6994973</v>
+        <v>6994807</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7854,7 +7854,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121343018</v>
+        <v>121343253</v>
       </c>
       <c r="B66" t="n">
         <v>78601</v>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518813</v>
+        <v>518799</v>
       </c>
       <c r="R66" t="n">
-        <v>6994667</v>
+        <v>6994749</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121343253</v>
+        <v>121346038</v>
       </c>
       <c r="B67" t="n">
         <v>78601</v>
@@ -8002,17 +8002,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518799</v>
+        <v>518544</v>
       </c>
       <c r="R67" t="n">
-        <v>6994749</v>
+        <v>6995061</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121346038</v>
+        <v>121343018</v>
       </c>
       <c r="B68" t="n">
         <v>78601</v>
@@ -8114,17 +8114,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518544</v>
+        <v>518813</v>
       </c>
       <c r="R68" t="n">
-        <v>6995061</v>
+        <v>6994667</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121343196</v>
+        <v>121345116</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +806,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518797</v>
+        <v>518559</v>
       </c>
       <c r="R3" t="n">
-        <v>6994707</v>
+        <v>6994969</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346005</v>
+        <v>121344384</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,37 +922,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518483</v>
+        <v>518741</v>
       </c>
       <c r="R4" t="n">
-        <v>6995124</v>
+        <v>6994995</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344456</v>
+        <v>121343959</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1054,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518727</v>
+        <v>518825</v>
       </c>
       <c r="R5" t="n">
-        <v>6994987</v>
+        <v>6994907</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345116</v>
+        <v>121345938</v>
       </c>
       <c r="B6" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,40 +1146,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518559</v>
+        <v>518387</v>
       </c>
       <c r="R6" t="n">
-        <v>6994969</v>
+        <v>6995152</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1214,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1224,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345946</v>
+        <v>121345954</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,21 +1258,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518414</v>
+        <v>518428</v>
       </c>
       <c r="R7" t="n">
-        <v>6995151</v>
+        <v>6995142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346126</v>
+        <v>121343920</v>
       </c>
       <c r="B8" t="n">
         <v>78601</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518627</v>
+        <v>518807</v>
       </c>
       <c r="R8" t="n">
-        <v>6994984</v>
+        <v>6994899</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343207</v>
+        <v>121346533</v>
       </c>
       <c r="B9" t="n">
-        <v>91259</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,44 +1478,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518808</v>
+        <v>518703</v>
       </c>
       <c r="R9" t="n">
-        <v>6994725</v>
+        <v>6994800</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,7 +1560,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1582,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121344731</v>
+        <v>121343524</v>
       </c>
       <c r="B10" t="n">
         <v>78601</v>
@@ -1618,17 +1614,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518652</v>
+        <v>518815</v>
       </c>
       <c r="R10" t="n">
-        <v>6994988</v>
+        <v>6994807</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1657,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343797</v>
+        <v>121346620</v>
       </c>
       <c r="B11" t="n">
         <v>78601</v>
@@ -1730,17 +1726,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518812</v>
+        <v>518774</v>
       </c>
       <c r="R11" t="n">
-        <v>6994875</v>
+        <v>6994685</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1769,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343229</v>
+        <v>121343797</v>
       </c>
       <c r="B12" t="n">
         <v>78601</v>
@@ -1842,14 +1838,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518808</v>
+        <v>518812</v>
       </c>
       <c r="R12" t="n">
-        <v>6994725</v>
+        <v>6994875</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1881,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346613</v>
+        <v>121346430</v>
       </c>
       <c r="B13" t="n">
         <v>78601</v>
@@ -1954,17 +1950,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518770</v>
+        <v>518614</v>
       </c>
       <c r="R13" t="n">
-        <v>6994702</v>
+        <v>6994902</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1993,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2026,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346092</v>
+        <v>121344818</v>
       </c>
       <c r="B14" t="n">
         <v>78601</v>
@@ -2070,13 +2066,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518610</v>
+        <v>518624</v>
       </c>
       <c r="R14" t="n">
-        <v>6995000</v>
+        <v>6995059</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345053</v>
+        <v>121343303</v>
       </c>
       <c r="B15" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,37 +2154,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518563</v>
+        <v>518809</v>
       </c>
       <c r="R15" t="n">
-        <v>6995042</v>
+        <v>6994765</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,7 +2213,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2227,7 +2223,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121343305</v>
+        <v>121343285</v>
       </c>
       <c r="B16" t="n">
         <v>78601</v>
@@ -2294,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518812</v>
+        <v>518804</v>
       </c>
       <c r="R16" t="n">
-        <v>6994779</v>
+        <v>6994760</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2329,7 +2325,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2335,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121344999</v>
+        <v>121343249</v>
       </c>
       <c r="B17" t="n">
         <v>78601</v>
@@ -2402,17 +2398,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518659</v>
+        <v>518808</v>
       </c>
       <c r="R17" t="n">
-        <v>6995028</v>
+        <v>6994740</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2441,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2447,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,7 +2474,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346074</v>
+        <v>121344731</v>
       </c>
       <c r="B18" t="n">
         <v>78601</v>
@@ -2518,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518583</v>
+        <v>518652</v>
       </c>
       <c r="R18" t="n">
-        <v>6995023</v>
+        <v>6994988</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,7 +2586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121343959</v>
+        <v>121344380</v>
       </c>
       <c r="B19" t="n">
         <v>78601</v>
@@ -2630,13 +2626,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518825</v>
+        <v>518768</v>
       </c>
       <c r="R19" t="n">
-        <v>6994907</v>
+        <v>6994994</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2665,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346635</v>
+        <v>121346092</v>
       </c>
       <c r="B20" t="n">
         <v>78601</v>
@@ -2738,17 +2734,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518776</v>
+        <v>518610</v>
       </c>
       <c r="R20" t="n">
-        <v>6994684</v>
+        <v>6995000</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2777,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,7 +2810,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121346430</v>
+        <v>121345064</v>
       </c>
       <c r="B21" t="n">
         <v>78601</v>
@@ -2850,14 +2846,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518614</v>
+        <v>518566</v>
       </c>
       <c r="R21" t="n">
-        <v>6994902</v>
+        <v>6995030</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,7 +2922,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121345064</v>
+        <v>121344193</v>
       </c>
       <c r="B22" t="n">
         <v>78601</v>
@@ -2962,17 +2958,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518566</v>
+        <v>518808</v>
       </c>
       <c r="R22" t="n">
-        <v>6995030</v>
+        <v>6994956</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,7 +3034,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121344796</v>
+        <v>121343468</v>
       </c>
       <c r="B23" t="n">
         <v>78601</v>
@@ -3074,14 +3070,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518665</v>
+        <v>518814</v>
       </c>
       <c r="R23" t="n">
-        <v>6995040</v>
+        <v>6994789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3113,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346232</v>
+        <v>121345053</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3166,37 +3162,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518626</v>
+        <v>518563</v>
       </c>
       <c r="R24" t="n">
-        <v>6994964</v>
+        <v>6995042</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3225,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,7 +3258,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121344308</v>
+        <v>121346595</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3298,14 +3294,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518783</v>
+        <v>518786</v>
       </c>
       <c r="R25" t="n">
-        <v>6994979</v>
+        <v>6994717</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,7 +3370,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346595</v>
+        <v>121343093</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3414,13 +3410,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518786</v>
+        <v>518801</v>
       </c>
       <c r="R26" t="n">
-        <v>6994717</v>
+        <v>6994670</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3449,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121343920</v>
+        <v>121345085</v>
       </c>
       <c r="B27" t="n">
         <v>78601</v>
@@ -3526,10 +3522,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518807</v>
+        <v>518559</v>
       </c>
       <c r="R27" t="n">
-        <v>6994899</v>
+        <v>6995004</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3561,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,7 +3594,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121343092</v>
+        <v>121344796</v>
       </c>
       <c r="B28" t="n">
         <v>78601</v>
@@ -3634,17 +3630,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518811</v>
+        <v>518665</v>
       </c>
       <c r="R28" t="n">
-        <v>6994686</v>
+        <v>6995040</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3673,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,10 +3706,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121344384</v>
+        <v>121343092</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3726,34 +3722,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518741</v>
+        <v>518811</v>
       </c>
       <c r="R29" t="n">
-        <v>6994995</v>
+        <v>6994686</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3785,7 +3781,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3791,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,7 +3818,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344380</v>
+        <v>121343298</v>
       </c>
       <c r="B30" t="n">
         <v>78601</v>
@@ -3858,17 +3854,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518768</v>
+        <v>518812</v>
       </c>
       <c r="R30" t="n">
-        <v>6994994</v>
+        <v>6994775</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3897,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,7 +3930,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121344818</v>
+        <v>121343732</v>
       </c>
       <c r="B31" t="n">
         <v>78601</v>
@@ -3974,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518624</v>
+        <v>518817</v>
       </c>
       <c r="R31" t="n">
-        <v>6995059</v>
+        <v>6994855</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4009,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121343160</v>
+        <v>121346289</v>
       </c>
       <c r="B32" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4062,34 +4058,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518815</v>
+        <v>518618</v>
       </c>
       <c r="R32" t="n">
-        <v>6994704</v>
+        <v>6994929</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4121,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,7 +4154,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121343625</v>
+        <v>121345946</v>
       </c>
       <c r="B33" t="n">
         <v>78601</v>
@@ -4194,17 +4190,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518819</v>
+        <v>518414</v>
       </c>
       <c r="R33" t="n">
-        <v>6994817</v>
+        <v>6995151</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4233,7 +4229,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4239,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,7 +4266,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121345085</v>
+        <v>121343253</v>
       </c>
       <c r="B34" t="n">
         <v>78601</v>
@@ -4306,14 +4302,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518559</v>
+        <v>518799</v>
       </c>
       <c r="R34" t="n">
-        <v>6995004</v>
+        <v>6994749</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4345,7 +4341,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4351,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,7 +4378,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346053</v>
+        <v>121346560</v>
       </c>
       <c r="B35" t="n">
         <v>78601</v>
@@ -4418,17 +4414,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518560</v>
+        <v>518787</v>
       </c>
       <c r="R35" t="n">
-        <v>6995039</v>
+        <v>6994752</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4457,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4463,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346533</v>
+        <v>121343478</v>
       </c>
       <c r="B36" t="n">
         <v>78601</v>
@@ -4534,10 +4530,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518703</v>
+        <v>518834</v>
       </c>
       <c r="R36" t="n">
-        <v>6994800</v>
+        <v>6994815</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4569,7 +4565,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4575,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,7 +4602,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121344213</v>
+        <v>121346586</v>
       </c>
       <c r="B37" t="n">
         <v>78601</v>
@@ -4642,14 +4638,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518792</v>
+        <v>518787</v>
       </c>
       <c r="R37" t="n">
-        <v>6994973</v>
+        <v>6994738</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,7 +4677,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4687,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,7 +4714,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121343303</v>
+        <v>121345073</v>
       </c>
       <c r="B38" t="n">
         <v>78601</v>
@@ -4754,14 +4750,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518809</v>
+        <v>518555</v>
       </c>
       <c r="R38" t="n">
-        <v>6994765</v>
+        <v>6995010</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4793,7 +4789,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4799,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,10 +4826,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121343289</v>
+        <v>121343160</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4846,21 +4842,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4870,10 +4866,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518814</v>
+        <v>518815</v>
       </c>
       <c r="R39" t="n">
-        <v>6994762</v>
+        <v>6994704</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4905,7 +4901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4911,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,7 +4938,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121343285</v>
+        <v>121346074</v>
       </c>
       <c r="B40" t="n">
         <v>78601</v>
@@ -4978,17 +4974,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518804</v>
+        <v>518583</v>
       </c>
       <c r="R40" t="n">
-        <v>6994760</v>
+        <v>6995023</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5017,7 +5013,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5027,7 +5023,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,7 +5050,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121343732</v>
+        <v>121346005</v>
       </c>
       <c r="B41" t="n">
         <v>78601</v>
@@ -5090,14 +5086,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518817</v>
+        <v>518483</v>
       </c>
       <c r="R41" t="n">
-        <v>6994855</v>
+        <v>6995124</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5129,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5139,7 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,7 +5162,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121343472</v>
+        <v>121346635</v>
       </c>
       <c r="B42" t="n">
         <v>78601</v>
@@ -5206,13 +5202,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518814</v>
+        <v>518776</v>
       </c>
       <c r="R42" t="n">
-        <v>6994800</v>
+        <v>6994684</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5241,7 +5237,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5251,7 +5247,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5278,7 +5274,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121343178</v>
+        <v>121343137</v>
       </c>
       <c r="B43" t="n">
         <v>78601</v>
@@ -5318,13 +5314,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518814</v>
+        <v>518823</v>
       </c>
       <c r="R43" t="n">
-        <v>6994717</v>
+        <v>6994691</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5353,7 +5349,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5359,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,7 +5386,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121344193</v>
+        <v>121344308</v>
       </c>
       <c r="B44" t="n">
         <v>78601</v>
@@ -5430,13 +5426,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518808</v>
+        <v>518783</v>
       </c>
       <c r="R44" t="n">
-        <v>6994956</v>
+        <v>6994979</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5465,7 +5461,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5475,7 +5471,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,7 +5498,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121343249</v>
+        <v>121343625</v>
       </c>
       <c r="B45" t="n">
         <v>78601</v>
@@ -5542,13 +5538,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518808</v>
+        <v>518819</v>
       </c>
       <c r="R45" t="n">
-        <v>6994740</v>
+        <v>6994817</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5577,7 +5573,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5587,7 +5583,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5614,7 +5610,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121346560</v>
+        <v>121346232</v>
       </c>
       <c r="B46" t="n">
         <v>78601</v>
@@ -5650,14 +5646,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518787</v>
+        <v>518626</v>
       </c>
       <c r="R46" t="n">
-        <v>6994752</v>
+        <v>6994964</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5689,7 +5685,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5699,7 +5695,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,7 +5722,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121345122</v>
+        <v>121343289</v>
       </c>
       <c r="B47" t="n">
         <v>78601</v>
@@ -5762,17 +5758,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518552</v>
+        <v>518814</v>
       </c>
       <c r="R47" t="n">
-        <v>6994973</v>
+        <v>6994762</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5801,7 +5797,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5807,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,7 +5834,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121346025</v>
+        <v>121346126</v>
       </c>
       <c r="B48" t="n">
         <v>78601</v>
@@ -5874,17 +5870,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518519</v>
+        <v>518627</v>
       </c>
       <c r="R48" t="n">
-        <v>6995085</v>
+        <v>6994984</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5913,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,7 +5946,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121343524</v>
+        <v>121346038</v>
       </c>
       <c r="B49" t="n">
         <v>78601</v>
@@ -5986,17 +5982,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518815</v>
+        <v>518544</v>
       </c>
       <c r="R49" t="n">
-        <v>6994807</v>
+        <v>6995061</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6025,7 +6021,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6031,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6062,10 +6058,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121345954</v>
+        <v>121343018</v>
       </c>
       <c r="B50" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6078,37 +6074,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518428</v>
+        <v>518813</v>
       </c>
       <c r="R50" t="n">
-        <v>6995142</v>
+        <v>6994667</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6174,10 +6170,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121343298</v>
+        <v>121345960</v>
       </c>
       <c r="B51" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6190,37 +6186,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518812</v>
+        <v>518444</v>
       </c>
       <c r="R51" t="n">
-        <v>6994775</v>
+        <v>6995141</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6249,7 +6245,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,7 +6255,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6286,7 +6282,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121345938</v>
+        <v>121343196</v>
       </c>
       <c r="B52" t="n">
         <v>78601</v>
@@ -6322,17 +6318,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518387</v>
+        <v>518797</v>
       </c>
       <c r="R52" t="n">
-        <v>6995152</v>
+        <v>6994707</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6361,7 +6357,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,7 +6367,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6398,10 +6394,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121346289</v>
+        <v>121343207</v>
       </c>
       <c r="B53" t="n">
-        <v>78601</v>
+        <v>91259</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6410,38 +6406,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518618</v>
+        <v>518808</v>
       </c>
       <c r="R53" t="n">
-        <v>6994929</v>
+        <v>6994725</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6473,7 +6472,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6482,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6492,6 +6491,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6510,7 +6510,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121346620</v>
+        <v>121344213</v>
       </c>
       <c r="B54" t="n">
         <v>78601</v>
@@ -6546,14 +6546,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518774</v>
+        <v>518792</v>
       </c>
       <c r="R54" t="n">
-        <v>6994685</v>
+        <v>6994973</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,7 +6622,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121345918</v>
+        <v>121345972</v>
       </c>
       <c r="B55" t="n">
         <v>78601</v>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518360</v>
+        <v>518465</v>
       </c>
       <c r="R55" t="n">
-        <v>6995099</v>
+        <v>6995120</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,7 +6734,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121343137</v>
+        <v>121346025</v>
       </c>
       <c r="B56" t="n">
         <v>78601</v>
@@ -6770,17 +6770,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518823</v>
+        <v>518519</v>
       </c>
       <c r="R56" t="n">
-        <v>6994691</v>
+        <v>6995085</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,7 +6846,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343478</v>
+        <v>121343305</v>
       </c>
       <c r="B57" t="n">
         <v>78601</v>
@@ -6886,13 +6886,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518834</v>
+        <v>518812</v>
       </c>
       <c r="R57" t="n">
-        <v>6994815</v>
+        <v>6994779</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121346586</v>
+        <v>121343022</v>
       </c>
       <c r="B58" t="n">
         <v>78601</v>
@@ -6998,13 +6998,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518787</v>
+        <v>518814</v>
       </c>
       <c r="R58" t="n">
-        <v>6994738</v>
+        <v>6994676</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,7 +7070,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121343809</v>
+        <v>121345918</v>
       </c>
       <c r="B59" t="n">
         <v>78601</v>
@@ -7106,17 +7106,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518808</v>
+        <v>518360</v>
       </c>
       <c r="R59" t="n">
-        <v>6994892</v>
+        <v>6995099</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,7 +7182,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121343022</v>
+        <v>121343809</v>
       </c>
       <c r="B60" t="n">
         <v>78601</v>
@@ -7218,17 +7218,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518814</v>
+        <v>518808</v>
       </c>
       <c r="R60" t="n">
-        <v>6994676</v>
+        <v>6994892</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,7 +7294,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121345972</v>
+        <v>121344999</v>
       </c>
       <c r="B61" t="n">
         <v>78601</v>
@@ -7330,14 +7330,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518465</v>
+        <v>518659</v>
       </c>
       <c r="R61" t="n">
-        <v>6995120</v>
+        <v>6995028</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,7 +7406,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121343468</v>
+        <v>121343229</v>
       </c>
       <c r="B62" t="n">
         <v>78601</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518814</v>
+        <v>518808</v>
       </c>
       <c r="R62" t="n">
-        <v>6994789</v>
+        <v>6994725</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,7 +7518,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121345073</v>
+        <v>121345122</v>
       </c>
       <c r="B63" t="n">
         <v>78601</v>
@@ -7554,14 +7554,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518555</v>
+        <v>518552</v>
       </c>
       <c r="R63" t="n">
-        <v>6995010</v>
+        <v>6994973</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343093</v>
+        <v>121343472</v>
       </c>
       <c r="B64" t="n">
         <v>78601</v>
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518801</v>
+        <v>518814</v>
       </c>
       <c r="R64" t="n">
-        <v>6994670</v>
+        <v>6994800</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121345960</v>
+        <v>121343178</v>
       </c>
       <c r="B65" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7758,37 +7758,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518444</v>
+        <v>518814</v>
       </c>
       <c r="R65" t="n">
-        <v>6995141</v>
+        <v>6994717</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,7 +7854,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121343253</v>
+        <v>121344456</v>
       </c>
       <c r="B66" t="n">
         <v>78601</v>
@@ -7890,14 +7890,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518799</v>
+        <v>518727</v>
       </c>
       <c r="R66" t="n">
-        <v>6994749</v>
+        <v>6994987</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121346038</v>
+        <v>121346053</v>
       </c>
       <c r="B67" t="n">
         <v>78601</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518544</v>
+        <v>518560</v>
       </c>
       <c r="R67" t="n">
-        <v>6995061</v>
+        <v>6995039</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343018</v>
+        <v>121346613</v>
       </c>
       <c r="B68" t="n">
         <v>78601</v>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518813</v>
+        <v>518770</v>
       </c>
       <c r="R68" t="n">
-        <v>6994667</v>
+        <v>6994702</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -3146,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121345053</v>
+        <v>121346595</v>
       </c>
       <c r="B24" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,37 +3162,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518563</v>
+        <v>518786</v>
       </c>
       <c r="R24" t="n">
-        <v>6995042</v>
+        <v>6994717</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,7 +3258,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346595</v>
+        <v>121343093</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3298,13 +3298,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518786</v>
+        <v>518801</v>
       </c>
       <c r="R25" t="n">
-        <v>6994717</v>
+        <v>6994670</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,7 +3370,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121343093</v>
+        <v>121345085</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3406,17 +3406,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518801</v>
+        <v>518559</v>
       </c>
       <c r="R26" t="n">
-        <v>6994670</v>
+        <v>6995004</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121345085</v>
+        <v>121344796</v>
       </c>
       <c r="B27" t="n">
         <v>78601</v>
@@ -3522,13 +3522,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518559</v>
+        <v>518665</v>
       </c>
       <c r="R27" t="n">
-        <v>6995004</v>
+        <v>6995040</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121344796</v>
+        <v>121345053</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3610,37 +3610,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518665</v>
+        <v>518563</v>
       </c>
       <c r="R28" t="n">
-        <v>6995040</v>
+        <v>6995042</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345116</v>
+        <v>121346232</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,40 +806,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518559</v>
+        <v>518626</v>
       </c>
       <c r="R3" t="n">
-        <v>6994969</v>
+        <v>6994964</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +884,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121344384</v>
+        <v>121345918</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518741</v>
+        <v>518360</v>
       </c>
       <c r="R4" t="n">
-        <v>6994995</v>
+        <v>6995099</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343959</v>
+        <v>121343207</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>91271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,38 +1026,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518825</v>
+        <v>518808</v>
       </c>
       <c r="R5" t="n">
-        <v>6994907</v>
+        <v>6994725</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,6 +1111,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345938</v>
+        <v>121343298</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,14 +1166,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518387</v>
+        <v>518812</v>
       </c>
       <c r="R6" t="n">
-        <v>6995152</v>
+        <v>6994775</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345954</v>
+        <v>121345972</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,21 +1258,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518428</v>
+        <v>518465</v>
       </c>
       <c r="R7" t="n">
-        <v>6995142</v>
+        <v>6995120</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343920</v>
+        <v>121346025</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518807</v>
+        <v>518519</v>
       </c>
       <c r="R8" t="n">
-        <v>6994899</v>
+        <v>6995085</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346533</v>
+        <v>121345946</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,14 +1502,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518703</v>
+        <v>518414</v>
       </c>
       <c r="R9" t="n">
-        <v>6994800</v>
+        <v>6995151</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343524</v>
+        <v>121346586</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518815</v>
+        <v>518787</v>
       </c>
       <c r="R10" t="n">
-        <v>6994807</v>
+        <v>6994738</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346620</v>
+        <v>121344193</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,17 +1726,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518774</v>
+        <v>518808</v>
       </c>
       <c r="R11" t="n">
-        <v>6994685</v>
+        <v>6994956</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343797</v>
+        <v>121346038</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,17 +1838,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518812</v>
+        <v>518544</v>
       </c>
       <c r="R12" t="n">
-        <v>6994875</v>
+        <v>6995061</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346430</v>
+        <v>121346126</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518614</v>
+        <v>518627</v>
       </c>
       <c r="R13" t="n">
-        <v>6994902</v>
+        <v>6994984</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121344818</v>
+        <v>121343253</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,17 +2062,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518624</v>
+        <v>518799</v>
       </c>
       <c r="R14" t="n">
-        <v>6995059</v>
+        <v>6994749</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121343303</v>
+        <v>121344796</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,14 +2174,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518809</v>
+        <v>518665</v>
       </c>
       <c r="R15" t="n">
-        <v>6994765</v>
+        <v>6995040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121343285</v>
+        <v>121343303</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518804</v>
+        <v>518809</v>
       </c>
       <c r="R16" t="n">
-        <v>6994760</v>
+        <v>6994765</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121343249</v>
+        <v>121346620</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518808</v>
+        <v>518774</v>
       </c>
       <c r="R17" t="n">
-        <v>6994740</v>
+        <v>6994685</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121344731</v>
+        <v>121346533</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,14 +2510,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518652</v>
+        <v>518703</v>
       </c>
       <c r="R18" t="n">
-        <v>6994988</v>
+        <v>6994800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121344380</v>
+        <v>121343524</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,17 +2622,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518768</v>
+        <v>518815</v>
       </c>
       <c r="R19" t="n">
-        <v>6994994</v>
+        <v>6994807</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346092</v>
+        <v>121343468</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,17 +2734,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518610</v>
+        <v>518814</v>
       </c>
       <c r="R20" t="n">
-        <v>6995000</v>
+        <v>6994789</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121345064</v>
+        <v>121343249</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,14 +2846,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518566</v>
+        <v>518808</v>
       </c>
       <c r="R21" t="n">
-        <v>6995030</v>
+        <v>6994740</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121344193</v>
+        <v>121343196</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,14 +2958,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518808</v>
+        <v>518797</v>
       </c>
       <c r="R22" t="n">
-        <v>6994956</v>
+        <v>6994707</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121343468</v>
+        <v>121344308</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3070,14 +3070,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518814</v>
+        <v>518783</v>
       </c>
       <c r="R23" t="n">
-        <v>6994789</v>
+        <v>6994979</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3146,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346595</v>
+        <v>121345960</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,37 +3162,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518786</v>
+        <v>518444</v>
       </c>
       <c r="R24" t="n">
-        <v>6994717</v>
+        <v>6995141</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,10 +3258,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121343093</v>
+        <v>121345954</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518801</v>
+        <v>518428</v>
       </c>
       <c r="R25" t="n">
-        <v>6994670</v>
+        <v>6995142</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121345085</v>
+        <v>121346053</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3406,14 +3406,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518559</v>
+        <v>518560</v>
       </c>
       <c r="R26" t="n">
-        <v>6995004</v>
+        <v>6995039</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121344796</v>
+        <v>121346595</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3518,14 +3518,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518665</v>
+        <v>518786</v>
       </c>
       <c r="R27" t="n">
-        <v>6995040</v>
+        <v>6994717</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121345053</v>
+        <v>121345073</v>
       </c>
       <c r="B28" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518563</v>
+        <v>518555</v>
       </c>
       <c r="R28" t="n">
-        <v>6995042</v>
+        <v>6995010</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,10 +3706,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343092</v>
+        <v>121343797</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3742,14 +3742,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518811</v>
+        <v>518812</v>
       </c>
       <c r="R29" t="n">
-        <v>6994686</v>
+        <v>6994875</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121343298</v>
+        <v>121344213</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3854,14 +3854,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518812</v>
+        <v>518792</v>
       </c>
       <c r="R30" t="n">
-        <v>6994775</v>
+        <v>6994973</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121343732</v>
+        <v>121346005</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,14 +3966,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518817</v>
+        <v>518483</v>
       </c>
       <c r="R31" t="n">
-        <v>6994855</v>
+        <v>6995124</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346289</v>
+        <v>121346635</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,17 +4078,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518618</v>
+        <v>518776</v>
       </c>
       <c r="R32" t="n">
-        <v>6994929</v>
+        <v>6994684</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121345946</v>
+        <v>121344999</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,17 +4190,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518414</v>
+        <v>518659</v>
       </c>
       <c r="R33" t="n">
-        <v>6995151</v>
+        <v>6995028</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,10 +4266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121343253</v>
+        <v>121344456</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4302,14 +4302,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518799</v>
+        <v>518727</v>
       </c>
       <c r="R34" t="n">
-        <v>6994749</v>
+        <v>6994987</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346560</v>
+        <v>121343178</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518787</v>
+        <v>518814</v>
       </c>
       <c r="R35" t="n">
-        <v>6994752</v>
+        <v>6994717</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121343478</v>
+        <v>121343160</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4530,13 +4530,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518834</v>
+        <v>518815</v>
       </c>
       <c r="R36" t="n">
-        <v>6994815</v>
+        <v>6994704</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,10 +4602,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346586</v>
+        <v>121346074</v>
       </c>
       <c r="B37" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,14 +4638,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518787</v>
+        <v>518583</v>
       </c>
       <c r="R37" t="n">
-        <v>6994738</v>
+        <v>6995023</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121345073</v>
+        <v>121346613</v>
       </c>
       <c r="B38" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4750,17 +4750,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518555</v>
+        <v>518770</v>
       </c>
       <c r="R38" t="n">
-        <v>6995010</v>
+        <v>6994702</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121343160</v>
+        <v>121343229</v>
       </c>
       <c r="B39" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4842,21 +4842,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518815</v>
+        <v>518808</v>
       </c>
       <c r="R39" t="n">
-        <v>6994704</v>
+        <v>6994725</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4938,10 +4938,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121346074</v>
+        <v>121343022</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4974,17 +4974,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518583</v>
+        <v>518814</v>
       </c>
       <c r="R40" t="n">
-        <v>6995023</v>
+        <v>6994676</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5050,10 +5050,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121346005</v>
+        <v>121346092</v>
       </c>
       <c r="B41" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5086,17 +5086,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518483</v>
+        <v>518610</v>
       </c>
       <c r="R41" t="n">
-        <v>6995124</v>
+        <v>6995000</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5162,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121346635</v>
+        <v>121343137</v>
       </c>
       <c r="B42" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5202,13 +5202,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518776</v>
+        <v>518823</v>
       </c>
       <c r="R42" t="n">
-        <v>6994684</v>
+        <v>6994691</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5274,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121343137</v>
+        <v>121343285</v>
       </c>
       <c r="B43" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518823</v>
+        <v>518804</v>
       </c>
       <c r="R43" t="n">
-        <v>6994691</v>
+        <v>6994760</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5386,10 +5386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121344308</v>
+        <v>121343959</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518783</v>
+        <v>518825</v>
       </c>
       <c r="R44" t="n">
-        <v>6994979</v>
+        <v>6994907</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5498,10 +5498,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121343625</v>
+        <v>121344380</v>
       </c>
       <c r="B45" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5534,17 +5534,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518819</v>
+        <v>518768</v>
       </c>
       <c r="R45" t="n">
-        <v>6994817</v>
+        <v>6994994</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5610,10 +5610,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121346232</v>
+        <v>121345064</v>
       </c>
       <c r="B46" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5646,14 +5646,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518626</v>
+        <v>518566</v>
       </c>
       <c r="R46" t="n">
-        <v>6994964</v>
+        <v>6995030</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,10 +5722,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121343289</v>
+        <v>121344731</v>
       </c>
       <c r="B47" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5758,17 +5758,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518814</v>
+        <v>518652</v>
       </c>
       <c r="R47" t="n">
-        <v>6994762</v>
+        <v>6994988</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5834,10 +5834,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121346126</v>
+        <v>121343809</v>
       </c>
       <c r="B48" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5874,13 +5874,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518627</v>
+        <v>518808</v>
       </c>
       <c r="R48" t="n">
-        <v>6994984</v>
+        <v>6994892</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5946,10 +5946,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121346038</v>
+        <v>121344384</v>
       </c>
       <c r="B49" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5962,37 +5962,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518544</v>
+        <v>518741</v>
       </c>
       <c r="R49" t="n">
-        <v>6995061</v>
+        <v>6994995</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6058,10 +6058,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121343018</v>
+        <v>121345938</v>
       </c>
       <c r="B50" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6094,17 +6094,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518813</v>
+        <v>518387</v>
       </c>
       <c r="R50" t="n">
-        <v>6994667</v>
+        <v>6995152</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6170,10 +6170,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121345960</v>
+        <v>121345116</v>
       </c>
       <c r="B51" t="n">
-        <v>79682</v>
+        <v>90709</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6186,34 +6186,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518444</v>
+        <v>518559</v>
       </c>
       <c r="R51" t="n">
-        <v>6995141</v>
+        <v>6994969</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6245,7 +6248,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6255,7 +6258,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6264,6 +6267,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6282,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121343196</v>
+        <v>121346430</v>
       </c>
       <c r="B52" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6318,17 +6322,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518797</v>
+        <v>518614</v>
       </c>
       <c r="R52" t="n">
-        <v>6994707</v>
+        <v>6994902</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6367,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6394,10 +6398,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121343207</v>
+        <v>121345053</v>
       </c>
       <c r="B53" t="n">
-        <v>91259</v>
+        <v>79685</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6406,41 +6410,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518808</v>
+        <v>518563</v>
       </c>
       <c r="R53" t="n">
-        <v>6994725</v>
+        <v>6995042</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6472,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6482,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6491,7 +6492,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121344213</v>
+        <v>121343472</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6546,17 +6546,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518792</v>
+        <v>518814</v>
       </c>
       <c r="R54" t="n">
-        <v>6994973</v>
+        <v>6994800</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,10 +6622,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121345972</v>
+        <v>121343478</v>
       </c>
       <c r="B55" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6658,17 +6658,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518465</v>
+        <v>518834</v>
       </c>
       <c r="R55" t="n">
-        <v>6995120</v>
+        <v>6994815</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,10 +6734,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121346025</v>
+        <v>121343625</v>
       </c>
       <c r="B56" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6770,17 +6770,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518519</v>
+        <v>518819</v>
       </c>
       <c r="R56" t="n">
-        <v>6995085</v>
+        <v>6994817</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343305</v>
+        <v>121343920</v>
       </c>
       <c r="B57" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6882,14 +6882,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518812</v>
+        <v>518807</v>
       </c>
       <c r="R57" t="n">
-        <v>6994779</v>
+        <v>6994899</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,10 +6958,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121343022</v>
+        <v>121345085</v>
       </c>
       <c r="B58" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6994,14 +6994,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518814</v>
+        <v>518559</v>
       </c>
       <c r="R58" t="n">
-        <v>6994676</v>
+        <v>6995004</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,10 +7070,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121345918</v>
+        <v>121344818</v>
       </c>
       <c r="B59" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7106,17 +7106,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518360</v>
+        <v>518624</v>
       </c>
       <c r="R59" t="n">
-        <v>6995099</v>
+        <v>6995059</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121343809</v>
+        <v>121343289</v>
       </c>
       <c r="B60" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7218,17 +7218,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518808</v>
+        <v>518814</v>
       </c>
       <c r="R60" t="n">
-        <v>6994892</v>
+        <v>6994762</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,10 +7294,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121344999</v>
+        <v>121345122</v>
       </c>
       <c r="B61" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7334,13 +7334,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518659</v>
+        <v>518552</v>
       </c>
       <c r="R61" t="n">
-        <v>6995028</v>
+        <v>6994973</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121343229</v>
+        <v>121343732</v>
       </c>
       <c r="B62" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7442,17 +7442,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518808</v>
+        <v>518817</v>
       </c>
       <c r="R62" t="n">
-        <v>6994725</v>
+        <v>6994855</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121345122</v>
+        <v>121346560</v>
       </c>
       <c r="B63" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7554,14 +7554,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518552</v>
+        <v>518787</v>
       </c>
       <c r="R63" t="n">
-        <v>6994973</v>
+        <v>6994752</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,10 +7630,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343472</v>
+        <v>121343093</v>
       </c>
       <c r="B64" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518814</v>
+        <v>518801</v>
       </c>
       <c r="R64" t="n">
-        <v>6994800</v>
+        <v>6994670</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121343178</v>
+        <v>121346289</v>
       </c>
       <c r="B65" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7778,17 +7778,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518814</v>
+        <v>518618</v>
       </c>
       <c r="R65" t="n">
-        <v>6994717</v>
+        <v>6994929</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,10 +7854,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121344456</v>
+        <v>121343092</v>
       </c>
       <c r="B66" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7890,14 +7890,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518727</v>
+        <v>518811</v>
       </c>
       <c r="R66" t="n">
-        <v>6994987</v>
+        <v>6994686</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121346053</v>
+        <v>121343018</v>
       </c>
       <c r="B67" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,14 +8002,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518560</v>
+        <v>518813</v>
       </c>
       <c r="R67" t="n">
-        <v>6995039</v>
+        <v>6994667</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,10 +8078,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121346613</v>
+        <v>121343305</v>
       </c>
       <c r="B68" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518770</v>
+        <v>518812</v>
       </c>
       <c r="R68" t="n">
-        <v>6994702</v>
+        <v>6994779</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346232</v>
+        <v>121346025</v>
       </c>
       <c r="B3" t="n">
         <v>78604</v>
@@ -826,14 +826,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518626</v>
+        <v>518519</v>
       </c>
       <c r="R3" t="n">
-        <v>6994964</v>
+        <v>6995085</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345918</v>
+        <v>121346586</v>
       </c>
       <c r="B4" t="n">
         <v>78604</v>
@@ -938,17 +938,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518360</v>
+        <v>518787</v>
       </c>
       <c r="R4" t="n">
-        <v>6995099</v>
+        <v>6994738</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343207</v>
+        <v>121345972</v>
       </c>
       <c r="B5" t="n">
-        <v>91271</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,41 +1026,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518808</v>
+        <v>518465</v>
       </c>
       <c r="R5" t="n">
-        <v>6994725</v>
+        <v>6995120</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1092,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1108,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343298</v>
+        <v>121346053</v>
       </c>
       <c r="B6" t="n">
         <v>78604</v>
@@ -1166,17 +1162,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518812</v>
+        <v>518560</v>
       </c>
       <c r="R6" t="n">
-        <v>6994775</v>
+        <v>6995039</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121345972</v>
+        <v>121343092</v>
       </c>
       <c r="B7" t="n">
         <v>78604</v>
@@ -1278,14 +1274,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518465</v>
+        <v>518811</v>
       </c>
       <c r="R7" t="n">
-        <v>6995120</v>
+        <v>6994686</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1317,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346025</v>
+        <v>121346038</v>
       </c>
       <c r="B8" t="n">
         <v>78604</v>
@@ -1394,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518519</v>
+        <v>518544</v>
       </c>
       <c r="R8" t="n">
-        <v>6995085</v>
+        <v>6995061</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345946</v>
+        <v>121343196</v>
       </c>
       <c r="B9" t="n">
         <v>78604</v>
@@ -1502,17 +1498,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518414</v>
+        <v>518797</v>
       </c>
       <c r="R9" t="n">
-        <v>6995151</v>
+        <v>6994707</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346586</v>
+        <v>121344213</v>
       </c>
       <c r="B10" t="n">
         <v>78604</v>
@@ -1614,14 +1610,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518787</v>
+        <v>518792</v>
       </c>
       <c r="R10" t="n">
-        <v>6994738</v>
+        <v>6994973</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121344193</v>
+        <v>121346620</v>
       </c>
       <c r="B11" t="n">
         <v>78604</v>
@@ -1726,17 +1722,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518808</v>
+        <v>518774</v>
       </c>
       <c r="R11" t="n">
-        <v>6994956</v>
+        <v>6994685</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,7 +1798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346038</v>
+        <v>121345918</v>
       </c>
       <c r="B12" t="n">
         <v>78604</v>
@@ -1842,13 +1838,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518544</v>
+        <v>518360</v>
       </c>
       <c r="R12" t="n">
-        <v>6995061</v>
+        <v>6995099</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346126</v>
+        <v>121344731</v>
       </c>
       <c r="B13" t="n">
         <v>78604</v>
@@ -1954,13 +1950,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518627</v>
+        <v>518652</v>
       </c>
       <c r="R13" t="n">
-        <v>6994984</v>
+        <v>6994988</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1995,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,7 +2022,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121343253</v>
+        <v>121343289</v>
       </c>
       <c r="B14" t="n">
         <v>78604</v>
@@ -2066,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518799</v>
+        <v>518814</v>
       </c>
       <c r="R14" t="n">
-        <v>6994749</v>
+        <v>6994762</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2101,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2111,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,7 +2134,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121344796</v>
+        <v>121343732</v>
       </c>
       <c r="B15" t="n">
         <v>78604</v>
@@ -2178,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518665</v>
+        <v>518817</v>
       </c>
       <c r="R15" t="n">
-        <v>6995040</v>
+        <v>6994855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,7 +2246,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121343303</v>
+        <v>121346635</v>
       </c>
       <c r="B16" t="n">
         <v>78604</v>
@@ -2290,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518809</v>
+        <v>518776</v>
       </c>
       <c r="R16" t="n">
-        <v>6994765</v>
+        <v>6994684</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2321,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2335,7 +2331,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2358,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346620</v>
+        <v>121346613</v>
       </c>
       <c r="B17" t="n">
         <v>78604</v>
@@ -2402,13 +2398,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518774</v>
+        <v>518770</v>
       </c>
       <c r="R17" t="n">
-        <v>6994685</v>
+        <v>6994702</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2474,7 +2470,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346533</v>
+        <v>121344818</v>
       </c>
       <c r="B18" t="n">
         <v>78604</v>
@@ -2510,14 +2506,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518703</v>
+        <v>518624</v>
       </c>
       <c r="R18" t="n">
-        <v>6994800</v>
+        <v>6995059</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2545,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2555,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,7 +2582,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121343524</v>
+        <v>121346533</v>
       </c>
       <c r="B19" t="n">
         <v>78604</v>
@@ -2626,13 +2622,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518815</v>
+        <v>518703</v>
       </c>
       <c r="R19" t="n">
-        <v>6994807</v>
+        <v>6994800</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2661,7 +2657,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2667,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,7 +2694,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121343468</v>
+        <v>121343478</v>
       </c>
       <c r="B20" t="n">
         <v>78604</v>
@@ -2738,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518814</v>
+        <v>518834</v>
       </c>
       <c r="R20" t="n">
-        <v>6994789</v>
+        <v>6994815</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,7 +2769,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2779,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,7 +2806,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343249</v>
+        <v>121343472</v>
       </c>
       <c r="B21" t="n">
         <v>78604</v>
@@ -2850,13 +2846,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518808</v>
+        <v>518814</v>
       </c>
       <c r="R21" t="n">
-        <v>6994740</v>
+        <v>6994800</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,7 +2881,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,7 +2891,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,7 +2918,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343196</v>
+        <v>121343093</v>
       </c>
       <c r="B22" t="n">
         <v>78604</v>
@@ -2962,13 +2958,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518797</v>
+        <v>518801</v>
       </c>
       <c r="R22" t="n">
-        <v>6994707</v>
+        <v>6994670</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,7 +2993,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,7 +3003,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,7 +3030,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121344308</v>
+        <v>121346005</v>
       </c>
       <c r="B23" t="n">
         <v>78604</v>
@@ -3070,14 +3066,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518783</v>
+        <v>518483</v>
       </c>
       <c r="R23" t="n">
-        <v>6994979</v>
+        <v>6995124</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,7 +3105,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3115,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3146,10 +3142,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121345960</v>
+        <v>121346595</v>
       </c>
       <c r="B24" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,37 +3158,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518444</v>
+        <v>518786</v>
       </c>
       <c r="R24" t="n">
-        <v>6995141</v>
+        <v>6994717</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3221,7 +3217,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3231,7 +3227,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121345954</v>
+        <v>121343229</v>
       </c>
       <c r="B25" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3274,37 +3270,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518428</v>
+        <v>518808</v>
       </c>
       <c r="R25" t="n">
-        <v>6995142</v>
+        <v>6994725</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3329,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3339,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,10 +3366,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346053</v>
+        <v>121345954</v>
       </c>
       <c r="B26" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,21 +3382,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3410,13 +3406,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518560</v>
+        <v>518428</v>
       </c>
       <c r="R26" t="n">
-        <v>6995039</v>
+        <v>6995142</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,7 +3441,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3451,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,7 +3478,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346595</v>
+        <v>121344308</v>
       </c>
       <c r="B27" t="n">
         <v>78604</v>
@@ -3518,14 +3514,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518786</v>
+        <v>518783</v>
       </c>
       <c r="R27" t="n">
-        <v>6994717</v>
+        <v>6994979</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3557,7 +3553,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3567,7 +3563,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,7 +3590,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121345073</v>
+        <v>121343249</v>
       </c>
       <c r="B28" t="n">
         <v>78604</v>
@@ -3630,14 +3626,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518555</v>
+        <v>518808</v>
       </c>
       <c r="R28" t="n">
-        <v>6995010</v>
+        <v>6994740</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3665,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3675,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,7 +3702,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343797</v>
+        <v>121343022</v>
       </c>
       <c r="B29" t="n">
         <v>78604</v>
@@ -3742,14 +3738,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518812</v>
+        <v>518814</v>
       </c>
       <c r="R29" t="n">
-        <v>6994875</v>
+        <v>6994676</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3781,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3791,7 +3787,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,7 +3814,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344213</v>
+        <v>121344193</v>
       </c>
       <c r="B30" t="n">
         <v>78604</v>
@@ -3858,13 +3854,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518792</v>
+        <v>518808</v>
       </c>
       <c r="R30" t="n">
-        <v>6994973</v>
+        <v>6994956</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,7 +3889,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3899,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346005</v>
+        <v>121343207</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>91272</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3942,41 +3938,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518483</v>
+        <v>518808</v>
       </c>
       <c r="R31" t="n">
-        <v>6995124</v>
+        <v>6994725</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4005,7 +4004,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4014,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4024,6 +4023,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346635</v>
+        <v>121346289</v>
       </c>
       <c r="B32" t="n">
         <v>78604</v>
@@ -4078,17 +4078,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518776</v>
+        <v>518618</v>
       </c>
       <c r="R32" t="n">
-        <v>6994684</v>
+        <v>6994929</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121344999</v>
+        <v>121344384</v>
       </c>
       <c r="B33" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518659</v>
+        <v>518741</v>
       </c>
       <c r="R33" t="n">
-        <v>6995028</v>
+        <v>6994995</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,7 +4266,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121344456</v>
+        <v>121345064</v>
       </c>
       <c r="B34" t="n">
         <v>78604</v>
@@ -4302,17 +4302,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518727</v>
+        <v>518566</v>
       </c>
       <c r="R34" t="n">
-        <v>6994987</v>
+        <v>6995030</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,7 +4378,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121343178</v>
+        <v>121345073</v>
       </c>
       <c r="B35" t="n">
         <v>78604</v>
@@ -4414,14 +4414,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518814</v>
+        <v>518555</v>
       </c>
       <c r="R35" t="n">
-        <v>6994717</v>
+        <v>6995010</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121343160</v>
+        <v>121343298</v>
       </c>
       <c r="B36" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4530,13 +4530,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518815</v>
+        <v>518812</v>
       </c>
       <c r="R36" t="n">
-        <v>6994704</v>
+        <v>6994775</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,7 +4602,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346074</v>
+        <v>121346232</v>
       </c>
       <c r="B37" t="n">
         <v>78604</v>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518583</v>
+        <v>518626</v>
       </c>
       <c r="R37" t="n">
-        <v>6995023</v>
+        <v>6994964</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121346613</v>
+        <v>121345116</v>
       </c>
       <c r="B38" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4730,34 +4730,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518770</v>
+        <v>518559</v>
       </c>
       <c r="R38" t="n">
-        <v>6994702</v>
+        <v>6994969</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4789,7 +4792,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4799,7 +4802,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4808,6 +4811,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4826,7 +4830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121343229</v>
+        <v>121343625</v>
       </c>
       <c r="B39" t="n">
         <v>78604</v>
@@ -4866,10 +4870,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518808</v>
+        <v>518819</v>
       </c>
       <c r="R39" t="n">
-        <v>6994725</v>
+        <v>6994817</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4901,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4911,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4938,7 +4942,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121343022</v>
+        <v>121343959</v>
       </c>
       <c r="B40" t="n">
         <v>78604</v>
@@ -4974,14 +4978,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518814</v>
+        <v>518825</v>
       </c>
       <c r="R40" t="n">
-        <v>6994676</v>
+        <v>6994907</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5013,7 +5017,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5027,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5050,7 +5054,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121346092</v>
+        <v>121344380</v>
       </c>
       <c r="B41" t="n">
         <v>78604</v>
@@ -5090,13 +5094,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518610</v>
+        <v>518768</v>
       </c>
       <c r="R41" t="n">
-        <v>6995000</v>
+        <v>6994994</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,7 +5129,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5139,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5162,7 +5166,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121343137</v>
+        <v>121345946</v>
       </c>
       <c r="B42" t="n">
         <v>78604</v>
@@ -5198,17 +5202,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518823</v>
+        <v>518414</v>
       </c>
       <c r="R42" t="n">
-        <v>6994691</v>
+        <v>6995151</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5237,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5247,7 +5251,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5274,7 +5278,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121343285</v>
+        <v>121346126</v>
       </c>
       <c r="B43" t="n">
         <v>78604</v>
@@ -5310,14 +5314,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518804</v>
+        <v>518627</v>
       </c>
       <c r="R43" t="n">
-        <v>6994760</v>
+        <v>6994984</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5349,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5359,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5386,10 +5390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121343959</v>
+        <v>121345960</v>
       </c>
       <c r="B44" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5402,34 +5406,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518825</v>
+        <v>518444</v>
       </c>
       <c r="R44" t="n">
-        <v>6994907</v>
+        <v>6995141</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5461,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5498,7 +5502,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121344380</v>
+        <v>121343524</v>
       </c>
       <c r="B45" t="n">
         <v>78604</v>
@@ -5534,17 +5538,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518768</v>
+        <v>518815</v>
       </c>
       <c r="R45" t="n">
-        <v>6994994</v>
+        <v>6994807</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5573,7 +5577,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5583,7 +5587,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5610,7 +5614,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121345064</v>
+        <v>121345122</v>
       </c>
       <c r="B46" t="n">
         <v>78604</v>
@@ -5646,14 +5650,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518566</v>
+        <v>518552</v>
       </c>
       <c r="R46" t="n">
-        <v>6995030</v>
+        <v>6994973</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5685,7 +5689,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5695,7 +5699,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,7 +5726,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121344731</v>
+        <v>121343920</v>
       </c>
       <c r="B47" t="n">
         <v>78604</v>
@@ -5762,13 +5766,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518652</v>
+        <v>518807</v>
       </c>
       <c r="R47" t="n">
-        <v>6994988</v>
+        <v>6994899</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5797,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5807,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5834,7 +5838,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121343809</v>
+        <v>121343468</v>
       </c>
       <c r="B48" t="n">
         <v>78604</v>
@@ -5870,14 +5874,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518808</v>
+        <v>518814</v>
       </c>
       <c r="R48" t="n">
-        <v>6994892</v>
+        <v>6994789</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5909,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5946,10 +5950,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121344384</v>
+        <v>121343797</v>
       </c>
       <c r="B49" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5962,21 +5966,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5986,10 +5990,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518741</v>
+        <v>518812</v>
       </c>
       <c r="R49" t="n">
-        <v>6994995</v>
+        <v>6994875</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6021,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6031,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6058,7 +6062,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121345938</v>
+        <v>121345085</v>
       </c>
       <c r="B50" t="n">
         <v>78604</v>
@@ -6094,17 +6098,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518387</v>
+        <v>518559</v>
       </c>
       <c r="R50" t="n">
-        <v>6995152</v>
+        <v>6995004</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6147,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6170,10 +6174,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121345116</v>
+        <v>121343305</v>
       </c>
       <c r="B51" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6186,37 +6190,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518559</v>
+        <v>518812</v>
       </c>
       <c r="R51" t="n">
-        <v>6994969</v>
+        <v>6994779</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6248,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6258,7 +6259,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6267,7 +6268,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6286,7 +6286,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121346430</v>
+        <v>121343018</v>
       </c>
       <c r="B52" t="n">
         <v>78604</v>
@@ -6322,17 +6322,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518614</v>
+        <v>518813</v>
       </c>
       <c r="R52" t="n">
-        <v>6994902</v>
+        <v>6994667</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6398,10 +6398,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121345053</v>
+        <v>121344456</v>
       </c>
       <c r="B53" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6414,34 +6414,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518563</v>
+        <v>518727</v>
       </c>
       <c r="R53" t="n">
-        <v>6995042</v>
+        <v>6994987</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121343472</v>
+        <v>121345053</v>
       </c>
       <c r="B54" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6526,34 +6526,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518814</v>
+        <v>518563</v>
       </c>
       <c r="R54" t="n">
-        <v>6994800</v>
+        <v>6995042</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,10 +6622,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121343478</v>
+        <v>121343160</v>
       </c>
       <c r="B55" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6662,13 +6662,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518834</v>
+        <v>518815</v>
       </c>
       <c r="R55" t="n">
-        <v>6994815</v>
+        <v>6994704</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,7 +6734,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121343625</v>
+        <v>121343303</v>
       </c>
       <c r="B56" t="n">
         <v>78604</v>
@@ -6774,13 +6774,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518819</v>
+        <v>518809</v>
       </c>
       <c r="R56" t="n">
-        <v>6994817</v>
+        <v>6994765</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,7 +6846,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343920</v>
+        <v>121346092</v>
       </c>
       <c r="B57" t="n">
         <v>78604</v>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518807</v>
+        <v>518610</v>
       </c>
       <c r="R57" t="n">
-        <v>6994899</v>
+        <v>6995000</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121345085</v>
+        <v>121344796</v>
       </c>
       <c r="B58" t="n">
         <v>78604</v>
@@ -6998,13 +6998,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518559</v>
+        <v>518665</v>
       </c>
       <c r="R58" t="n">
-        <v>6995004</v>
+        <v>6995040</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,7 +7070,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121344818</v>
+        <v>121345938</v>
       </c>
       <c r="B59" t="n">
         <v>78604</v>
@@ -7106,14 +7106,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518624</v>
+        <v>518387</v>
       </c>
       <c r="R59" t="n">
-        <v>6995059</v>
+        <v>6995152</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,7 +7182,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121343289</v>
+        <v>121343809</v>
       </c>
       <c r="B60" t="n">
         <v>78604</v>
@@ -7218,17 +7218,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518814</v>
+        <v>518808</v>
       </c>
       <c r="R60" t="n">
-        <v>6994762</v>
+        <v>6994892</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,7 +7294,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121345122</v>
+        <v>121343137</v>
       </c>
       <c r="B61" t="n">
         <v>78604</v>
@@ -7330,17 +7330,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518552</v>
+        <v>518823</v>
       </c>
       <c r="R61" t="n">
-        <v>6994973</v>
+        <v>6994691</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,7 +7406,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121343732</v>
+        <v>121343253</v>
       </c>
       <c r="B62" t="n">
         <v>78604</v>
@@ -7442,17 +7442,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518817</v>
+        <v>518799</v>
       </c>
       <c r="R62" t="n">
-        <v>6994855</v>
+        <v>6994749</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,7 +7518,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121346560</v>
+        <v>121343285</v>
       </c>
       <c r="B63" t="n">
         <v>78604</v>
@@ -7558,13 +7558,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518787</v>
+        <v>518804</v>
       </c>
       <c r="R63" t="n">
-        <v>6994752</v>
+        <v>6994760</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343093</v>
+        <v>121346074</v>
       </c>
       <c r="B64" t="n">
         <v>78604</v>
@@ -7666,17 +7666,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518801</v>
+        <v>518583</v>
       </c>
       <c r="R64" t="n">
-        <v>6994670</v>
+        <v>6995023</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,7 +7742,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121346289</v>
+        <v>121346560</v>
       </c>
       <c r="B65" t="n">
         <v>78604</v>
@@ -7778,17 +7778,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518618</v>
+        <v>518787</v>
       </c>
       <c r="R65" t="n">
-        <v>6994929</v>
+        <v>6994752</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,7 +7854,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121343092</v>
+        <v>121344999</v>
       </c>
       <c r="B66" t="n">
         <v>78604</v>
@@ -7890,14 +7890,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518811</v>
+        <v>518659</v>
       </c>
       <c r="R66" t="n">
-        <v>6994686</v>
+        <v>6995028</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121343018</v>
+        <v>121346430</v>
       </c>
       <c r="B67" t="n">
         <v>78604</v>
@@ -8002,17 +8002,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518813</v>
+        <v>518614</v>
       </c>
       <c r="R67" t="n">
-        <v>6994667</v>
+        <v>6994902</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343305</v>
+        <v>121343178</v>
       </c>
       <c r="B68" t="n">
         <v>78604</v>
@@ -8118,13 +8118,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518812</v>
+        <v>518814</v>
       </c>
       <c r="R68" t="n">
-        <v>6994779</v>
+        <v>6994717</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346025</v>
+        <v>121343018</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,17 +826,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518519</v>
+        <v>518813</v>
       </c>
       <c r="R3" t="n">
-        <v>6995085</v>
+        <v>6994667</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346586</v>
+        <v>121345073</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,14 +938,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518787</v>
+        <v>518555</v>
       </c>
       <c r="R4" t="n">
-        <v>6994738</v>
+        <v>6995010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345972</v>
+        <v>121345918</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518465</v>
+        <v>518360</v>
       </c>
       <c r="R5" t="n">
-        <v>6995120</v>
+        <v>6995099</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346053</v>
+        <v>121346430</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,17 +1162,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518560</v>
+        <v>518614</v>
       </c>
       <c r="R6" t="n">
-        <v>6995039</v>
+        <v>6994902</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343092</v>
+        <v>121343303</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518811</v>
+        <v>518809</v>
       </c>
       <c r="R7" t="n">
-        <v>6994686</v>
+        <v>6994765</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346038</v>
+        <v>121346533</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,14 +1386,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518544</v>
+        <v>518703</v>
       </c>
       <c r="R8" t="n">
-        <v>6995061</v>
+        <v>6994800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343196</v>
+        <v>121344213</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,17 +1498,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518797</v>
+        <v>518792</v>
       </c>
       <c r="R9" t="n">
-        <v>6994707</v>
+        <v>6994973</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121344213</v>
+        <v>121346092</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518792</v>
+        <v>518610</v>
       </c>
       <c r="R10" t="n">
-        <v>6994973</v>
+        <v>6995000</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346620</v>
+        <v>121346560</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518774</v>
+        <v>518787</v>
       </c>
       <c r="R11" t="n">
-        <v>6994685</v>
+        <v>6994752</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345918</v>
+        <v>121345960</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,21 +1814,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518360</v>
+        <v>518444</v>
       </c>
       <c r="R12" t="n">
-        <v>6995099</v>
+        <v>6995141</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121344731</v>
+        <v>121344380</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,13 +1950,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518652</v>
+        <v>518768</v>
       </c>
       <c r="R13" t="n">
-        <v>6994988</v>
+        <v>6994994</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121343289</v>
+        <v>121343809</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,17 +2058,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518814</v>
+        <v>518808</v>
       </c>
       <c r="R14" t="n">
-        <v>6994762</v>
+        <v>6994892</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121343732</v>
+        <v>121346620</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,14 +2170,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518817</v>
+        <v>518774</v>
       </c>
       <c r="R15" t="n">
-        <v>6994855</v>
+        <v>6994685</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346635</v>
+        <v>121344731</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,14 +2282,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518776</v>
+        <v>518652</v>
       </c>
       <c r="R16" t="n">
-        <v>6994684</v>
+        <v>6994988</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346613</v>
+        <v>121346635</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518770</v>
+        <v>518776</v>
       </c>
       <c r="R17" t="n">
-        <v>6994702</v>
+        <v>6994684</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121344818</v>
+        <v>121346038</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,14 +2506,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518624</v>
+        <v>518544</v>
       </c>
       <c r="R18" t="n">
-        <v>6995059</v>
+        <v>6995061</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,10 +2582,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346533</v>
+        <v>121345116</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2598,37 +2598,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518703</v>
+        <v>518559</v>
       </c>
       <c r="R19" t="n">
-        <v>6994800</v>
+        <v>6994969</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,7 +2660,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2667,7 +2670,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,6 +2679,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2694,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121343478</v>
+        <v>121346005</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,14 +2734,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518834</v>
+        <v>518483</v>
       </c>
       <c r="R20" t="n">
-        <v>6994815</v>
+        <v>6995124</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2769,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2779,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343472</v>
+        <v>121345122</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,17 +2846,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518814</v>
+        <v>518552</v>
       </c>
       <c r="R21" t="n">
-        <v>6994800</v>
+        <v>6994973</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2881,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2891,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343093</v>
+        <v>121343732</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2954,17 +2958,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518801</v>
+        <v>518817</v>
       </c>
       <c r="R22" t="n">
-        <v>6994670</v>
+        <v>6994855</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2993,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3003,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346005</v>
+        <v>121345954</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,21 +3050,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3070,10 +3074,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518483</v>
+        <v>518428</v>
       </c>
       <c r="R23" t="n">
-        <v>6995124</v>
+        <v>6995142</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3105,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3115,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346595</v>
+        <v>121343524</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3182,13 +3186,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518786</v>
+        <v>518815</v>
       </c>
       <c r="R24" t="n">
-        <v>6994717</v>
+        <v>6994807</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3217,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3227,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,10 +3258,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121343229</v>
+        <v>121346586</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3294,13 +3298,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518808</v>
+        <v>518787</v>
       </c>
       <c r="R25" t="n">
-        <v>6994725</v>
+        <v>6994738</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121345954</v>
+        <v>121345085</v>
       </c>
       <c r="B26" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3382,37 +3386,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518428</v>
+        <v>518559</v>
       </c>
       <c r="R26" t="n">
-        <v>6995142</v>
+        <v>6995004</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3441,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3451,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121344308</v>
+        <v>121343137</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3514,17 +3518,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518783</v>
+        <v>518823</v>
       </c>
       <c r="R27" t="n">
-        <v>6994979</v>
+        <v>6994691</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3553,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3563,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3590,10 +3594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121343249</v>
+        <v>121343092</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3630,13 +3634,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518808</v>
+        <v>518811</v>
       </c>
       <c r="R28" t="n">
-        <v>6994740</v>
+        <v>6994686</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3665,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3675,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3702,10 +3706,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343022</v>
+        <v>121344796</v>
       </c>
       <c r="B29" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3738,17 +3742,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518814</v>
+        <v>518665</v>
       </c>
       <c r="R29" t="n">
-        <v>6994676</v>
+        <v>6995040</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3777,7 +3781,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3787,7 +3791,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344193</v>
+        <v>121343472</v>
       </c>
       <c r="B30" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3850,14 +3854,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518808</v>
+        <v>518814</v>
       </c>
       <c r="R30" t="n">
-        <v>6994956</v>
+        <v>6994800</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3889,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3899,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3926,10 +3930,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121343207</v>
+        <v>121346232</v>
       </c>
       <c r="B31" t="n">
-        <v>91272</v>
+        <v>78607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3938,44 +3942,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518808</v>
+        <v>518626</v>
       </c>
       <c r="R31" t="n">
-        <v>6994725</v>
+        <v>6994964</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4004,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4014,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4023,7 +4024,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346289</v>
+        <v>121343178</v>
       </c>
       <c r="B32" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,17 +4078,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518618</v>
+        <v>518814</v>
       </c>
       <c r="R32" t="n">
-        <v>6994929</v>
+        <v>6994717</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121344384</v>
+        <v>121343289</v>
       </c>
       <c r="B33" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4170,34 +4170,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518741</v>
+        <v>518814</v>
       </c>
       <c r="R33" t="n">
-        <v>6994995</v>
+        <v>6994762</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,10 +4266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121345064</v>
+        <v>121343468</v>
       </c>
       <c r="B34" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4302,14 +4302,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518566</v>
+        <v>518814</v>
       </c>
       <c r="R34" t="n">
-        <v>6995030</v>
+        <v>6994789</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121345073</v>
+        <v>121344193</v>
       </c>
       <c r="B35" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,17 +4414,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518555</v>
+        <v>518808</v>
       </c>
       <c r="R35" t="n">
-        <v>6995010</v>
+        <v>6994956</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121343298</v>
+        <v>121344818</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4526,14 +4526,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518812</v>
+        <v>518624</v>
       </c>
       <c r="R36" t="n">
-        <v>6994775</v>
+        <v>6995059</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,10 +4602,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346232</v>
+        <v>121345938</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,14 +4638,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518626</v>
+        <v>518387</v>
       </c>
       <c r="R37" t="n">
-        <v>6994964</v>
+        <v>6995152</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121345116</v>
+        <v>121346613</v>
       </c>
       <c r="B38" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4730,37 +4730,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518559</v>
+        <v>518770</v>
       </c>
       <c r="R38" t="n">
-        <v>6994969</v>
+        <v>6994702</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4792,7 +4789,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4802,7 +4799,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4811,7 +4808,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4830,10 +4826,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121343625</v>
+        <v>121345053</v>
       </c>
       <c r="B39" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4846,34 +4842,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518819</v>
+        <v>518563</v>
       </c>
       <c r="R39" t="n">
-        <v>6994817</v>
+        <v>6995042</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4905,7 +4901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4911,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,10 +4938,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121343959</v>
+        <v>121343253</v>
       </c>
       <c r="B40" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4978,14 +4974,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518825</v>
+        <v>518799</v>
       </c>
       <c r="R40" t="n">
-        <v>6994907</v>
+        <v>6994749</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5017,7 +5013,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5027,7 +5023,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,10 +5050,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121344380</v>
+        <v>121343285</v>
       </c>
       <c r="B41" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5090,17 +5086,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518768</v>
+        <v>518804</v>
       </c>
       <c r="R41" t="n">
-        <v>6994994</v>
+        <v>6994760</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5129,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5139,7 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121345946</v>
+        <v>121344308</v>
       </c>
       <c r="B42" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5202,14 +5198,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518414</v>
+        <v>518783</v>
       </c>
       <c r="R42" t="n">
-        <v>6995151</v>
+        <v>6994979</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5241,7 +5237,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5251,7 +5247,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5281,7 +5277,7 @@
         <v>121346126</v>
       </c>
       <c r="B43" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5390,10 +5386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121345960</v>
+        <v>121343797</v>
       </c>
       <c r="B44" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5406,34 +5402,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518444</v>
+        <v>518812</v>
       </c>
       <c r="R44" t="n">
-        <v>6995141</v>
+        <v>6994875</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5465,7 +5461,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5475,7 +5471,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,10 +5498,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121343524</v>
+        <v>121343160</v>
       </c>
       <c r="B45" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5518,21 +5514,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5545,7 +5541,7 @@
         <v>518815</v>
       </c>
       <c r="R45" t="n">
-        <v>6994807</v>
+        <v>6994704</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5577,7 +5573,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5587,7 +5583,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5614,10 +5610,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121345122</v>
+        <v>121346053</v>
       </c>
       <c r="B46" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,17 +5646,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518552</v>
+        <v>518560</v>
       </c>
       <c r="R46" t="n">
-        <v>6994973</v>
+        <v>6995039</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5689,7 +5685,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5699,7 +5695,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,10 +5722,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121343920</v>
+        <v>121343478</v>
       </c>
       <c r="B47" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5762,17 +5758,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518807</v>
+        <v>518834</v>
       </c>
       <c r="R47" t="n">
-        <v>6994899</v>
+        <v>6994815</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5801,7 +5797,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5807,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,10 +5834,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121343468</v>
+        <v>121346074</v>
       </c>
       <c r="B48" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5874,14 +5870,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518814</v>
+        <v>518583</v>
       </c>
       <c r="R48" t="n">
-        <v>6994789</v>
+        <v>6995023</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5913,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,10 +5946,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121343797</v>
+        <v>121344456</v>
       </c>
       <c r="B49" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5990,10 +5986,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518812</v>
+        <v>518727</v>
       </c>
       <c r="R49" t="n">
-        <v>6994875</v>
+        <v>6994987</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6025,7 +6021,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6031,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6062,10 +6058,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121345085</v>
+        <v>121345064</v>
       </c>
       <c r="B50" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6098,17 +6094,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518559</v>
+        <v>518566</v>
       </c>
       <c r="R50" t="n">
-        <v>6995004</v>
+        <v>6995030</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6174,10 +6170,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121343305</v>
+        <v>121346025</v>
       </c>
       <c r="B51" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6210,17 +6206,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518812</v>
+        <v>518519</v>
       </c>
       <c r="R51" t="n">
-        <v>6994779</v>
+        <v>6995085</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6249,7 +6245,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,7 +6255,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6286,10 +6282,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121343018</v>
+        <v>121343207</v>
       </c>
       <c r="B52" t="n">
-        <v>78604</v>
+        <v>91275</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6298,38 +6294,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518813</v>
+        <v>518808</v>
       </c>
       <c r="R52" t="n">
-        <v>6994667</v>
+        <v>6994725</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6361,7 +6360,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,7 +6370,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6380,6 +6379,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121344456</v>
+        <v>121343249</v>
       </c>
       <c r="B53" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6434,17 +6434,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518727</v>
+        <v>518808</v>
       </c>
       <c r="R53" t="n">
-        <v>6994987</v>
+        <v>6994740</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121345053</v>
+        <v>121343305</v>
       </c>
       <c r="B54" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6526,34 +6526,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518563</v>
+        <v>518812</v>
       </c>
       <c r="R54" t="n">
-        <v>6995042</v>
+        <v>6994779</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,10 +6622,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121343160</v>
+        <v>121343959</v>
       </c>
       <c r="B55" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6638,34 +6638,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518815</v>
+        <v>518825</v>
       </c>
       <c r="R55" t="n">
-        <v>6994704</v>
+        <v>6994907</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,10 +6734,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121343303</v>
+        <v>121345946</v>
       </c>
       <c r="B56" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6770,14 +6770,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518809</v>
+        <v>518414</v>
       </c>
       <c r="R56" t="n">
-        <v>6994765</v>
+        <v>6995151</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121346092</v>
+        <v>121343920</v>
       </c>
       <c r="B57" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518610</v>
+        <v>518807</v>
       </c>
       <c r="R57" t="n">
-        <v>6995000</v>
+        <v>6994899</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,10 +6958,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121344796</v>
+        <v>121346595</v>
       </c>
       <c r="B58" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6994,14 +6994,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518665</v>
+        <v>518786</v>
       </c>
       <c r="R58" t="n">
-        <v>6995040</v>
+        <v>6994717</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,10 +7070,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121345938</v>
+        <v>121344999</v>
       </c>
       <c r="B59" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7106,17 +7106,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518387</v>
+        <v>518659</v>
       </c>
       <c r="R59" t="n">
-        <v>6995152</v>
+        <v>6995028</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121343809</v>
+        <v>121344384</v>
       </c>
       <c r="B60" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7198,21 +7198,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518808</v>
+        <v>518741</v>
       </c>
       <c r="R60" t="n">
-        <v>6994892</v>
+        <v>6994995</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,10 +7294,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121343137</v>
+        <v>121343298</v>
       </c>
       <c r="B61" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7334,13 +7334,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518823</v>
+        <v>518812</v>
       </c>
       <c r="R61" t="n">
-        <v>6994691</v>
+        <v>6994775</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121343253</v>
+        <v>121345972</v>
       </c>
       <c r="B62" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7442,14 +7442,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518799</v>
+        <v>518465</v>
       </c>
       <c r="R62" t="n">
-        <v>6994749</v>
+        <v>6995120</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121343285</v>
+        <v>121343196</v>
       </c>
       <c r="B63" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518804</v>
+        <v>518797</v>
       </c>
       <c r="R63" t="n">
-        <v>6994760</v>
+        <v>6994707</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,10 +7630,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121346074</v>
+        <v>121343229</v>
       </c>
       <c r="B64" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7666,17 +7666,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518583</v>
+        <v>518808</v>
       </c>
       <c r="R64" t="n">
-        <v>6995023</v>
+        <v>6994725</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121346560</v>
+        <v>121343625</v>
       </c>
       <c r="B65" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7782,13 +7782,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518787</v>
+        <v>518819</v>
       </c>
       <c r="R65" t="n">
-        <v>6994752</v>
+        <v>6994817</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,10 +7854,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121344999</v>
+        <v>121346289</v>
       </c>
       <c r="B66" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518659</v>
+        <v>518618</v>
       </c>
       <c r="R66" t="n">
-        <v>6995028</v>
+        <v>6994929</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121346430</v>
+        <v>121343093</v>
       </c>
       <c r="B67" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,17 +8002,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518614</v>
+        <v>518801</v>
       </c>
       <c r="R67" t="n">
-        <v>6994902</v>
+        <v>6994670</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,10 +8078,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343178</v>
+        <v>121343022</v>
       </c>
       <c r="B68" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8121,10 +8121,10 @@
         <v>518814</v>
       </c>
       <c r="R68" t="n">
-        <v>6994717</v>
+        <v>6994676</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121343018</v>
+        <v>121345918</v>
       </c>
       <c r="B3" t="n">
         <v>78607</v>
@@ -826,14 +826,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518813</v>
+        <v>518360</v>
       </c>
       <c r="R3" t="n">
-        <v>6994667</v>
+        <v>6995099</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345073</v>
+        <v>121345064</v>
       </c>
       <c r="B4" t="n">
         <v>78607</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518555</v>
+        <v>518566</v>
       </c>
       <c r="R4" t="n">
-        <v>6995010</v>
+        <v>6995030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121345918</v>
+        <v>121343809</v>
       </c>
       <c r="B5" t="n">
         <v>78607</v>
@@ -1050,17 +1050,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518360</v>
+        <v>518808</v>
       </c>
       <c r="R5" t="n">
-        <v>6995099</v>
+        <v>6994892</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346430</v>
+        <v>121343018</v>
       </c>
       <c r="B6" t="n">
         <v>78607</v>
@@ -1162,17 +1162,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518614</v>
+        <v>518813</v>
       </c>
       <c r="R6" t="n">
-        <v>6994902</v>
+        <v>6994667</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343303</v>
+        <v>121343253</v>
       </c>
       <c r="B7" t="n">
         <v>78607</v>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518809</v>
+        <v>518799</v>
       </c>
       <c r="R7" t="n">
-        <v>6994765</v>
+        <v>6994749</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346533</v>
+        <v>121344193</v>
       </c>
       <c r="B8" t="n">
         <v>78607</v>
@@ -1386,17 +1386,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518703</v>
+        <v>518808</v>
       </c>
       <c r="R8" t="n">
-        <v>6994800</v>
+        <v>6994956</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121344213</v>
+        <v>121346074</v>
       </c>
       <c r="B9" t="n">
         <v>78607</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518792</v>
+        <v>518583</v>
       </c>
       <c r="R9" t="n">
-        <v>6994973</v>
+        <v>6995023</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346092</v>
+        <v>121345116</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,34 +1590,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518610</v>
+        <v>518559</v>
       </c>
       <c r="R10" t="n">
-        <v>6995000</v>
+        <v>6994969</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1649,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,6 +1671,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1686,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346560</v>
+        <v>121345972</v>
       </c>
       <c r="B11" t="n">
         <v>78607</v>
@@ -1722,17 +1726,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518787</v>
+        <v>518465</v>
       </c>
       <c r="R11" t="n">
-        <v>6994752</v>
+        <v>6995120</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345960</v>
+        <v>121343093</v>
       </c>
       <c r="B12" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,37 +1818,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518444</v>
+        <v>518801</v>
       </c>
       <c r="R12" t="n">
-        <v>6995141</v>
+        <v>6994670</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121344380</v>
+        <v>121346005</v>
       </c>
       <c r="B13" t="n">
         <v>78607</v>
@@ -1946,17 +1950,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518768</v>
+        <v>518483</v>
       </c>
       <c r="R13" t="n">
-        <v>6994994</v>
+        <v>6995124</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,7 +2026,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121343809</v>
+        <v>121346289</v>
       </c>
       <c r="B14" t="n">
         <v>78607</v>
@@ -2062,13 +2066,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518808</v>
+        <v>518618</v>
       </c>
       <c r="R14" t="n">
-        <v>6994892</v>
+        <v>6994929</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346620</v>
+        <v>121345954</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,34 +2154,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518774</v>
+        <v>518428</v>
       </c>
       <c r="R15" t="n">
-        <v>6994685</v>
+        <v>6995142</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,7 +2213,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2223,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121344731</v>
+        <v>121343298</v>
       </c>
       <c r="B16" t="n">
         <v>78607</v>
@@ -2282,14 +2286,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518652</v>
+        <v>518812</v>
       </c>
       <c r="R16" t="n">
-        <v>6994988</v>
+        <v>6994775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2321,7 +2325,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2335,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346635</v>
+        <v>121344731</v>
       </c>
       <c r="B17" t="n">
         <v>78607</v>
@@ -2394,14 +2398,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518776</v>
+        <v>518652</v>
       </c>
       <c r="R17" t="n">
-        <v>6994684</v>
+        <v>6994988</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,7 +2447,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,7 +2474,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346038</v>
+        <v>121343196</v>
       </c>
       <c r="B18" t="n">
         <v>78607</v>
@@ -2506,17 +2510,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518544</v>
+        <v>518797</v>
       </c>
       <c r="R18" t="n">
-        <v>6995061</v>
+        <v>6994707</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2545,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2555,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121345116</v>
+        <v>121344380</v>
       </c>
       <c r="B19" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2598,40 +2602,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518559</v>
+        <v>518768</v>
       </c>
       <c r="R19" t="n">
-        <v>6994969</v>
+        <v>6994994</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,7 +2680,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346005</v>
+        <v>121343178</v>
       </c>
       <c r="B20" t="n">
         <v>78607</v>
@@ -2734,14 +2734,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518483</v>
+        <v>518814</v>
       </c>
       <c r="R20" t="n">
-        <v>6995124</v>
+        <v>6994717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121345122</v>
+        <v>121343478</v>
       </c>
       <c r="B21" t="n">
         <v>78607</v>
@@ -2846,14 +2846,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518552</v>
+        <v>518834</v>
       </c>
       <c r="R21" t="n">
-        <v>6994973</v>
+        <v>6994815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343732</v>
+        <v>121343468</v>
       </c>
       <c r="B22" t="n">
         <v>78607</v>
@@ -2958,14 +2958,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518817</v>
+        <v>518814</v>
       </c>
       <c r="R22" t="n">
-        <v>6994855</v>
+        <v>6994789</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,7 +3034,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121345954</v>
+        <v>121345053</v>
       </c>
       <c r="B23" t="n">
         <v>79688</v>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518428</v>
+        <v>518563</v>
       </c>
       <c r="R23" t="n">
-        <v>6995142</v>
+        <v>6995042</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3146,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121343524</v>
+        <v>121343160</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,21 +3162,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,7 +3189,7 @@
         <v>518815</v>
       </c>
       <c r="R24" t="n">
-        <v>6994807</v>
+        <v>6994704</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,10 +3258,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346586</v>
+        <v>121344384</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3274,37 +3274,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518787</v>
+        <v>518741</v>
       </c>
       <c r="R25" t="n">
-        <v>6994738</v>
+        <v>6994995</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,7 +3370,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121345085</v>
+        <v>121343092</v>
       </c>
       <c r="B26" t="n">
         <v>78607</v>
@@ -3406,14 +3406,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518559</v>
+        <v>518811</v>
       </c>
       <c r="R26" t="n">
-        <v>6995004</v>
+        <v>6994686</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121343137</v>
+        <v>121343289</v>
       </c>
       <c r="B27" t="n">
         <v>78607</v>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518823</v>
+        <v>518814</v>
       </c>
       <c r="R27" t="n">
-        <v>6994691</v>
+        <v>6994762</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,7 +3594,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121343092</v>
+        <v>121346620</v>
       </c>
       <c r="B28" t="n">
         <v>78607</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518811</v>
+        <v>518774</v>
       </c>
       <c r="R28" t="n">
-        <v>6994686</v>
+        <v>6994685</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,7 +3706,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121344796</v>
+        <v>121345938</v>
       </c>
       <c r="B29" t="n">
         <v>78607</v>
@@ -3742,14 +3742,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518665</v>
+        <v>518387</v>
       </c>
       <c r="R29" t="n">
-        <v>6995040</v>
+        <v>6995152</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,7 +3818,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121343472</v>
+        <v>121343137</v>
       </c>
       <c r="B30" t="n">
         <v>78607</v>
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518814</v>
+        <v>518823</v>
       </c>
       <c r="R30" t="n">
-        <v>6994800</v>
+        <v>6994691</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346232</v>
+        <v>121343303</v>
       </c>
       <c r="B31" t="n">
         <v>78607</v>
@@ -3966,14 +3966,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518626</v>
+        <v>518809</v>
       </c>
       <c r="R31" t="n">
-        <v>6994964</v>
+        <v>6994765</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,7 +4042,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121343178</v>
+        <v>121346430</v>
       </c>
       <c r="B32" t="n">
         <v>78607</v>
@@ -4078,14 +4078,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518814</v>
+        <v>518614</v>
       </c>
       <c r="R32" t="n">
-        <v>6994717</v>
+        <v>6994902</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,7 +4154,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121343289</v>
+        <v>121346025</v>
       </c>
       <c r="B33" t="n">
         <v>78607</v>
@@ -4190,17 +4190,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518814</v>
+        <v>518519</v>
       </c>
       <c r="R33" t="n">
-        <v>6994762</v>
+        <v>6995085</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,7 +4266,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121343468</v>
+        <v>121343959</v>
       </c>
       <c r="B34" t="n">
         <v>78607</v>
@@ -4302,17 +4302,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518814</v>
+        <v>518825</v>
       </c>
       <c r="R34" t="n">
-        <v>6994789</v>
+        <v>6994907</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,7 +4378,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121344193</v>
+        <v>121343524</v>
       </c>
       <c r="B35" t="n">
         <v>78607</v>
@@ -4414,14 +4414,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518808</v>
+        <v>518815</v>
       </c>
       <c r="R35" t="n">
-        <v>6994956</v>
+        <v>6994807</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,7 +4490,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121344818</v>
+        <v>121346595</v>
       </c>
       <c r="B36" t="n">
         <v>78607</v>
@@ -4526,14 +4526,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518624</v>
+        <v>518786</v>
       </c>
       <c r="R36" t="n">
-        <v>6995059</v>
+        <v>6994717</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,7 +4602,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121345938</v>
+        <v>121346126</v>
       </c>
       <c r="B37" t="n">
         <v>78607</v>
@@ -4638,17 +4638,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518387</v>
+        <v>518627</v>
       </c>
       <c r="R37" t="n">
-        <v>6995152</v>
+        <v>6994984</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,7 +4714,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121346613</v>
+        <v>121343285</v>
       </c>
       <c r="B38" t="n">
         <v>78607</v>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518770</v>
+        <v>518804</v>
       </c>
       <c r="R38" t="n">
-        <v>6994702</v>
+        <v>6994760</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121345053</v>
+        <v>121343249</v>
       </c>
       <c r="B39" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4842,37 +4842,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518563</v>
+        <v>518808</v>
       </c>
       <c r="R39" t="n">
-        <v>6995042</v>
+        <v>6994740</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4938,7 +4938,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121343253</v>
+        <v>121343022</v>
       </c>
       <c r="B40" t="n">
         <v>78607</v>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518799</v>
+        <v>518814</v>
       </c>
       <c r="R40" t="n">
-        <v>6994749</v>
+        <v>6994676</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5050,10 +5050,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121343285</v>
+        <v>121345960</v>
       </c>
       <c r="B41" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5066,34 +5066,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518804</v>
+        <v>518444</v>
       </c>
       <c r="R41" t="n">
-        <v>6994760</v>
+        <v>6995141</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5162,7 +5162,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121344308</v>
+        <v>121346613</v>
       </c>
       <c r="B42" t="n">
         <v>78607</v>
@@ -5198,17 +5198,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518783</v>
+        <v>518770</v>
       </c>
       <c r="R42" t="n">
-        <v>6994979</v>
+        <v>6994702</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5274,7 +5274,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121346126</v>
+        <v>121346038</v>
       </c>
       <c r="B43" t="n">
         <v>78607</v>
@@ -5310,17 +5310,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518627</v>
+        <v>518544</v>
       </c>
       <c r="R43" t="n">
-        <v>6994984</v>
+        <v>6995061</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121343797</v>
+        <v>121344818</v>
       </c>
       <c r="B44" t="n">
         <v>78607</v>
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518812</v>
+        <v>518624</v>
       </c>
       <c r="R44" t="n">
-        <v>6994875</v>
+        <v>6995059</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5498,10 +5498,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121343160</v>
+        <v>121344456</v>
       </c>
       <c r="B45" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5514,34 +5514,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518815</v>
+        <v>518727</v>
       </c>
       <c r="R45" t="n">
-        <v>6994704</v>
+        <v>6994987</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5610,7 +5610,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121346053</v>
+        <v>121346232</v>
       </c>
       <c r="B46" t="n">
         <v>78607</v>
@@ -5646,17 +5646,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518560</v>
+        <v>518626</v>
       </c>
       <c r="R46" t="n">
-        <v>6995039</v>
+        <v>6994964</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,7 +5722,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121343478</v>
+        <v>121345946</v>
       </c>
       <c r="B47" t="n">
         <v>78607</v>
@@ -5758,14 +5758,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518834</v>
+        <v>518414</v>
       </c>
       <c r="R47" t="n">
-        <v>6994815</v>
+        <v>6995151</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5834,7 +5834,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121346074</v>
+        <v>121345122</v>
       </c>
       <c r="B48" t="n">
         <v>78607</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518583</v>
+        <v>518552</v>
       </c>
       <c r="R48" t="n">
-        <v>6995023</v>
+        <v>6994973</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5946,7 +5946,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121344456</v>
+        <v>121343625</v>
       </c>
       <c r="B49" t="n">
         <v>78607</v>
@@ -5982,14 +5982,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518727</v>
+        <v>518819</v>
       </c>
       <c r="R49" t="n">
-        <v>6994987</v>
+        <v>6994817</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6058,7 +6058,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121345064</v>
+        <v>121346560</v>
       </c>
       <c r="B50" t="n">
         <v>78607</v>
@@ -6094,14 +6094,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518566</v>
+        <v>518787</v>
       </c>
       <c r="R50" t="n">
-        <v>6995030</v>
+        <v>6994752</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6170,7 +6170,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121346025</v>
+        <v>121343920</v>
       </c>
       <c r="B51" t="n">
         <v>78607</v>
@@ -6206,17 +6206,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518519</v>
+        <v>518807</v>
       </c>
       <c r="R51" t="n">
-        <v>6995085</v>
+        <v>6994899</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6282,10 +6282,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121343207</v>
+        <v>121346635</v>
       </c>
       <c r="B52" t="n">
-        <v>91275</v>
+        <v>78607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6294,44 +6294,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518808</v>
+        <v>518776</v>
       </c>
       <c r="R52" t="n">
-        <v>6994725</v>
+        <v>6994684</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6360,7 +6357,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6370,7 +6367,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6379,7 +6376,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6398,7 +6394,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121343249</v>
+        <v>121343732</v>
       </c>
       <c r="B53" t="n">
         <v>78607</v>
@@ -6434,14 +6430,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518808</v>
+        <v>518817</v>
       </c>
       <c r="R53" t="n">
-        <v>6994740</v>
+        <v>6994855</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6473,7 +6469,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6479,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,7 +6506,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121343305</v>
+        <v>121343472</v>
       </c>
       <c r="B54" t="n">
         <v>78607</v>
@@ -6550,10 +6546,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518812</v>
+        <v>518814</v>
       </c>
       <c r="R54" t="n">
-        <v>6994779</v>
+        <v>6994800</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6585,7 +6581,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6591,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,7 +6618,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121343959</v>
+        <v>121346092</v>
       </c>
       <c r="B55" t="n">
         <v>78607</v>
@@ -6662,10 +6658,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518825</v>
+        <v>518610</v>
       </c>
       <c r="R55" t="n">
-        <v>6994907</v>
+        <v>6995000</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6697,7 +6693,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6703,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,7 +6730,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121345946</v>
+        <v>121343305</v>
       </c>
       <c r="B56" t="n">
         <v>78607</v>
@@ -6770,17 +6766,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518414</v>
+        <v>518812</v>
       </c>
       <c r="R56" t="n">
-        <v>6995151</v>
+        <v>6994779</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6809,7 +6805,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6815,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,7 +6842,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343920</v>
+        <v>121344213</v>
       </c>
       <c r="B57" t="n">
         <v>78607</v>
@@ -6886,13 +6882,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518807</v>
+        <v>518792</v>
       </c>
       <c r="R57" t="n">
-        <v>6994899</v>
+        <v>6994973</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6921,7 +6917,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6927,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,7 +6954,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121346595</v>
+        <v>121346586</v>
       </c>
       <c r="B58" t="n">
         <v>78607</v>
@@ -6998,10 +6994,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518786</v>
+        <v>518787</v>
       </c>
       <c r="R58" t="n">
-        <v>6994717</v>
+        <v>6994738</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7033,7 +7029,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7039,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,10 +7066,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121344999</v>
+        <v>121343207</v>
       </c>
       <c r="B59" t="n">
-        <v>78607</v>
+        <v>91275</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7082,38 +7078,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518659</v>
+        <v>518808</v>
       </c>
       <c r="R59" t="n">
-        <v>6995028</v>
+        <v>6994725</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7145,7 +7144,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7154,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7164,6 +7163,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7182,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121344384</v>
+        <v>121344308</v>
       </c>
       <c r="B60" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7198,21 +7198,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518741</v>
+        <v>518783</v>
       </c>
       <c r="R60" t="n">
-        <v>6994995</v>
+        <v>6994979</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,7 +7294,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121343298</v>
+        <v>121345073</v>
       </c>
       <c r="B61" t="n">
         <v>78607</v>
@@ -7330,14 +7330,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518812</v>
+        <v>518555</v>
       </c>
       <c r="R61" t="n">
-        <v>6994775</v>
+        <v>6995010</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,7 +7406,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121345972</v>
+        <v>121345085</v>
       </c>
       <c r="B62" t="n">
         <v>78607</v>
@@ -7442,14 +7442,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518465</v>
+        <v>518559</v>
       </c>
       <c r="R62" t="n">
-        <v>6995120</v>
+        <v>6995004</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,7 +7518,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121343196</v>
+        <v>121344796</v>
       </c>
       <c r="B63" t="n">
         <v>78607</v>
@@ -7554,17 +7554,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518797</v>
+        <v>518665</v>
       </c>
       <c r="R63" t="n">
-        <v>6994707</v>
+        <v>6995040</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343229</v>
+        <v>121346053</v>
       </c>
       <c r="B64" t="n">
         <v>78607</v>
@@ -7666,14 +7666,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518808</v>
+        <v>518560</v>
       </c>
       <c r="R64" t="n">
-        <v>6994725</v>
+        <v>6995039</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,7 +7742,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121343625</v>
+        <v>121343797</v>
       </c>
       <c r="B65" t="n">
         <v>78607</v>
@@ -7778,14 +7778,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518819</v>
+        <v>518812</v>
       </c>
       <c r="R65" t="n">
-        <v>6994817</v>
+        <v>6994875</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,7 +7854,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121346289</v>
+        <v>121346533</v>
       </c>
       <c r="B66" t="n">
         <v>78607</v>
@@ -7890,17 +7890,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518618</v>
+        <v>518703</v>
       </c>
       <c r="R66" t="n">
-        <v>6994929</v>
+        <v>6994800</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121343093</v>
+        <v>121343229</v>
       </c>
       <c r="B67" t="n">
         <v>78607</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518801</v>
+        <v>518808</v>
       </c>
       <c r="R67" t="n">
-        <v>6994670</v>
+        <v>6994725</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343022</v>
+        <v>121344999</v>
       </c>
       <c r="B68" t="n">
         <v>78607</v>
@@ -8114,14 +8114,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518814</v>
+        <v>518659</v>
       </c>
       <c r="R68" t="n">
-        <v>6994676</v>
+        <v>6995028</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8188,6 +8188,118 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121539052</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79689</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lugnet, Lugnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>518823</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6994700</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -1462,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346074</v>
+        <v>121345116</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,37 +1478,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518583</v>
+        <v>518559</v>
       </c>
       <c r="R9" t="n">
-        <v>6995023</v>
+        <v>6994969</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,6 +1559,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121345116</v>
+        <v>121346074</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,40 +1594,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518559</v>
+        <v>518583</v>
       </c>
       <c r="R10" t="n">
-        <v>6994969</v>
+        <v>6995023</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,7 +1672,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -6842,10 +6842,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121344213</v>
+        <v>121343207</v>
       </c>
       <c r="B57" t="n">
-        <v>78607</v>
+        <v>91275</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6854,41 +6854,44 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518792</v>
+        <v>518808</v>
       </c>
       <c r="R57" t="n">
-        <v>6994973</v>
+        <v>6994725</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6917,7 +6920,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6927,7 +6930,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6936,6 +6939,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6954,7 +6958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121346586</v>
+        <v>121344213</v>
       </c>
       <c r="B58" t="n">
         <v>78607</v>
@@ -6990,14 +6994,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518787</v>
+        <v>518792</v>
       </c>
       <c r="R58" t="n">
-        <v>6994738</v>
+        <v>6994973</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7029,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7039,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7066,10 +7070,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121343207</v>
+        <v>121346586</v>
       </c>
       <c r="B59" t="n">
-        <v>91275</v>
+        <v>78607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7078,44 +7082,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518808</v>
+        <v>518787</v>
       </c>
       <c r="R59" t="n">
-        <v>6994725</v>
+        <v>6994738</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7144,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7154,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7163,7 +7164,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345918</v>
+        <v>121343207</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>91281</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518360</v>
+        <v>518808</v>
       </c>
       <c r="R3" t="n">
-        <v>6995099</v>
+        <v>6994725</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345064</v>
+        <v>121343092</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,17 +942,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518566</v>
+        <v>518811</v>
       </c>
       <c r="R4" t="n">
-        <v>6995030</v>
+        <v>6994686</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343809</v>
+        <v>121344213</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518808</v>
+        <v>518792</v>
       </c>
       <c r="R5" t="n">
-        <v>6994892</v>
+        <v>6994973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343018</v>
+        <v>121345938</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,17 +1166,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518813</v>
+        <v>518387</v>
       </c>
       <c r="R6" t="n">
-        <v>6994667</v>
+        <v>6995152</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343253</v>
+        <v>121346092</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,14 +1278,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518799</v>
+        <v>518610</v>
       </c>
       <c r="R7" t="n">
-        <v>6994749</v>
+        <v>6995000</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121344193</v>
+        <v>121345073</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,17 +1390,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518808</v>
+        <v>518555</v>
       </c>
       <c r="R8" t="n">
-        <v>6994956</v>
+        <v>6995010</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345116</v>
+        <v>121343178</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,40 +1482,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518559</v>
+        <v>518814</v>
       </c>
       <c r="R9" t="n">
-        <v>6994969</v>
+        <v>6994717</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,7 +1560,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346074</v>
+        <v>121343478</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,14 +1614,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518583</v>
+        <v>518834</v>
       </c>
       <c r="R10" t="n">
-        <v>6995023</v>
+        <v>6994815</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345972</v>
+        <v>121346074</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,17 +1726,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518465</v>
+        <v>518583</v>
       </c>
       <c r="R11" t="n">
-        <v>6995120</v>
+        <v>6995023</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343093</v>
+        <v>121345954</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,37 +1818,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518801</v>
+        <v>518428</v>
       </c>
       <c r="R12" t="n">
-        <v>6994670</v>
+        <v>6995142</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346005</v>
+        <v>121345116</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,37 +1930,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518483</v>
+        <v>518559</v>
       </c>
       <c r="R13" t="n">
-        <v>6995124</v>
+        <v>6994969</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,6 +2011,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2026,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346289</v>
+        <v>121343625</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,14 +2066,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518618</v>
+        <v>518819</v>
       </c>
       <c r="R14" t="n">
-        <v>6994929</v>
+        <v>6994817</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2101,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2111,7 +2115,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345954</v>
+        <v>121346595</v>
       </c>
       <c r="B15" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,34 +2158,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518428</v>
+        <v>518786</v>
       </c>
       <c r="R15" t="n">
-        <v>6995142</v>
+        <v>6994717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,7 +2217,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2227,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121343298</v>
+        <v>121346560</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518812</v>
+        <v>518787</v>
       </c>
       <c r="R16" t="n">
-        <v>6994775</v>
+        <v>6994752</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2335,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121344731</v>
+        <v>121343959</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,13 +2406,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518652</v>
+        <v>518825</v>
       </c>
       <c r="R17" t="n">
-        <v>6994988</v>
+        <v>6994907</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2437,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121343196</v>
+        <v>121343920</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,14 +2514,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518797</v>
+        <v>518807</v>
       </c>
       <c r="R18" t="n">
-        <v>6994707</v>
+        <v>6994899</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2549,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2563,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121344380</v>
+        <v>121343305</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,17 +2626,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518768</v>
+        <v>518812</v>
       </c>
       <c r="R19" t="n">
-        <v>6994994</v>
+        <v>6994779</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2661,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121343178</v>
+        <v>121346232</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,14 +2738,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518814</v>
+        <v>518626</v>
       </c>
       <c r="R20" t="n">
-        <v>6994717</v>
+        <v>6994964</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343478</v>
+        <v>121344731</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,14 +2850,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518834</v>
+        <v>518652</v>
       </c>
       <c r="R21" t="n">
-        <v>6994815</v>
+        <v>6994988</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343468</v>
+        <v>121343797</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,17 +2962,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518814</v>
+        <v>518812</v>
       </c>
       <c r="R22" t="n">
-        <v>6994789</v>
+        <v>6994875</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121345053</v>
+        <v>121346430</v>
       </c>
       <c r="B23" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,37 +3054,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518563</v>
+        <v>518614</v>
       </c>
       <c r="R23" t="n">
-        <v>6995042</v>
+        <v>6994902</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3109,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3146,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121343160</v>
+        <v>121346613</v>
       </c>
       <c r="B24" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3186,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518815</v>
+        <v>518770</v>
       </c>
       <c r="R24" t="n">
-        <v>6994704</v>
+        <v>6994702</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3221,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3231,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,10 +3262,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121344384</v>
+        <v>121343093</v>
       </c>
       <c r="B25" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3274,37 +3278,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518741</v>
+        <v>518801</v>
       </c>
       <c r="R25" t="n">
-        <v>6994995</v>
+        <v>6994670</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121343092</v>
+        <v>121345946</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3406,17 +3410,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518811</v>
+        <v>518414</v>
       </c>
       <c r="R26" t="n">
-        <v>6994686</v>
+        <v>6995151</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121343289</v>
+        <v>121344384</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3498,34 +3502,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518814</v>
+        <v>518741</v>
       </c>
       <c r="R27" t="n">
-        <v>6994762</v>
+        <v>6994995</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3557,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,10 +3598,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346620</v>
+        <v>121345122</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3630,14 +3634,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518774</v>
+        <v>518552</v>
       </c>
       <c r="R28" t="n">
-        <v>6994685</v>
+        <v>6994973</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,10 +3710,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121345938</v>
+        <v>121343022</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3742,17 +3746,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518387</v>
+        <v>518814</v>
       </c>
       <c r="R29" t="n">
-        <v>6995152</v>
+        <v>6994676</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3791,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,10 +3822,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121343137</v>
+        <v>121343289</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518823</v>
+        <v>518814</v>
       </c>
       <c r="R30" t="n">
-        <v>6994691</v>
+        <v>6994762</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3893,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121343303</v>
+        <v>121345064</v>
       </c>
       <c r="B31" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,14 +3970,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518809</v>
+        <v>518566</v>
       </c>
       <c r="R31" t="n">
-        <v>6994765</v>
+        <v>6995030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4005,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346430</v>
+        <v>121343809</v>
       </c>
       <c r="B32" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4082,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518614</v>
+        <v>518808</v>
       </c>
       <c r="R32" t="n">
-        <v>6994902</v>
+        <v>6994892</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4117,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121346025</v>
+        <v>121343253</v>
       </c>
       <c r="B33" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4190,17 +4194,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518519</v>
+        <v>518799</v>
       </c>
       <c r="R33" t="n">
-        <v>6995085</v>
+        <v>6994749</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4229,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,10 +4270,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121343959</v>
+        <v>121343018</v>
       </c>
       <c r="B34" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4302,14 +4306,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518825</v>
+        <v>518813</v>
       </c>
       <c r="R34" t="n">
-        <v>6994907</v>
+        <v>6994667</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4341,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121343524</v>
+        <v>121343137</v>
       </c>
       <c r="B35" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4418,10 +4422,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518815</v>
+        <v>518823</v>
       </c>
       <c r="R35" t="n">
-        <v>6994807</v>
+        <v>6994691</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4453,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346595</v>
+        <v>121344999</v>
       </c>
       <c r="B36" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4526,17 +4530,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518786</v>
+        <v>518659</v>
       </c>
       <c r="R36" t="n">
-        <v>6994717</v>
+        <v>6995028</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4565,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,10 +4606,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346126</v>
+        <v>121343468</v>
       </c>
       <c r="B37" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,17 +4642,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518627</v>
+        <v>518814</v>
       </c>
       <c r="R37" t="n">
-        <v>6994984</v>
+        <v>6994789</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4677,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,10 +4718,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121343285</v>
+        <v>121343249</v>
       </c>
       <c r="B38" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4754,13 +4758,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518804</v>
+        <v>518808</v>
       </c>
       <c r="R38" t="n">
-        <v>6994760</v>
+        <v>6994740</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4789,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4799,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4826,10 +4830,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121343249</v>
+        <v>121346038</v>
       </c>
       <c r="B39" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4862,14 +4866,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518808</v>
+        <v>518544</v>
       </c>
       <c r="R39" t="n">
-        <v>6994740</v>
+        <v>6995061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4901,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4911,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4938,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121343022</v>
+        <v>121346620</v>
       </c>
       <c r="B40" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4978,13 +4982,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518814</v>
+        <v>518774</v>
       </c>
       <c r="R40" t="n">
-        <v>6994676</v>
+        <v>6994685</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5013,7 +5017,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5027,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5050,10 +5054,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121345960</v>
+        <v>121345918</v>
       </c>
       <c r="B41" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5066,21 +5070,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5090,10 +5094,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518444</v>
+        <v>518360</v>
       </c>
       <c r="R41" t="n">
-        <v>6995141</v>
+        <v>6995099</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5125,7 +5129,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5139,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5162,10 +5166,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121346613</v>
+        <v>121346126</v>
       </c>
       <c r="B42" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5198,14 +5202,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518770</v>
+        <v>518627</v>
       </c>
       <c r="R42" t="n">
-        <v>6994702</v>
+        <v>6994984</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5237,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5247,7 +5251,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5274,10 +5278,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121346038</v>
+        <v>121343732</v>
       </c>
       <c r="B43" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5310,14 +5314,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518544</v>
+        <v>518817</v>
       </c>
       <c r="R43" t="n">
-        <v>6995061</v>
+        <v>6994855</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5349,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5359,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5386,10 +5390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121344818</v>
+        <v>121345085</v>
       </c>
       <c r="B44" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5426,13 +5430,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518624</v>
+        <v>518559</v>
       </c>
       <c r="R44" t="n">
-        <v>6995059</v>
+        <v>6995004</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5461,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5498,10 +5502,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121344456</v>
+        <v>121346289</v>
       </c>
       <c r="B45" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5538,10 +5542,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518727</v>
+        <v>518618</v>
       </c>
       <c r="R45" t="n">
-        <v>6994987</v>
+        <v>6994929</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5573,7 +5577,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5583,7 +5587,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5610,10 +5614,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121346232</v>
+        <v>121344193</v>
       </c>
       <c r="B46" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,13 +5654,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518626</v>
+        <v>518808</v>
       </c>
       <c r="R46" t="n">
-        <v>6994964</v>
+        <v>6994956</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5685,7 +5689,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5695,7 +5699,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,10 +5726,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121345946</v>
+        <v>121344818</v>
       </c>
       <c r="B47" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5758,14 +5762,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518414</v>
+        <v>518624</v>
       </c>
       <c r="R47" t="n">
-        <v>6995151</v>
+        <v>6995059</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5797,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5807,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5834,10 +5838,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121345122</v>
+        <v>121346586</v>
       </c>
       <c r="B48" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5870,14 +5874,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518552</v>
+        <v>518787</v>
       </c>
       <c r="R48" t="n">
-        <v>6994973</v>
+        <v>6994738</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5909,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5946,10 +5950,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121343625</v>
+        <v>121346053</v>
       </c>
       <c r="B49" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5982,14 +5986,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518819</v>
+        <v>518560</v>
       </c>
       <c r="R49" t="n">
-        <v>6994817</v>
+        <v>6995039</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6021,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6031,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6058,10 +6062,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121346560</v>
+        <v>121345960</v>
       </c>
       <c r="B50" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6074,37 +6078,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518787</v>
+        <v>518444</v>
       </c>
       <c r="R50" t="n">
-        <v>6994752</v>
+        <v>6995141</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6147,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6170,10 +6174,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121343920</v>
+        <v>121343303</v>
       </c>
       <c r="B51" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6206,17 +6210,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518807</v>
+        <v>518809</v>
       </c>
       <c r="R51" t="n">
-        <v>6994899</v>
+        <v>6994765</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6245,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6255,7 +6259,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6282,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121346635</v>
+        <v>121343285</v>
       </c>
       <c r="B52" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6322,13 +6326,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518776</v>
+        <v>518804</v>
       </c>
       <c r="R52" t="n">
-        <v>6994684</v>
+        <v>6994760</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6367,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6394,10 +6398,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121343732</v>
+        <v>121344380</v>
       </c>
       <c r="B53" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6434,13 +6438,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518817</v>
+        <v>518768</v>
       </c>
       <c r="R53" t="n">
-        <v>6994855</v>
+        <v>6994994</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6469,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6479,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6506,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121343472</v>
+        <v>121344796</v>
       </c>
       <c r="B54" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6542,17 +6546,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518814</v>
+        <v>518665</v>
       </c>
       <c r="R54" t="n">
-        <v>6994800</v>
+        <v>6995040</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6581,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6591,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,10 +6622,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121346092</v>
+        <v>121343160</v>
       </c>
       <c r="B55" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6634,34 +6638,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518610</v>
+        <v>518815</v>
       </c>
       <c r="R55" t="n">
-        <v>6995000</v>
+        <v>6994704</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6693,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6703,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6730,10 +6734,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121343305</v>
+        <v>121344456</v>
       </c>
       <c r="B56" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6766,14 +6770,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518812</v>
+        <v>518727</v>
       </c>
       <c r="R56" t="n">
-        <v>6994779</v>
+        <v>6994987</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6805,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6815,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343207</v>
+        <v>121343298</v>
       </c>
       <c r="B57" t="n">
-        <v>91275</v>
+        <v>78608</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6854,44 +6858,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518808</v>
+        <v>518812</v>
       </c>
       <c r="R57" t="n">
-        <v>6994725</v>
+        <v>6994775</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6920,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6930,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6939,7 +6940,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6958,10 +6958,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121344213</v>
+        <v>121343472</v>
       </c>
       <c r="B58" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6994,17 +6994,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518792</v>
+        <v>518814</v>
       </c>
       <c r="R58" t="n">
-        <v>6994973</v>
+        <v>6994800</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,10 +7070,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121346586</v>
+        <v>121343524</v>
       </c>
       <c r="B59" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7110,13 +7110,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518787</v>
+        <v>518815</v>
       </c>
       <c r="R59" t="n">
-        <v>6994738</v>
+        <v>6994807</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121344308</v>
+        <v>121343229</v>
       </c>
       <c r="B60" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7218,17 +7218,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518783</v>
+        <v>518808</v>
       </c>
       <c r="R60" t="n">
-        <v>6994979</v>
+        <v>6994725</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,10 +7294,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121345073</v>
+        <v>121345053</v>
       </c>
       <c r="B61" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7310,21 +7310,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7334,13 +7334,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518555</v>
+        <v>518563</v>
       </c>
       <c r="R61" t="n">
-        <v>6995010</v>
+        <v>6995042</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121345085</v>
+        <v>121345972</v>
       </c>
       <c r="B62" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7442,14 +7442,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518559</v>
+        <v>518465</v>
       </c>
       <c r="R62" t="n">
-        <v>6995004</v>
+        <v>6995120</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121344796</v>
+        <v>121346005</v>
       </c>
       <c r="B63" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7554,14 +7554,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518665</v>
+        <v>518483</v>
       </c>
       <c r="R63" t="n">
-        <v>6995040</v>
+        <v>6995124</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,10 +7630,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121346053</v>
+        <v>121343196</v>
       </c>
       <c r="B64" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7666,14 +7666,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518560</v>
+        <v>518797</v>
       </c>
       <c r="R64" t="n">
-        <v>6995039</v>
+        <v>6994707</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121343797</v>
+        <v>121344308</v>
       </c>
       <c r="B65" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7782,13 +7782,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518812</v>
+        <v>518783</v>
       </c>
       <c r="R65" t="n">
-        <v>6994875</v>
+        <v>6994979</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7857,7 +7857,7 @@
         <v>121346533</v>
       </c>
       <c r="B66" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7966,10 +7966,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121343229</v>
+        <v>121346025</v>
       </c>
       <c r="B67" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,17 +8002,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518808</v>
+        <v>518519</v>
       </c>
       <c r="R67" t="n">
-        <v>6994725</v>
+        <v>6995085</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,10 +8078,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121344999</v>
+        <v>121346635</v>
       </c>
       <c r="B68" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8114,17 +8114,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518659</v>
+        <v>518776</v>
       </c>
       <c r="R68" t="n">
-        <v>6995028</v>
+        <v>6994684</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -6846,7 +6846,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343298</v>
+        <v>121343229</v>
       </c>
       <c r="B57" t="n">
         <v>78608</v>
@@ -6886,13 +6886,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518812</v>
+        <v>518808</v>
       </c>
       <c r="R57" t="n">
-        <v>6994775</v>
+        <v>6994725</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121343472</v>
+        <v>121343298</v>
       </c>
       <c r="B58" t="n">
         <v>78608</v>
@@ -6998,13 +6998,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518814</v>
+        <v>518812</v>
       </c>
       <c r="R58" t="n">
-        <v>6994800</v>
+        <v>6994775</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,7 +7070,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121343524</v>
+        <v>121343472</v>
       </c>
       <c r="B59" t="n">
         <v>78608</v>
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518815</v>
+        <v>518814</v>
       </c>
       <c r="R59" t="n">
-        <v>6994807</v>
+        <v>6994800</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,7 +7182,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121343229</v>
+        <v>121343524</v>
       </c>
       <c r="B60" t="n">
         <v>78608</v>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518808</v>
+        <v>518815</v>
       </c>
       <c r="R60" t="n">
-        <v>6994725</v>
+        <v>6994807</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121343207</v>
+        <v>121343137</v>
       </c>
       <c r="B3" t="n">
-        <v>91281</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,41 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518808</v>
+        <v>518823</v>
       </c>
       <c r="R3" t="n">
-        <v>6994725</v>
+        <v>6994691</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -868,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +884,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121343092</v>
+        <v>121345116</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,34 +918,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518811</v>
+        <v>518559</v>
       </c>
       <c r="R4" t="n">
-        <v>6994686</v>
+        <v>6994969</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +999,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344213</v>
+        <v>121343809</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518792</v>
+        <v>518808</v>
       </c>
       <c r="R5" t="n">
-        <v>6994973</v>
+        <v>6994892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121345938</v>
+        <v>121344999</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,17 +1166,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518387</v>
+        <v>518659</v>
       </c>
       <c r="R6" t="n">
-        <v>6995152</v>
+        <v>6995028</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346092</v>
+        <v>121343625</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,14 +1278,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518610</v>
+        <v>518819</v>
       </c>
       <c r="R7" t="n">
-        <v>6995000</v>
+        <v>6994817</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345073</v>
+        <v>121343959</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518555</v>
+        <v>518825</v>
       </c>
       <c r="R8" t="n">
-        <v>6995010</v>
+        <v>6994907</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343178</v>
+        <v>121346620</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518814</v>
+        <v>518774</v>
       </c>
       <c r="R9" t="n">
-        <v>6994717</v>
+        <v>6994685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343478</v>
+        <v>121343093</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518834</v>
+        <v>518801</v>
       </c>
       <c r="R10" t="n">
-        <v>6994815</v>
+        <v>6994670</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346074</v>
+        <v>121343478</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,14 +1726,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518583</v>
+        <v>518834</v>
       </c>
       <c r="R11" t="n">
-        <v>6995023</v>
+        <v>6994815</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121345954</v>
+        <v>121344796</v>
       </c>
       <c r="B12" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,34 +1818,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518428</v>
+        <v>518665</v>
       </c>
       <c r="R12" t="n">
-        <v>6995142</v>
+        <v>6995040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345116</v>
+        <v>121345918</v>
       </c>
       <c r="B13" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,37 +1930,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518559</v>
+        <v>518360</v>
       </c>
       <c r="R13" t="n">
-        <v>6994969</v>
+        <v>6995099</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1992,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,7 +2008,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2030,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121343625</v>
+        <v>121346092</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,14 +2062,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518819</v>
+        <v>518610</v>
       </c>
       <c r="R14" t="n">
-        <v>6994817</v>
+        <v>6995000</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2105,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346595</v>
+        <v>121343160</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,21 +2154,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,13 +2178,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518786</v>
+        <v>518815</v>
       </c>
       <c r="R15" t="n">
-        <v>6994717</v>
+        <v>6994704</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,7 +2213,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2227,7 +2223,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346560</v>
+        <v>121346025</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,14 +2286,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518787</v>
+        <v>518519</v>
       </c>
       <c r="R16" t="n">
-        <v>6994752</v>
+        <v>6995085</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2329,7 +2325,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2335,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121343959</v>
+        <v>121344456</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518825</v>
+        <v>518727</v>
       </c>
       <c r="R17" t="n">
-        <v>6994907</v>
+        <v>6994987</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2441,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2447,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121343920</v>
+        <v>121343285</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,14 +2510,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518807</v>
+        <v>518804</v>
       </c>
       <c r="R18" t="n">
-        <v>6994899</v>
+        <v>6994760</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2553,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121343305</v>
+        <v>121346635</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,13 +2626,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518812</v>
+        <v>518776</v>
       </c>
       <c r="R19" t="n">
-        <v>6994779</v>
+        <v>6994684</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2665,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346232</v>
+        <v>121346038</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,14 +2734,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518626</v>
+        <v>518544</v>
       </c>
       <c r="R20" t="n">
-        <v>6994964</v>
+        <v>6995061</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121344731</v>
+        <v>121343732</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2854,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518652</v>
+        <v>518817</v>
       </c>
       <c r="R21" t="n">
-        <v>6994988</v>
+        <v>6994855</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343797</v>
+        <v>121345954</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,37 +2938,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518812</v>
+        <v>518428</v>
       </c>
       <c r="R22" t="n">
-        <v>6994875</v>
+        <v>6995142</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346430</v>
+        <v>121343524</v>
       </c>
       <c r="B23" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3074,17 +3070,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518614</v>
+        <v>518815</v>
       </c>
       <c r="R23" t="n">
-        <v>6994902</v>
+        <v>6994807</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346613</v>
+        <v>121343022</v>
       </c>
       <c r="B24" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,10 +3186,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518770</v>
+        <v>518814</v>
       </c>
       <c r="R24" t="n">
-        <v>6994702</v>
+        <v>6994676</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3225,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,10 +3258,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121343093</v>
+        <v>121343018</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,13 +3298,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518801</v>
+        <v>518813</v>
       </c>
       <c r="R25" t="n">
-        <v>6994670</v>
+        <v>6994667</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3337,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121345946</v>
+        <v>121344384</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,37 +3386,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518414</v>
+        <v>518741</v>
       </c>
       <c r="R26" t="n">
-        <v>6995151</v>
+        <v>6994995</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3449,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121344384</v>
+        <v>121345946</v>
       </c>
       <c r="B27" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3502,37 +3498,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518741</v>
+        <v>518414</v>
       </c>
       <c r="R27" t="n">
-        <v>6994995</v>
+        <v>6995151</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3561,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,7 +3597,7 @@
         <v>121345122</v>
       </c>
       <c r="B28" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3710,10 +3706,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343022</v>
+        <v>121343249</v>
       </c>
       <c r="B29" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,13 +3746,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518814</v>
+        <v>518808</v>
       </c>
       <c r="R29" t="n">
-        <v>6994676</v>
+        <v>6994740</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3785,7 +3781,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3791,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121343289</v>
+        <v>121344308</v>
       </c>
       <c r="B30" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,17 +3854,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518814</v>
+        <v>518783</v>
       </c>
       <c r="R30" t="n">
-        <v>6994762</v>
+        <v>6994979</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3897,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,10 +3930,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121345064</v>
+        <v>121345938</v>
       </c>
       <c r="B31" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518566</v>
+        <v>518387</v>
       </c>
       <c r="R31" t="n">
-        <v>6995030</v>
+        <v>6995152</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4009,7 +4005,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,7 +4015,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121343809</v>
+        <v>121346005</v>
       </c>
       <c r="B32" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4082,14 +4078,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518808</v>
+        <v>518483</v>
       </c>
       <c r="R32" t="n">
-        <v>6994892</v>
+        <v>6995124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121343253</v>
+        <v>121343229</v>
       </c>
       <c r="B33" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,10 +4194,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518799</v>
+        <v>518808</v>
       </c>
       <c r="R33" t="n">
-        <v>6994749</v>
+        <v>6994725</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4233,7 +4229,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4239,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,10 +4266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121343018</v>
+        <v>121346613</v>
       </c>
       <c r="B34" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,10 +4306,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518813</v>
+        <v>518770</v>
       </c>
       <c r="R34" t="n">
-        <v>6994667</v>
+        <v>6994702</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4345,7 +4341,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4351,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121343137</v>
+        <v>121345972</v>
       </c>
       <c r="B35" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4418,14 +4414,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518823</v>
+        <v>518465</v>
       </c>
       <c r="R35" t="n">
-        <v>6994691</v>
+        <v>6995120</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4457,7 +4453,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4463,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121344999</v>
+        <v>121344380</v>
       </c>
       <c r="B36" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,13 +4530,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518659</v>
+        <v>518768</v>
       </c>
       <c r="R36" t="n">
-        <v>6995028</v>
+        <v>6994994</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4569,7 +4565,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4575,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,10 +4602,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121343468</v>
+        <v>121345064</v>
       </c>
       <c r="B37" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4642,14 +4638,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518814</v>
+        <v>518566</v>
       </c>
       <c r="R37" t="n">
-        <v>6994789</v>
+        <v>6995030</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,7 +4677,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4687,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,10 +4714,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121343249</v>
+        <v>121346430</v>
       </c>
       <c r="B38" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4754,14 +4750,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518808</v>
+        <v>518614</v>
       </c>
       <c r="R38" t="n">
-        <v>6994740</v>
+        <v>6994902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4793,7 +4789,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4799,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,10 +4826,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346038</v>
+        <v>121346053</v>
       </c>
       <c r="B39" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4870,13 +4866,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518544</v>
+        <v>518560</v>
       </c>
       <c r="R39" t="n">
-        <v>6995061</v>
+        <v>6995039</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4905,7 +4901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4911,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,10 +4938,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121346620</v>
+        <v>121344193</v>
       </c>
       <c r="B40" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4978,17 +4974,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518774</v>
+        <v>518808</v>
       </c>
       <c r="R40" t="n">
-        <v>6994685</v>
+        <v>6994956</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5017,7 +5013,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5027,7 +5023,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,10 +5050,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121345918</v>
+        <v>121346586</v>
       </c>
       <c r="B41" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5090,17 +5086,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518360</v>
+        <v>518787</v>
       </c>
       <c r="R41" t="n">
-        <v>6995099</v>
+        <v>6994738</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5129,7 +5125,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5139,7 +5135,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121346126</v>
+        <v>121343092</v>
       </c>
       <c r="B42" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5202,14 +5198,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518627</v>
+        <v>518811</v>
       </c>
       <c r="R42" t="n">
-        <v>6994984</v>
+        <v>6994686</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5241,7 +5237,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5251,7 +5247,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5278,10 +5274,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121343732</v>
+        <v>121343797</v>
       </c>
       <c r="B43" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5318,13 +5314,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518817</v>
+        <v>518812</v>
       </c>
       <c r="R43" t="n">
-        <v>6994855</v>
+        <v>6994875</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5353,7 +5349,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5359,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,10 +5386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121345085</v>
+        <v>121346560</v>
       </c>
       <c r="B44" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5426,17 +5422,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518559</v>
+        <v>518787</v>
       </c>
       <c r="R44" t="n">
-        <v>6995004</v>
+        <v>6994752</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5465,7 +5461,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5475,7 +5471,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,10 +5498,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121346289</v>
+        <v>121345073</v>
       </c>
       <c r="B45" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5538,17 +5534,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518618</v>
+        <v>518555</v>
       </c>
       <c r="R45" t="n">
-        <v>6994929</v>
+        <v>6995010</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5577,7 +5573,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5587,7 +5583,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5614,10 +5610,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121344193</v>
+        <v>121346533</v>
       </c>
       <c r="B46" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,17 +5646,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518808</v>
+        <v>518703</v>
       </c>
       <c r="R46" t="n">
-        <v>6994956</v>
+        <v>6994800</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5689,7 +5685,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5699,7 +5695,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,10 +5722,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121344818</v>
+        <v>121343289</v>
       </c>
       <c r="B47" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5762,17 +5758,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518624</v>
+        <v>518814</v>
       </c>
       <c r="R47" t="n">
-        <v>6995059</v>
+        <v>6994762</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5801,7 +5797,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5807,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,10 +5834,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121346586</v>
+        <v>121343920</v>
       </c>
       <c r="B48" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5874,17 +5870,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518787</v>
+        <v>518807</v>
       </c>
       <c r="R48" t="n">
-        <v>6994738</v>
+        <v>6994899</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5913,7 +5909,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5919,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,10 +5946,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121346053</v>
+        <v>121343298</v>
       </c>
       <c r="B49" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5986,17 +5982,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518560</v>
+        <v>518812</v>
       </c>
       <c r="R49" t="n">
-        <v>6995039</v>
+        <v>6994775</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6025,7 +6021,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6031,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6062,10 +6058,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121345960</v>
+        <v>121345085</v>
       </c>
       <c r="B50" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6078,34 +6074,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518444</v>
+        <v>518559</v>
       </c>
       <c r="R50" t="n">
-        <v>6995141</v>
+        <v>6995004</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6137,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6174,10 +6170,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121343303</v>
+        <v>121344818</v>
       </c>
       <c r="B51" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6210,14 +6206,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518809</v>
+        <v>518624</v>
       </c>
       <c r="R51" t="n">
-        <v>6994765</v>
+        <v>6995059</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6249,7 +6245,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,7 +6255,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6286,10 +6282,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121343285</v>
+        <v>121344731</v>
       </c>
       <c r="B52" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6322,17 +6318,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518804</v>
+        <v>518652</v>
       </c>
       <c r="R52" t="n">
-        <v>6994760</v>
+        <v>6994988</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6361,7 +6357,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,7 +6367,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6398,10 +6394,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121344380</v>
+        <v>121343196</v>
       </c>
       <c r="B53" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6434,17 +6430,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518768</v>
+        <v>518797</v>
       </c>
       <c r="R53" t="n">
-        <v>6994994</v>
+        <v>6994707</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6473,7 +6469,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6479,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,10 +6506,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121344796</v>
+        <v>121344213</v>
       </c>
       <c r="B54" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6550,10 +6546,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518665</v>
+        <v>518792</v>
       </c>
       <c r="R54" t="n">
-        <v>6995040</v>
+        <v>6994973</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6585,7 +6581,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6591,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,10 +6618,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121343160</v>
+        <v>121346289</v>
       </c>
       <c r="B55" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6638,34 +6634,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518815</v>
+        <v>518618</v>
       </c>
       <c r="R55" t="n">
-        <v>6994704</v>
+        <v>6994929</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6697,7 +6693,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6703,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,10 +6730,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121344456</v>
+        <v>121345053</v>
       </c>
       <c r="B56" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6750,34 +6746,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518727</v>
+        <v>518563</v>
       </c>
       <c r="R56" t="n">
-        <v>6994987</v>
+        <v>6995042</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6809,7 +6805,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6815,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,10 +6842,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343229</v>
+        <v>121345960</v>
       </c>
       <c r="B57" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6862,34 +6858,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518808</v>
+        <v>518444</v>
       </c>
       <c r="R57" t="n">
-        <v>6994725</v>
+        <v>6995141</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6921,7 +6917,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6927,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,10 +6954,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121343298</v>
+        <v>121346074</v>
       </c>
       <c r="B58" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6994,14 +6990,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518812</v>
+        <v>518583</v>
       </c>
       <c r="R58" t="n">
-        <v>6994775</v>
+        <v>6995023</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7033,7 +7029,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7039,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,10 +7066,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121343472</v>
+        <v>121346126</v>
       </c>
       <c r="B59" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7106,14 +7102,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518814</v>
+        <v>518627</v>
       </c>
       <c r="R59" t="n">
-        <v>6994800</v>
+        <v>6994984</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7145,7 +7141,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7151,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,10 +7178,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121343524</v>
+        <v>121343253</v>
       </c>
       <c r="B60" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7222,10 +7218,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518815</v>
+        <v>518799</v>
       </c>
       <c r="R60" t="n">
-        <v>6994807</v>
+        <v>6994749</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7257,7 +7253,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7263,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,10 +7290,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121345053</v>
+        <v>121343178</v>
       </c>
       <c r="B61" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7310,37 +7306,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518563</v>
+        <v>518814</v>
       </c>
       <c r="R61" t="n">
-        <v>6995042</v>
+        <v>6994717</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7369,7 +7365,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7375,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,10 +7402,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121345972</v>
+        <v>121343305</v>
       </c>
       <c r="B62" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7442,14 +7438,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518465</v>
+        <v>518812</v>
       </c>
       <c r="R62" t="n">
-        <v>6995120</v>
+        <v>6994779</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7481,7 +7477,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7487,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,10 +7514,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121346005</v>
+        <v>121346232</v>
       </c>
       <c r="B63" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7554,14 +7550,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518483</v>
+        <v>518626</v>
       </c>
       <c r="R63" t="n">
-        <v>6995124</v>
+        <v>6994964</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7593,7 +7589,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7599,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,10 +7626,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343196</v>
+        <v>121343472</v>
       </c>
       <c r="B64" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7670,10 +7666,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518797</v>
+        <v>518814</v>
       </c>
       <c r="R64" t="n">
-        <v>6994707</v>
+        <v>6994800</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7705,7 +7701,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7711,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7738,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121344308</v>
+        <v>121343207</v>
       </c>
       <c r="B65" t="n">
-        <v>78608</v>
+        <v>91282</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7754,41 +7750,44 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518783</v>
+        <v>518808</v>
       </c>
       <c r="R65" t="n">
-        <v>6994979</v>
+        <v>6994725</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7816,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7826,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7836,6 +7835,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7854,10 +7854,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121346533</v>
+        <v>121346595</v>
       </c>
       <c r="B66" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518703</v>
+        <v>518786</v>
       </c>
       <c r="R66" t="n">
-        <v>6994800</v>
+        <v>6994717</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121346025</v>
+        <v>121343303</v>
       </c>
       <c r="B67" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8002,14 +8002,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518519</v>
+        <v>518809</v>
       </c>
       <c r="R67" t="n">
-        <v>6995085</v>
+        <v>6994765</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,10 +8078,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121346635</v>
+        <v>121343468</v>
       </c>
       <c r="B68" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518776</v>
+        <v>518814</v>
       </c>
       <c r="R68" t="n">
-        <v>6994684</v>
+        <v>6994789</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8193,7 +8193,7 @@
         <v>121539052</v>
       </c>
       <c r="B69" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121343137</v>
+        <v>121345085</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -826,14 +826,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518823</v>
+        <v>518559</v>
       </c>
       <c r="R3" t="n">
-        <v>6994691</v>
+        <v>6995004</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121345116</v>
+        <v>121343018</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,37 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518559</v>
+        <v>518813</v>
       </c>
       <c r="R4" t="n">
-        <v>6994969</v>
+        <v>6994667</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -980,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343809</v>
+        <v>121346613</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1054,17 +1050,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518808</v>
+        <v>518770</v>
       </c>
       <c r="R5" t="n">
-        <v>6994892</v>
+        <v>6994702</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344999</v>
+        <v>121344456</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1170,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518659</v>
+        <v>518727</v>
       </c>
       <c r="R6" t="n">
-        <v>6995028</v>
+        <v>6994987</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1205,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343625</v>
+        <v>121346005</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1278,17 +1274,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518819</v>
+        <v>518483</v>
       </c>
       <c r="R7" t="n">
-        <v>6994817</v>
+        <v>6995124</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343959</v>
+        <v>121345064</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1390,17 +1386,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518825</v>
+        <v>518566</v>
       </c>
       <c r="R8" t="n">
-        <v>6994907</v>
+        <v>6995030</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346620</v>
+        <v>121343207</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>91282</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,41 +1474,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518774</v>
+        <v>518808</v>
       </c>
       <c r="R9" t="n">
-        <v>6994685</v>
+        <v>6994725</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,6 +1559,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343093</v>
+        <v>121343809</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1614,17 +1614,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518801</v>
+        <v>518808</v>
       </c>
       <c r="R10" t="n">
-        <v>6994670</v>
+        <v>6994892</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343478</v>
+        <v>121343303</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518834</v>
+        <v>518809</v>
       </c>
       <c r="R11" t="n">
-        <v>6994815</v>
+        <v>6994765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121344796</v>
+        <v>121343920</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518665</v>
+        <v>518807</v>
       </c>
       <c r="R12" t="n">
-        <v>6995040</v>
+        <v>6994899</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345918</v>
+        <v>121343797</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1950,14 +1950,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518360</v>
+        <v>518812</v>
       </c>
       <c r="R13" t="n">
-        <v>6995099</v>
+        <v>6994875</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346092</v>
+        <v>121345053</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,34 +2042,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518610</v>
+        <v>518563</v>
       </c>
       <c r="R14" t="n">
-        <v>6995000</v>
+        <v>6995042</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121343160</v>
+        <v>121343524</v>
       </c>
       <c r="B15" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,21 +2154,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
         <v>518815</v>
       </c>
       <c r="R15" t="n">
-        <v>6994704</v>
+        <v>6994807</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,7 +2250,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346025</v>
+        <v>121344796</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2286,14 +2286,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518519</v>
+        <v>518665</v>
       </c>
       <c r="R16" t="n">
-        <v>6995085</v>
+        <v>6995040</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121344456</v>
+        <v>121345946</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2398,17 +2398,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518727</v>
+        <v>518414</v>
       </c>
       <c r="R17" t="n">
-        <v>6994987</v>
+        <v>6995151</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121343285</v>
+        <v>121345954</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,37 +2490,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518804</v>
+        <v>518428</v>
       </c>
       <c r="R18" t="n">
-        <v>6994760</v>
+        <v>6995142</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,7 +2586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346635</v>
+        <v>121343092</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518776</v>
+        <v>518811</v>
       </c>
       <c r="R19" t="n">
-        <v>6994684</v>
+        <v>6994686</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346038</v>
+        <v>121345116</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,37 +2714,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518544</v>
+        <v>518559</v>
       </c>
       <c r="R20" t="n">
-        <v>6995061</v>
+        <v>6994969</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2773,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,6 +2795,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2810,7 +2814,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343732</v>
+        <v>121343249</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2846,14 +2850,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518817</v>
+        <v>518808</v>
       </c>
       <c r="R21" t="n">
-        <v>6994855</v>
+        <v>6994740</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121345954</v>
+        <v>121343959</v>
       </c>
       <c r="B22" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,37 +2942,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518428</v>
+        <v>518825</v>
       </c>
       <c r="R22" t="n">
-        <v>6995142</v>
+        <v>6994907</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121343524</v>
+        <v>121344384</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,34 +3054,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518815</v>
+        <v>518741</v>
       </c>
       <c r="R23" t="n">
-        <v>6994807</v>
+        <v>6994995</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3109,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3146,7 +3150,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121343022</v>
+        <v>121346126</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -3182,14 +3186,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518814</v>
+        <v>518627</v>
       </c>
       <c r="R24" t="n">
-        <v>6994676</v>
+        <v>6994984</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3221,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3231,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,7 +3262,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121343018</v>
+        <v>121344818</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3294,17 +3298,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518813</v>
+        <v>518624</v>
       </c>
       <c r="R25" t="n">
-        <v>6994667</v>
+        <v>6995059</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121344384</v>
+        <v>121346038</v>
       </c>
       <c r="B26" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,37 +3390,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518741</v>
+        <v>518544</v>
       </c>
       <c r="R26" t="n">
-        <v>6994995</v>
+        <v>6995061</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,7 +3486,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121345946</v>
+        <v>121343137</v>
       </c>
       <c r="B27" t="n">
         <v>78609</v>
@@ -3518,17 +3522,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518414</v>
+        <v>518823</v>
       </c>
       <c r="R27" t="n">
-        <v>6995151</v>
+        <v>6994691</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3557,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121345122</v>
+        <v>121346620</v>
       </c>
       <c r="B28" t="n">
         <v>78609</v>
@@ -3630,14 +3634,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518552</v>
+        <v>518774</v>
       </c>
       <c r="R28" t="n">
-        <v>6994973</v>
+        <v>6994685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,7 +3710,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343249</v>
+        <v>121343285</v>
       </c>
       <c r="B29" t="n">
         <v>78609</v>
@@ -3746,13 +3750,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518808</v>
+        <v>518804</v>
       </c>
       <c r="R29" t="n">
-        <v>6994740</v>
+        <v>6994760</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3791,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,7 +3822,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121344308</v>
+        <v>121343472</v>
       </c>
       <c r="B30" t="n">
         <v>78609</v>
@@ -3854,17 +3858,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518783</v>
+        <v>518814</v>
       </c>
       <c r="R30" t="n">
-        <v>6994979</v>
+        <v>6994800</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121345938</v>
+        <v>121344999</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3966,17 +3970,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518387</v>
+        <v>518659</v>
       </c>
       <c r="R31" t="n">
-        <v>6995152</v>
+        <v>6995028</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4005,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4015,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,7 +4046,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346005</v>
+        <v>121346092</v>
       </c>
       <c r="B32" t="n">
         <v>78609</v>
@@ -4078,17 +4082,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518483</v>
+        <v>518610</v>
       </c>
       <c r="R32" t="n">
-        <v>6995124</v>
+        <v>6995000</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4154,7 +4158,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121343229</v>
+        <v>121343478</v>
       </c>
       <c r="B33" t="n">
         <v>78609</v>
@@ -4194,13 +4198,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518808</v>
+        <v>518834</v>
       </c>
       <c r="R33" t="n">
-        <v>6994725</v>
+        <v>6994815</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4229,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,7 +4270,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121346613</v>
+        <v>121343022</v>
       </c>
       <c r="B34" t="n">
         <v>78609</v>
@@ -4306,10 +4310,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518770</v>
+        <v>518814</v>
       </c>
       <c r="R34" t="n">
-        <v>6994702</v>
+        <v>6994676</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4341,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4351,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,7 +4382,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121345972</v>
+        <v>121343229</v>
       </c>
       <c r="B35" t="n">
         <v>78609</v>
@@ -4414,14 +4418,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518465</v>
+        <v>518808</v>
       </c>
       <c r="R35" t="n">
-        <v>6995120</v>
+        <v>6994725</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4453,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121344380</v>
+        <v>121346560</v>
       </c>
       <c r="B36" t="n">
         <v>78609</v>
@@ -4526,17 +4530,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518768</v>
+        <v>518787</v>
       </c>
       <c r="R36" t="n">
-        <v>6994994</v>
+        <v>6994752</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4565,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4602,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121345064</v>
+        <v>121346533</v>
       </c>
       <c r="B37" t="n">
         <v>78609</v>
@@ -4638,14 +4642,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518566</v>
+        <v>518703</v>
       </c>
       <c r="R37" t="n">
-        <v>6995030</v>
+        <v>6994800</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4677,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,7 +4718,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121346430</v>
+        <v>121343305</v>
       </c>
       <c r="B38" t="n">
         <v>78609</v>
@@ -4750,17 +4754,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518614</v>
+        <v>518812</v>
       </c>
       <c r="R38" t="n">
-        <v>6994902</v>
+        <v>6994779</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4789,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4799,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4826,7 +4830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346053</v>
+        <v>121346232</v>
       </c>
       <c r="B39" t="n">
         <v>78609</v>
@@ -4862,17 +4866,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518560</v>
+        <v>518626</v>
       </c>
       <c r="R39" t="n">
-        <v>6995039</v>
+        <v>6994964</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4901,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4911,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4938,7 +4942,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121344193</v>
+        <v>121343196</v>
       </c>
       <c r="B40" t="n">
         <v>78609</v>
@@ -4974,14 +4978,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518808</v>
+        <v>518797</v>
       </c>
       <c r="R40" t="n">
-        <v>6994956</v>
+        <v>6994707</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5013,7 +5017,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5023,7 +5027,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5050,7 +5054,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121346586</v>
+        <v>121343093</v>
       </c>
       <c r="B41" t="n">
         <v>78609</v>
@@ -5090,13 +5094,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518787</v>
+        <v>518801</v>
       </c>
       <c r="R41" t="n">
-        <v>6994738</v>
+        <v>6994670</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5125,7 +5129,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5135,7 +5139,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5162,7 +5166,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121343092</v>
+        <v>121346074</v>
       </c>
       <c r="B42" t="n">
         <v>78609</v>
@@ -5198,17 +5202,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518811</v>
+        <v>518583</v>
       </c>
       <c r="R42" t="n">
-        <v>6994686</v>
+        <v>6995023</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5237,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5247,7 +5251,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5274,7 +5278,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121343797</v>
+        <v>121346635</v>
       </c>
       <c r="B43" t="n">
         <v>78609</v>
@@ -5310,17 +5314,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518812</v>
+        <v>518776</v>
       </c>
       <c r="R43" t="n">
-        <v>6994875</v>
+        <v>6994684</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5349,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5359,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5386,7 +5390,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121346560</v>
+        <v>121345073</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -5422,14 +5426,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518787</v>
+        <v>518555</v>
       </c>
       <c r="R44" t="n">
-        <v>6994752</v>
+        <v>6995010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5461,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5498,7 +5502,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121345073</v>
+        <v>121346025</v>
       </c>
       <c r="B45" t="n">
         <v>78609</v>
@@ -5538,10 +5542,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518555</v>
+        <v>518519</v>
       </c>
       <c r="R45" t="n">
-        <v>6995010</v>
+        <v>6995085</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5573,7 +5577,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5583,7 +5587,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5610,7 +5614,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121346533</v>
+        <v>121344380</v>
       </c>
       <c r="B46" t="n">
         <v>78609</v>
@@ -5646,17 +5650,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518703</v>
+        <v>518768</v>
       </c>
       <c r="R46" t="n">
-        <v>6994800</v>
+        <v>6994994</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5685,7 +5689,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5695,7 +5699,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5722,7 +5726,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121343289</v>
+        <v>121343625</v>
       </c>
       <c r="B47" t="n">
         <v>78609</v>
@@ -5762,10 +5766,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518814</v>
+        <v>518819</v>
       </c>
       <c r="R47" t="n">
-        <v>6994762</v>
+        <v>6994817</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5797,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5807,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5834,7 +5838,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121343920</v>
+        <v>121344731</v>
       </c>
       <c r="B48" t="n">
         <v>78609</v>
@@ -5874,13 +5878,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518807</v>
+        <v>518652</v>
       </c>
       <c r="R48" t="n">
-        <v>6994899</v>
+        <v>6994988</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5909,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5946,7 +5950,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121343298</v>
+        <v>121345972</v>
       </c>
       <c r="B49" t="n">
         <v>78609</v>
@@ -5982,17 +5986,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518812</v>
+        <v>518465</v>
       </c>
       <c r="R49" t="n">
-        <v>6994775</v>
+        <v>6995120</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6021,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6031,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6058,7 +6062,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121345085</v>
+        <v>121343732</v>
       </c>
       <c r="B50" t="n">
         <v>78609</v>
@@ -6098,13 +6102,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518559</v>
+        <v>518817</v>
       </c>
       <c r="R50" t="n">
-        <v>6995004</v>
+        <v>6994855</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6147,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6170,7 +6174,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121344818</v>
+        <v>121346430</v>
       </c>
       <c r="B51" t="n">
         <v>78609</v>
@@ -6210,10 +6214,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518624</v>
+        <v>518614</v>
       </c>
       <c r="R51" t="n">
-        <v>6995059</v>
+        <v>6994902</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6245,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6255,7 +6259,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6282,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121344731</v>
+        <v>121343160</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6298,37 +6302,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518652</v>
+        <v>518815</v>
       </c>
       <c r="R52" t="n">
-        <v>6994988</v>
+        <v>6994704</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6367,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6394,7 +6398,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121343196</v>
+        <v>121346053</v>
       </c>
       <c r="B53" t="n">
         <v>78609</v>
@@ -6430,14 +6434,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518797</v>
+        <v>518560</v>
       </c>
       <c r="R53" t="n">
-        <v>6994707</v>
+        <v>6995039</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6469,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6479,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6506,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121344213</v>
+        <v>121345960</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6522,37 +6526,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518792</v>
+        <v>518444</v>
       </c>
       <c r="R54" t="n">
-        <v>6994973</v>
+        <v>6995141</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6581,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6591,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,7 +6622,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121346289</v>
+        <v>121345938</v>
       </c>
       <c r="B55" t="n">
         <v>78609</v>
@@ -6654,17 +6658,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518618</v>
+        <v>518387</v>
       </c>
       <c r="R55" t="n">
-        <v>6994929</v>
+        <v>6995152</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6693,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6703,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6730,10 +6734,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121345053</v>
+        <v>121346289</v>
       </c>
       <c r="B56" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6746,34 +6750,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518563</v>
+        <v>518618</v>
       </c>
       <c r="R56" t="n">
-        <v>6995042</v>
+        <v>6994929</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6805,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6815,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6842,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121345960</v>
+        <v>121343253</v>
       </c>
       <c r="B57" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6858,34 +6862,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518444</v>
+        <v>518799</v>
       </c>
       <c r="R57" t="n">
-        <v>6995141</v>
+        <v>6994749</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6917,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6927,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6954,7 +6958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121346074</v>
+        <v>121343468</v>
       </c>
       <c r="B58" t="n">
         <v>78609</v>
@@ -6990,14 +6994,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518583</v>
+        <v>518814</v>
       </c>
       <c r="R58" t="n">
-        <v>6995023</v>
+        <v>6994789</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7029,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7039,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7066,7 +7070,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121346126</v>
+        <v>121343178</v>
       </c>
       <c r="B59" t="n">
         <v>78609</v>
@@ -7102,17 +7106,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518627</v>
+        <v>518814</v>
       </c>
       <c r="R59" t="n">
-        <v>6994984</v>
+        <v>6994717</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7141,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7151,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7178,7 +7182,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121343253</v>
+        <v>121345122</v>
       </c>
       <c r="B60" t="n">
         <v>78609</v>
@@ -7214,17 +7218,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518799</v>
+        <v>518552</v>
       </c>
       <c r="R60" t="n">
-        <v>6994749</v>
+        <v>6994973</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7253,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7263,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7290,7 +7294,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121343178</v>
+        <v>121345918</v>
       </c>
       <c r="B61" t="n">
         <v>78609</v>
@@ -7326,17 +7330,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518814</v>
+        <v>518360</v>
       </c>
       <c r="R61" t="n">
-        <v>6994717</v>
+        <v>6995099</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7365,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7375,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7402,7 +7406,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121343305</v>
+        <v>121344193</v>
       </c>
       <c r="B62" t="n">
         <v>78609</v>
@@ -7438,14 +7442,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518812</v>
+        <v>518808</v>
       </c>
       <c r="R62" t="n">
-        <v>6994779</v>
+        <v>6994956</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7477,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7487,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7514,7 +7518,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121346232</v>
+        <v>121346586</v>
       </c>
       <c r="B63" t="n">
         <v>78609</v>
@@ -7550,14 +7554,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518626</v>
+        <v>518787</v>
       </c>
       <c r="R63" t="n">
-        <v>6994964</v>
+        <v>6994738</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7589,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7599,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7626,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343472</v>
+        <v>121344308</v>
       </c>
       <c r="B64" t="n">
         <v>78609</v>
@@ -7662,17 +7666,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518814</v>
+        <v>518783</v>
       </c>
       <c r="R64" t="n">
-        <v>6994800</v>
+        <v>6994979</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7701,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7711,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7738,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121343207</v>
+        <v>121344213</v>
       </c>
       <c r="B65" t="n">
-        <v>91282</v>
+        <v>78609</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7750,44 +7754,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518808</v>
+        <v>518792</v>
       </c>
       <c r="R65" t="n">
-        <v>6994725</v>
+        <v>6994973</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7816,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7826,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7835,7 +7836,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7966,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121343303</v>
+        <v>121343298</v>
       </c>
       <c r="B67" t="n">
         <v>78609</v>
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518809</v>
+        <v>518812</v>
       </c>
       <c r="R67" t="n">
-        <v>6994765</v>
+        <v>6994775</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8078,7 +8078,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343468</v>
+        <v>121343289</v>
       </c>
       <c r="B68" t="n">
         <v>78609</v>
@@ -8121,10 +8121,10 @@
         <v>518814</v>
       </c>
       <c r="R68" t="n">
-        <v>6994789</v>
+        <v>6994762</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121345085</v>
+        <v>121346126</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518559</v>
+        <v>518627</v>
       </c>
       <c r="R3" t="n">
-        <v>6995004</v>
+        <v>6994984</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121343018</v>
+        <v>121343249</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518813</v>
+        <v>518808</v>
       </c>
       <c r="R4" t="n">
-        <v>6994667</v>
+        <v>6994740</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346613</v>
+        <v>121343305</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518770</v>
+        <v>518812</v>
       </c>
       <c r="R5" t="n">
-        <v>6994702</v>
+        <v>6994779</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344456</v>
+        <v>121344380</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518727</v>
+        <v>518768</v>
       </c>
       <c r="R6" t="n">
-        <v>6994987</v>
+        <v>6994994</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121345064</v>
+        <v>121346430</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1386,14 +1386,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518566</v>
+        <v>518614</v>
       </c>
       <c r="R8" t="n">
-        <v>6995030</v>
+        <v>6994902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343207</v>
+        <v>121343468</v>
       </c>
       <c r="B9" t="n">
-        <v>91282</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,44 +1474,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518808</v>
+        <v>518814</v>
       </c>
       <c r="R9" t="n">
-        <v>6994725</v>
+        <v>6994789</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,7 +1556,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1578,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343809</v>
+        <v>121346620</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1614,14 +1610,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518808</v>
+        <v>518774</v>
       </c>
       <c r="R10" t="n">
-        <v>6994892</v>
+        <v>6994685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343303</v>
+        <v>121345918</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1726,17 +1722,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518809</v>
+        <v>518360</v>
       </c>
       <c r="R11" t="n">
-        <v>6994765</v>
+        <v>6995099</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,7 +1798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343920</v>
+        <v>121343093</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1838,17 +1834,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518807</v>
+        <v>518801</v>
       </c>
       <c r="R12" t="n">
-        <v>6994899</v>
+        <v>6994670</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121343797</v>
+        <v>121346560</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1950,17 +1946,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518812</v>
+        <v>518787</v>
       </c>
       <c r="R13" t="n">
-        <v>6994875</v>
+        <v>6994752</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1995,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121345053</v>
+        <v>121346635</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,37 +2038,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518563</v>
+        <v>518776</v>
       </c>
       <c r="R14" t="n">
-        <v>6995042</v>
+        <v>6994684</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2111,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,7 +2134,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121343524</v>
+        <v>121345073</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2174,17 +2170,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518815</v>
+        <v>518555</v>
       </c>
       <c r="R15" t="n">
-        <v>6994807</v>
+        <v>6995010</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2213,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,7 +2246,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121344796</v>
+        <v>121345972</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2286,17 +2282,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518665</v>
+        <v>518465</v>
       </c>
       <c r="R16" t="n">
-        <v>6995040</v>
+        <v>6995120</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2325,7 +2321,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2335,7 +2331,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345946</v>
+        <v>121345116</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,37 +2374,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518414</v>
+        <v>518559</v>
       </c>
       <c r="R17" t="n">
-        <v>6995151</v>
+        <v>6994969</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2437,7 +2436,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,7 +2446,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,6 +2455,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121345954</v>
+        <v>121346533</v>
       </c>
       <c r="B18" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,34 +2490,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518428</v>
+        <v>518703</v>
       </c>
       <c r="R18" t="n">
-        <v>6995142</v>
+        <v>6994800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,7 +2586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121343092</v>
+        <v>121343229</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518811</v>
+        <v>518808</v>
       </c>
       <c r="R19" t="n">
-        <v>6994686</v>
+        <v>6994725</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121345116</v>
+        <v>121344731</v>
       </c>
       <c r="B20" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,40 +2714,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518559</v>
+        <v>518652</v>
       </c>
       <c r="R20" t="n">
-        <v>6994969</v>
+        <v>6994988</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2776,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2795,7 +2792,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2814,7 +2810,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343249</v>
+        <v>121343524</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2854,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518808</v>
+        <v>518815</v>
       </c>
       <c r="R21" t="n">
-        <v>6994740</v>
+        <v>6994807</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2889,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,7 +2922,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343959</v>
+        <v>121343797</v>
       </c>
       <c r="B22" t="n">
         <v>78609</v>
@@ -2966,10 +2962,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518825</v>
+        <v>518812</v>
       </c>
       <c r="R22" t="n">
-        <v>6994907</v>
+        <v>6994875</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3001,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121344384</v>
+        <v>121343303</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,37 +3050,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518741</v>
+        <v>518809</v>
       </c>
       <c r="R23" t="n">
-        <v>6994995</v>
+        <v>6994765</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,7 +3146,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346126</v>
+        <v>121345064</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -3186,17 +3182,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518627</v>
+        <v>518566</v>
       </c>
       <c r="R24" t="n">
-        <v>6994984</v>
+        <v>6995030</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3225,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,7 +3258,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121344818</v>
+        <v>121343920</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3302,13 +3298,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518624</v>
+        <v>518807</v>
       </c>
       <c r="R25" t="n">
-        <v>6995059</v>
+        <v>6994899</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3337,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346038</v>
+        <v>121343207</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>91282</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,41 +3382,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518544</v>
+        <v>518808</v>
       </c>
       <c r="R26" t="n">
-        <v>6995061</v>
+        <v>6994725</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3449,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3468,6 +3467,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121343137</v>
+        <v>121343732</v>
       </c>
       <c r="B27" t="n">
         <v>78609</v>
@@ -3522,17 +3522,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518823</v>
+        <v>518817</v>
       </c>
       <c r="R27" t="n">
-        <v>6994691</v>
+        <v>6994855</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346620</v>
+        <v>121343022</v>
       </c>
       <c r="B28" t="n">
         <v>78609</v>
@@ -3638,13 +3638,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518774</v>
+        <v>518814</v>
       </c>
       <c r="R28" t="n">
-        <v>6994685</v>
+        <v>6994676</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,7 +3710,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343285</v>
+        <v>121343478</v>
       </c>
       <c r="B29" t="n">
         <v>78609</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518804</v>
+        <v>518834</v>
       </c>
       <c r="R29" t="n">
-        <v>6994760</v>
+        <v>6994815</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,7 +3822,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121343472</v>
+        <v>121343285</v>
       </c>
       <c r="B30" t="n">
         <v>78609</v>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518814</v>
+        <v>518804</v>
       </c>
       <c r="R30" t="n">
-        <v>6994800</v>
+        <v>6994760</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121344999</v>
+        <v>121346038</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3970,17 +3970,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518659</v>
+        <v>518544</v>
       </c>
       <c r="R31" t="n">
-        <v>6995028</v>
+        <v>6995061</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,7 +4046,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346092</v>
+        <v>121346053</v>
       </c>
       <c r="B32" t="n">
         <v>78609</v>
@@ -4082,14 +4082,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518610</v>
+        <v>518560</v>
       </c>
       <c r="R32" t="n">
-        <v>6995000</v>
+        <v>6995039</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121343478</v>
+        <v>121343160</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4198,13 +4198,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518834</v>
+        <v>518815</v>
       </c>
       <c r="R33" t="n">
-        <v>6994815</v>
+        <v>6994704</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,7 +4270,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121343022</v>
+        <v>121343809</v>
       </c>
       <c r="B34" t="n">
         <v>78609</v>
@@ -4306,17 +4306,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518814</v>
+        <v>518808</v>
       </c>
       <c r="R34" t="n">
-        <v>6994676</v>
+        <v>6994892</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,7 +4382,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121343229</v>
+        <v>121346025</v>
       </c>
       <c r="B35" t="n">
         <v>78609</v>
@@ -4418,17 +4418,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518808</v>
+        <v>518519</v>
       </c>
       <c r="R35" t="n">
-        <v>6994725</v>
+        <v>6995085</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346560</v>
+        <v>121346586</v>
       </c>
       <c r="B36" t="n">
         <v>78609</v>
@@ -4537,7 +4537,7 @@
         <v>518787</v>
       </c>
       <c r="R36" t="n">
-        <v>6994752</v>
+        <v>6994738</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346533</v>
+        <v>121346074</v>
       </c>
       <c r="B37" t="n">
         <v>78609</v>
@@ -4642,14 +4642,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518703</v>
+        <v>518583</v>
       </c>
       <c r="R37" t="n">
-        <v>6994800</v>
+        <v>6995023</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,7 +4718,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121343305</v>
+        <v>121343018</v>
       </c>
       <c r="B38" t="n">
         <v>78609</v>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518812</v>
+        <v>518813</v>
       </c>
       <c r="R38" t="n">
-        <v>6994779</v>
+        <v>6994667</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,7 +4830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346232</v>
+        <v>121344213</v>
       </c>
       <c r="B39" t="n">
         <v>78609</v>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518626</v>
+        <v>518792</v>
       </c>
       <c r="R39" t="n">
-        <v>6994964</v>
+        <v>6994973</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121343196</v>
+        <v>121345960</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4958,34 +4958,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518797</v>
+        <v>518444</v>
       </c>
       <c r="R40" t="n">
-        <v>6994707</v>
+        <v>6995141</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,7 +5054,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121343093</v>
+        <v>121343092</v>
       </c>
       <c r="B41" t="n">
         <v>78609</v>
@@ -5094,13 +5094,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518801</v>
+        <v>518811</v>
       </c>
       <c r="R41" t="n">
-        <v>6994670</v>
+        <v>6994686</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,7 +5166,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121346074</v>
+        <v>121345938</v>
       </c>
       <c r="B42" t="n">
         <v>78609</v>
@@ -5202,14 +5202,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518583</v>
+        <v>518387</v>
       </c>
       <c r="R42" t="n">
-        <v>6995023</v>
+        <v>6995152</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5278,7 +5278,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121346635</v>
+        <v>121344456</v>
       </c>
       <c r="B43" t="n">
         <v>78609</v>
@@ -5314,17 +5314,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518776</v>
+        <v>518727</v>
       </c>
       <c r="R43" t="n">
-        <v>6994684</v>
+        <v>6994987</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,7 +5390,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121345073</v>
+        <v>121343178</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -5426,14 +5426,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518555</v>
+        <v>518814</v>
       </c>
       <c r="R44" t="n">
-        <v>6995010</v>
+        <v>6994717</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,7 +5502,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121346025</v>
+        <v>121344818</v>
       </c>
       <c r="B45" t="n">
         <v>78609</v>
@@ -5538,14 +5538,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518519</v>
+        <v>518624</v>
       </c>
       <c r="R45" t="n">
-        <v>6995085</v>
+        <v>6995059</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5614,7 +5614,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121344380</v>
+        <v>121345946</v>
       </c>
       <c r="B46" t="n">
         <v>78609</v>
@@ -5650,17 +5650,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518768</v>
+        <v>518414</v>
       </c>
       <c r="R46" t="n">
-        <v>6994994</v>
+        <v>6995151</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,7 +5726,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121343625</v>
+        <v>121346595</v>
       </c>
       <c r="B47" t="n">
         <v>78609</v>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518819</v>
+        <v>518786</v>
       </c>
       <c r="R47" t="n">
-        <v>6994817</v>
+        <v>6994717</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,7 +5838,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121344731</v>
+        <v>121346613</v>
       </c>
       <c r="B48" t="n">
         <v>78609</v>
@@ -5874,17 +5874,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518652</v>
+        <v>518770</v>
       </c>
       <c r="R48" t="n">
-        <v>6994988</v>
+        <v>6994702</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,7 +5950,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121345972</v>
+        <v>121343289</v>
       </c>
       <c r="B49" t="n">
         <v>78609</v>
@@ -5986,14 +5986,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518465</v>
+        <v>518814</v>
       </c>
       <c r="R49" t="n">
-        <v>6995120</v>
+        <v>6994762</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6062,7 +6062,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121343732</v>
+        <v>121346092</v>
       </c>
       <c r="B50" t="n">
         <v>78609</v>
@@ -6102,13 +6102,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518817</v>
+        <v>518610</v>
       </c>
       <c r="R50" t="n">
-        <v>6994855</v>
+        <v>6995000</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6174,7 +6174,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121346430</v>
+        <v>121345085</v>
       </c>
       <c r="B51" t="n">
         <v>78609</v>
@@ -6214,13 +6214,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518614</v>
+        <v>518559</v>
       </c>
       <c r="R51" t="n">
-        <v>6994902</v>
+        <v>6995004</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6286,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121343160</v>
+        <v>121345122</v>
       </c>
       <c r="B52" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6302,37 +6302,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518815</v>
+        <v>518552</v>
       </c>
       <c r="R52" t="n">
-        <v>6994704</v>
+        <v>6994973</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6398,10 +6398,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121346053</v>
+        <v>121345053</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6414,21 +6414,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6438,10 +6438,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518560</v>
+        <v>518563</v>
       </c>
       <c r="R53" t="n">
-        <v>6995039</v>
+        <v>6995042</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121345960</v>
+        <v>121343253</v>
       </c>
       <c r="B54" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6526,34 +6526,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518444</v>
+        <v>518799</v>
       </c>
       <c r="R54" t="n">
-        <v>6995141</v>
+        <v>6994749</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,7 +6622,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121345938</v>
+        <v>121346232</v>
       </c>
       <c r="B55" t="n">
         <v>78609</v>
@@ -6658,14 +6658,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518387</v>
+        <v>518626</v>
       </c>
       <c r="R55" t="n">
-        <v>6995152</v>
+        <v>6994964</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,7 +6734,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121346289</v>
+        <v>121343959</v>
       </c>
       <c r="B56" t="n">
         <v>78609</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518618</v>
+        <v>518825</v>
       </c>
       <c r="R56" t="n">
-        <v>6994929</v>
+        <v>6994907</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,7 +6846,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343253</v>
+        <v>121343472</v>
       </c>
       <c r="B57" t="n">
         <v>78609</v>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518799</v>
+        <v>518814</v>
       </c>
       <c r="R57" t="n">
-        <v>6994749</v>
+        <v>6994800</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121343468</v>
+        <v>121346289</v>
       </c>
       <c r="B58" t="n">
         <v>78609</v>
@@ -6994,17 +6994,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518814</v>
+        <v>518618</v>
       </c>
       <c r="R58" t="n">
-        <v>6994789</v>
+        <v>6994929</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,7 +7070,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121343178</v>
+        <v>121344308</v>
       </c>
       <c r="B59" t="n">
         <v>78609</v>
@@ -7106,14 +7106,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518814</v>
+        <v>518783</v>
       </c>
       <c r="R59" t="n">
-        <v>6994717</v>
+        <v>6994979</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,7 +7182,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121345122</v>
+        <v>121344193</v>
       </c>
       <c r="B60" t="n">
         <v>78609</v>
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518552</v>
+        <v>518808</v>
       </c>
       <c r="R60" t="n">
-        <v>6994973</v>
+        <v>6994956</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,7 +7294,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121345918</v>
+        <v>121343196</v>
       </c>
       <c r="B61" t="n">
         <v>78609</v>
@@ -7330,14 +7330,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518360</v>
+        <v>518797</v>
       </c>
       <c r="R61" t="n">
-        <v>6995099</v>
+        <v>6994707</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121344193</v>
+        <v>121345954</v>
       </c>
       <c r="B62" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7422,37 +7422,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518808</v>
+        <v>518428</v>
       </c>
       <c r="R62" t="n">
-        <v>6994956</v>
+        <v>6995142</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121346586</v>
+        <v>121344384</v>
       </c>
       <c r="B63" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7534,37 +7534,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518787</v>
+        <v>518741</v>
       </c>
       <c r="R63" t="n">
-        <v>6994738</v>
+        <v>6994995</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121344308</v>
+        <v>121343625</v>
       </c>
       <c r="B64" t="n">
         <v>78609</v>
@@ -7666,17 +7666,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518783</v>
+        <v>518819</v>
       </c>
       <c r="R64" t="n">
-        <v>6994979</v>
+        <v>6994817</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,7 +7742,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121344213</v>
+        <v>121344999</v>
       </c>
       <c r="B65" t="n">
         <v>78609</v>
@@ -7782,13 +7782,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518792</v>
+        <v>518659</v>
       </c>
       <c r="R65" t="n">
-        <v>6994973</v>
+        <v>6995028</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,7 +7854,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121346595</v>
+        <v>121343298</v>
       </c>
       <c r="B66" t="n">
         <v>78609</v>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518786</v>
+        <v>518812</v>
       </c>
       <c r="R66" t="n">
-        <v>6994717</v>
+        <v>6994775</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121343298</v>
+        <v>121343137</v>
       </c>
       <c r="B67" t="n">
         <v>78609</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518812</v>
+        <v>518823</v>
       </c>
       <c r="R67" t="n">
-        <v>6994775</v>
+        <v>6994691</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343289</v>
+        <v>121344796</v>
       </c>
       <c r="B68" t="n">
         <v>78609</v>
@@ -8114,17 +8114,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518814</v>
+        <v>518665</v>
       </c>
       <c r="R68" t="n">
-        <v>6994762</v>
+        <v>6995040</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346126</v>
+        <v>121344999</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518627</v>
+        <v>518659</v>
       </c>
       <c r="R3" t="n">
-        <v>6994984</v>
+        <v>6995028</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121343249</v>
+        <v>121343137</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518808</v>
+        <v>518823</v>
       </c>
       <c r="R4" t="n">
-        <v>6994740</v>
+        <v>6994691</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343305</v>
+        <v>121346586</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518812</v>
+        <v>518787</v>
       </c>
       <c r="R5" t="n">
-        <v>6994779</v>
+        <v>6994738</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121344380</v>
+        <v>121343478</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1162,17 +1162,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518768</v>
+        <v>518834</v>
       </c>
       <c r="R6" t="n">
-        <v>6994994</v>
+        <v>6994815</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346005</v>
+        <v>121344213</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1274,14 +1274,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518483</v>
+        <v>518792</v>
       </c>
       <c r="R7" t="n">
-        <v>6995124</v>
+        <v>6994973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346430</v>
+        <v>121343472</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1386,17 +1386,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518614</v>
+        <v>518814</v>
       </c>
       <c r="R8" t="n">
-        <v>6994902</v>
+        <v>6994800</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,7 +1462,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343468</v>
+        <v>121343092</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518814</v>
+        <v>518811</v>
       </c>
       <c r="R9" t="n">
-        <v>6994789</v>
+        <v>6994686</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346620</v>
+        <v>121343298</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518774</v>
+        <v>518812</v>
       </c>
       <c r="R10" t="n">
-        <v>6994685</v>
+        <v>6994775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121345918</v>
+        <v>121346289</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1722,14 +1722,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518360</v>
+        <v>518618</v>
       </c>
       <c r="R11" t="n">
-        <v>6995099</v>
+        <v>6994929</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,7 +1798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343093</v>
+        <v>121344796</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1834,17 +1834,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518801</v>
+        <v>518665</v>
       </c>
       <c r="R12" t="n">
-        <v>6994670</v>
+        <v>6995040</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346560</v>
+        <v>121345116</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,37 +1926,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518787</v>
+        <v>518559</v>
       </c>
       <c r="R13" t="n">
-        <v>6994752</v>
+        <v>6994969</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1988,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +1998,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,6 +2007,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2022,7 +2026,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346635</v>
+        <v>121343289</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2062,13 +2066,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518776</v>
+        <v>518814</v>
       </c>
       <c r="R14" t="n">
-        <v>6994684</v>
+        <v>6994762</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,7 +2138,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121345073</v>
+        <v>121343468</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2170,14 +2174,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518555</v>
+        <v>518814</v>
       </c>
       <c r="R15" t="n">
-        <v>6995010</v>
+        <v>6994789</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,7 +2213,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2223,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345972</v>
+        <v>121345053</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,21 +2266,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2286,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518465</v>
+        <v>518563</v>
       </c>
       <c r="R16" t="n">
-        <v>6995120</v>
+        <v>6995042</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2321,7 +2325,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,7 +2335,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121345116</v>
+        <v>121344818</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2374,40 +2378,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518559</v>
+        <v>518624</v>
       </c>
       <c r="R17" t="n">
-        <v>6994969</v>
+        <v>6995059</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,7 +2447,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,7 +2456,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346533</v>
+        <v>121343207</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>91282</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,41 +2486,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518703</v>
+        <v>518808</v>
       </c>
       <c r="R18" t="n">
-        <v>6994800</v>
+        <v>6994725</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2549,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,6 +2571,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2586,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121343229</v>
+        <v>121345960</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2602,34 +2606,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518808</v>
+        <v>518444</v>
       </c>
       <c r="R19" t="n">
-        <v>6994725</v>
+        <v>6995141</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2661,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,7 +2702,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121344731</v>
+        <v>121343303</v>
       </c>
       <c r="B20" t="n">
         <v>78609</v>
@@ -2734,14 +2738,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518652</v>
+        <v>518809</v>
       </c>
       <c r="R20" t="n">
-        <v>6994988</v>
+        <v>6994765</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,7 +2814,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343524</v>
+        <v>121344731</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2846,17 +2850,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518815</v>
+        <v>518652</v>
       </c>
       <c r="R21" t="n">
-        <v>6994807</v>
+        <v>6994988</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,7 +2926,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343797</v>
+        <v>121345938</v>
       </c>
       <c r="B22" t="n">
         <v>78609</v>
@@ -2958,17 +2962,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518812</v>
+        <v>518387</v>
       </c>
       <c r="R22" t="n">
-        <v>6994875</v>
+        <v>6995152</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,7 +3038,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121343303</v>
+        <v>121346430</v>
       </c>
       <c r="B23" t="n">
         <v>78609</v>
@@ -3070,14 +3074,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518809</v>
+        <v>518614</v>
       </c>
       <c r="R23" t="n">
-        <v>6994765</v>
+        <v>6994902</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3146,7 +3150,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121345064</v>
+        <v>121345073</v>
       </c>
       <c r="B24" t="n">
         <v>78609</v>
@@ -3186,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518566</v>
+        <v>518555</v>
       </c>
       <c r="R24" t="n">
-        <v>6995030</v>
+        <v>6995010</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3221,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3231,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,7 +3262,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121343920</v>
+        <v>121346038</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3294,17 +3298,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518807</v>
+        <v>518544</v>
       </c>
       <c r="R25" t="n">
-        <v>6994899</v>
+        <v>6995061</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3343,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3370,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121343207</v>
+        <v>121346620</v>
       </c>
       <c r="B26" t="n">
-        <v>91282</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3382,44 +3386,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518808</v>
+        <v>518774</v>
       </c>
       <c r="R26" t="n">
-        <v>6994725</v>
+        <v>6994685</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3448,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3467,7 +3468,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121343732</v>
+        <v>121346635</v>
       </c>
       <c r="B27" t="n">
         <v>78609</v>
@@ -3522,14 +3522,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518817</v>
+        <v>518776</v>
       </c>
       <c r="R27" t="n">
-        <v>6994855</v>
+        <v>6994684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121343022</v>
+        <v>121343018</v>
       </c>
       <c r="B28" t="n">
         <v>78609</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518814</v>
+        <v>518813</v>
       </c>
       <c r="R28" t="n">
-        <v>6994676</v>
+        <v>6994667</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,7 +3710,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343478</v>
+        <v>121343229</v>
       </c>
       <c r="B29" t="n">
         <v>78609</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518834</v>
+        <v>518808</v>
       </c>
       <c r="R29" t="n">
-        <v>6994815</v>
+        <v>6994725</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,7 +3822,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121343285</v>
+        <v>121346074</v>
       </c>
       <c r="B30" t="n">
         <v>78609</v>
@@ -3858,17 +3858,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518804</v>
+        <v>518583</v>
       </c>
       <c r="R30" t="n">
-        <v>6994760</v>
+        <v>6995023</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346038</v>
+        <v>121345122</v>
       </c>
       <c r="B31" t="n">
         <v>78609</v>
@@ -3970,14 +3970,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518544</v>
+        <v>518552</v>
       </c>
       <c r="R31" t="n">
-        <v>6995061</v>
+        <v>6994973</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,7 +4046,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346053</v>
+        <v>121343625</v>
       </c>
       <c r="B32" t="n">
         <v>78609</v>
@@ -4082,14 +4082,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518560</v>
+        <v>518819</v>
       </c>
       <c r="R32" t="n">
-        <v>6995039</v>
+        <v>6994817</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121343160</v>
+        <v>121344308</v>
       </c>
       <c r="B33" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,37 +4174,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518815</v>
+        <v>518783</v>
       </c>
       <c r="R33" t="n">
-        <v>6994704</v>
+        <v>6994979</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,7 +4270,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121343809</v>
+        <v>121343093</v>
       </c>
       <c r="B34" t="n">
         <v>78609</v>
@@ -4306,17 +4306,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518808</v>
+        <v>518801</v>
       </c>
       <c r="R34" t="n">
-        <v>6994892</v>
+        <v>6994670</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,7 +4382,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346025</v>
+        <v>121346092</v>
       </c>
       <c r="B35" t="n">
         <v>78609</v>
@@ -4418,17 +4418,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518519</v>
+        <v>518610</v>
       </c>
       <c r="R35" t="n">
-        <v>6995085</v>
+        <v>6995000</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346586</v>
+        <v>121343253</v>
       </c>
       <c r="B36" t="n">
         <v>78609</v>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518787</v>
+        <v>518799</v>
       </c>
       <c r="R36" t="n">
-        <v>6994738</v>
+        <v>6994749</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346074</v>
+        <v>121343285</v>
       </c>
       <c r="B37" t="n">
         <v>78609</v>
@@ -4642,17 +4642,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518583</v>
+        <v>518804</v>
       </c>
       <c r="R37" t="n">
-        <v>6995023</v>
+        <v>6994760</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,7 +4718,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121343018</v>
+        <v>121344456</v>
       </c>
       <c r="B38" t="n">
         <v>78609</v>
@@ -4754,14 +4754,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518813</v>
+        <v>518727</v>
       </c>
       <c r="R38" t="n">
-        <v>6994667</v>
+        <v>6994987</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,7 +4830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121344213</v>
+        <v>121345972</v>
       </c>
       <c r="B39" t="n">
         <v>78609</v>
@@ -4866,17 +4866,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518792</v>
+        <v>518465</v>
       </c>
       <c r="R39" t="n">
-        <v>6994973</v>
+        <v>6995120</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121345960</v>
+        <v>121343732</v>
       </c>
       <c r="B40" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4958,37 +4958,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518444</v>
+        <v>518817</v>
       </c>
       <c r="R40" t="n">
-        <v>6995141</v>
+        <v>6994855</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,7 +5054,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121343092</v>
+        <v>121343809</v>
       </c>
       <c r="B41" t="n">
         <v>78609</v>
@@ -5090,17 +5090,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518811</v>
+        <v>518808</v>
       </c>
       <c r="R41" t="n">
-        <v>6994686</v>
+        <v>6994892</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,10 +5166,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121345938</v>
+        <v>121345954</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5182,21 +5182,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518387</v>
+        <v>518428</v>
       </c>
       <c r="R42" t="n">
-        <v>6995152</v>
+        <v>6995142</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5278,7 +5278,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121344456</v>
+        <v>121346053</v>
       </c>
       <c r="B43" t="n">
         <v>78609</v>
@@ -5314,14 +5314,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518727</v>
+        <v>518560</v>
       </c>
       <c r="R43" t="n">
-        <v>6994987</v>
+        <v>6995039</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,7 +5390,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121343178</v>
+        <v>121346595</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518814</v>
+        <v>518786</v>
       </c>
       <c r="R44" t="n">
         <v>6994717</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,7 +5502,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121344818</v>
+        <v>121344380</v>
       </c>
       <c r="B45" t="n">
         <v>78609</v>
@@ -5542,13 +5542,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518624</v>
+        <v>518768</v>
       </c>
       <c r="R45" t="n">
-        <v>6995059</v>
+        <v>6994994</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5614,7 +5614,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121345946</v>
+        <v>121346005</v>
       </c>
       <c r="B46" t="n">
         <v>78609</v>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518414</v>
+        <v>518483</v>
       </c>
       <c r="R46" t="n">
-        <v>6995151</v>
+        <v>6995124</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,7 +5726,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121346595</v>
+        <v>121343920</v>
       </c>
       <c r="B47" t="n">
         <v>78609</v>
@@ -5762,17 +5762,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518786</v>
+        <v>518807</v>
       </c>
       <c r="R47" t="n">
-        <v>6994717</v>
+        <v>6994899</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,7 +5838,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121346613</v>
+        <v>121345918</v>
       </c>
       <c r="B48" t="n">
         <v>78609</v>
@@ -5874,14 +5874,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518770</v>
+        <v>518360</v>
       </c>
       <c r="R48" t="n">
-        <v>6994702</v>
+        <v>6995099</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,7 +5950,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121343289</v>
+        <v>121344193</v>
       </c>
       <c r="B49" t="n">
         <v>78609</v>
@@ -5986,14 +5986,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518814</v>
+        <v>518808</v>
       </c>
       <c r="R49" t="n">
-        <v>6994762</v>
+        <v>6994956</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6062,7 +6062,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121346092</v>
+        <v>121343196</v>
       </c>
       <c r="B50" t="n">
         <v>78609</v>
@@ -6098,14 +6098,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518610</v>
+        <v>518797</v>
       </c>
       <c r="R50" t="n">
-        <v>6995000</v>
+        <v>6994707</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6174,7 +6174,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121345085</v>
+        <v>121346560</v>
       </c>
       <c r="B51" t="n">
         <v>78609</v>
@@ -6210,17 +6210,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518559</v>
+        <v>518787</v>
       </c>
       <c r="R51" t="n">
-        <v>6995004</v>
+        <v>6994752</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6286,7 +6286,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121345122</v>
+        <v>121346126</v>
       </c>
       <c r="B52" t="n">
         <v>78609</v>
@@ -6326,13 +6326,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518552</v>
+        <v>518627</v>
       </c>
       <c r="R52" t="n">
-        <v>6994973</v>
+        <v>6994984</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6398,10 +6398,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121345053</v>
+        <v>121343178</v>
       </c>
       <c r="B53" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6414,37 +6414,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518563</v>
+        <v>518814</v>
       </c>
       <c r="R53" t="n">
-        <v>6995042</v>
+        <v>6994717</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,7 +6510,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121343253</v>
+        <v>121343797</v>
       </c>
       <c r="B54" t="n">
         <v>78609</v>
@@ -6546,14 +6546,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518799</v>
+        <v>518812</v>
       </c>
       <c r="R54" t="n">
-        <v>6994749</v>
+        <v>6994875</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,7 +6622,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121346232</v>
+        <v>121346613</v>
       </c>
       <c r="B55" t="n">
         <v>78609</v>
@@ -6658,17 +6658,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518626</v>
+        <v>518770</v>
       </c>
       <c r="R55" t="n">
-        <v>6994964</v>
+        <v>6994702</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,7 +6734,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121343959</v>
+        <v>121345946</v>
       </c>
       <c r="B56" t="n">
         <v>78609</v>
@@ -6770,17 +6770,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518825</v>
+        <v>518414</v>
       </c>
       <c r="R56" t="n">
-        <v>6994907</v>
+        <v>6995151</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,7 +6846,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121343472</v>
+        <v>121345064</v>
       </c>
       <c r="B57" t="n">
         <v>78609</v>
@@ -6882,17 +6882,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518814</v>
+        <v>518566</v>
       </c>
       <c r="R57" t="n">
-        <v>6994800</v>
+        <v>6995030</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121346289</v>
+        <v>121345085</v>
       </c>
       <c r="B58" t="n">
         <v>78609</v>
@@ -6998,10 +6998,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518618</v>
+        <v>518559</v>
       </c>
       <c r="R58" t="n">
-        <v>6994929</v>
+        <v>6995004</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,7 +7070,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121344308</v>
+        <v>121346232</v>
       </c>
       <c r="B59" t="n">
         <v>78609</v>
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518783</v>
+        <v>518626</v>
       </c>
       <c r="R59" t="n">
-        <v>6994979</v>
+        <v>6994964</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121344193</v>
+        <v>121343160</v>
       </c>
       <c r="B60" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7198,34 +7198,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518808</v>
+        <v>518815</v>
       </c>
       <c r="R60" t="n">
-        <v>6994956</v>
+        <v>6994704</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,7 +7294,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121343196</v>
+        <v>121346025</v>
       </c>
       <c r="B61" t="n">
         <v>78609</v>
@@ -7330,17 +7330,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518797</v>
+        <v>518519</v>
       </c>
       <c r="R61" t="n">
-        <v>6994707</v>
+        <v>6995085</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121345954</v>
+        <v>121346533</v>
       </c>
       <c r="B62" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7422,34 +7422,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518428</v>
+        <v>518703</v>
       </c>
       <c r="R62" t="n">
-        <v>6995142</v>
+        <v>6994800</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121344384</v>
+        <v>121343249</v>
       </c>
       <c r="B63" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7534,37 +7534,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518741</v>
+        <v>518808</v>
       </c>
       <c r="R63" t="n">
-        <v>6994995</v>
+        <v>6994740</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343625</v>
+        <v>121343305</v>
       </c>
       <c r="B64" t="n">
         <v>78609</v>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518819</v>
+        <v>518812</v>
       </c>
       <c r="R64" t="n">
-        <v>6994817</v>
+        <v>6994779</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121344999</v>
+        <v>121344384</v>
       </c>
       <c r="B65" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7758,21 +7758,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518659</v>
+        <v>518741</v>
       </c>
       <c r="R65" t="n">
-        <v>6995028</v>
+        <v>6994995</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,7 +7854,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121343298</v>
+        <v>121343022</v>
       </c>
       <c r="B66" t="n">
         <v>78609</v>
@@ -7894,13 +7894,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518812</v>
+        <v>518814</v>
       </c>
       <c r="R66" t="n">
-        <v>6994775</v>
+        <v>6994676</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121343137</v>
+        <v>121343959</v>
       </c>
       <c r="B67" t="n">
         <v>78609</v>
@@ -8002,14 +8002,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518823</v>
+        <v>518825</v>
       </c>
       <c r="R67" t="n">
-        <v>6994691</v>
+        <v>6994907</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121344796</v>
+        <v>121343524</v>
       </c>
       <c r="B68" t="n">
         <v>78609</v>
@@ -8114,17 +8114,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518665</v>
+        <v>518815</v>
       </c>
       <c r="R68" t="n">
-        <v>6995040</v>
+        <v>6994807</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -1462,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343092</v>
+        <v>121345116</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,34 +1478,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518811</v>
+        <v>518559</v>
       </c>
       <c r="R9" t="n">
-        <v>6994686</v>
+        <v>6994969</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1537,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1550,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,6 +1559,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1574,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343298</v>
+        <v>121343092</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1614,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518812</v>
+        <v>518811</v>
       </c>
       <c r="R10" t="n">
-        <v>6994775</v>
+        <v>6994686</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346289</v>
+        <v>121343298</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1722,17 +1726,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518618</v>
+        <v>518812</v>
       </c>
       <c r="R11" t="n">
-        <v>6994929</v>
+        <v>6994775</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121344796</v>
+        <v>121346289</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1838,13 +1842,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518665</v>
+        <v>518618</v>
       </c>
       <c r="R12" t="n">
-        <v>6995040</v>
+        <v>6994929</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345116</v>
+        <v>121344796</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,40 +1930,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518559</v>
+        <v>518665</v>
       </c>
       <c r="R13" t="n">
-        <v>6994969</v>
+        <v>6995040</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,7 +2008,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121343285</v>
+        <v>121344456</v>
       </c>
       <c r="B37" t="n">
         <v>78609</v>
@@ -4642,14 +4642,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518804</v>
+        <v>518727</v>
       </c>
       <c r="R37" t="n">
-        <v>6994760</v>
+        <v>6994987</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,7 +4718,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121344456</v>
+        <v>121343285</v>
       </c>
       <c r="B38" t="n">
         <v>78609</v>
@@ -4754,14 +4754,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518727</v>
+        <v>518804</v>
       </c>
       <c r="R38" t="n">
-        <v>6994987</v>
+        <v>6994760</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6398,7 +6398,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121343178</v>
+        <v>121343797</v>
       </c>
       <c r="B53" t="n">
         <v>78609</v>
@@ -6434,17 +6434,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518814</v>
+        <v>518812</v>
       </c>
       <c r="R53" t="n">
-        <v>6994717</v>
+        <v>6994875</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,7 +6510,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121343797</v>
+        <v>121343178</v>
       </c>
       <c r="B54" t="n">
         <v>78609</v>
@@ -6546,17 +6546,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518812</v>
+        <v>518814</v>
       </c>
       <c r="R54" t="n">
-        <v>6994875</v>
+        <v>6994717</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6958,7 +6958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121345085</v>
+        <v>121346232</v>
       </c>
       <c r="B58" t="n">
         <v>78609</v>
@@ -6998,13 +6998,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518559</v>
+        <v>518626</v>
       </c>
       <c r="R58" t="n">
-        <v>6995004</v>
+        <v>6994964</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,7 +7070,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121346232</v>
+        <v>121345085</v>
       </c>
       <c r="B59" t="n">
         <v>78609</v>
@@ -7110,13 +7110,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518626</v>
+        <v>518559</v>
       </c>
       <c r="R59" t="n">
-        <v>6994964</v>
+        <v>6995004</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7406,7 +7406,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121346533</v>
+        <v>121343305</v>
       </c>
       <c r="B62" t="n">
         <v>78609</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518703</v>
+        <v>518812</v>
       </c>
       <c r="R62" t="n">
-        <v>6994800</v>
+        <v>6994779</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,7 +7518,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121343249</v>
+        <v>121346533</v>
       </c>
       <c r="B63" t="n">
         <v>78609</v>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518808</v>
+        <v>518703</v>
       </c>
       <c r="R63" t="n">
-        <v>6994740</v>
+        <v>6994800</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343305</v>
+        <v>121343249</v>
       </c>
       <c r="B64" t="n">
         <v>78609</v>
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518812</v>
+        <v>518808</v>
       </c>
       <c r="R64" t="n">
-        <v>6994779</v>
+        <v>6994740</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -1462,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121345116</v>
+        <v>121343092</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,37 +1478,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518559</v>
+        <v>518811</v>
       </c>
       <c r="R9" t="n">
-        <v>6994969</v>
+        <v>6994686</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1540,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,7 +1556,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1578,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343092</v>
+        <v>121343298</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1618,13 +1614,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518811</v>
+        <v>518812</v>
       </c>
       <c r="R10" t="n">
-        <v>6994686</v>
+        <v>6994775</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343298</v>
+        <v>121346289</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1726,17 +1722,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518812</v>
+        <v>518618</v>
       </c>
       <c r="R11" t="n">
-        <v>6994775</v>
+        <v>6994929</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,7 +1798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346289</v>
+        <v>121344796</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1842,13 +1838,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518618</v>
+        <v>518665</v>
       </c>
       <c r="R12" t="n">
-        <v>6994929</v>
+        <v>6995040</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121344796</v>
+        <v>121345116</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,37 +1926,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518665</v>
+        <v>518559</v>
       </c>
       <c r="R13" t="n">
-        <v>6995040</v>
+        <v>6994969</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +1988,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,7 +1998,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,6 +2007,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346038</v>
+        <v>121346074</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3298,14 +3298,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518544</v>
+        <v>518583</v>
       </c>
       <c r="R25" t="n">
-        <v>6995061</v>
+        <v>6995023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,7 +3374,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346620</v>
+        <v>121346038</v>
       </c>
       <c r="B26" t="n">
         <v>78609</v>
@@ -3410,14 +3410,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518774</v>
+        <v>518544</v>
       </c>
       <c r="R26" t="n">
-        <v>6994685</v>
+        <v>6995061</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,7 +3486,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346635</v>
+        <v>121346620</v>
       </c>
       <c r="B27" t="n">
         <v>78609</v>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518776</v>
+        <v>518774</v>
       </c>
       <c r="R27" t="n">
-        <v>6994684</v>
+        <v>6994685</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121343018</v>
+        <v>121346635</v>
       </c>
       <c r="B28" t="n">
         <v>78609</v>
@@ -3638,13 +3638,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518813</v>
+        <v>518776</v>
       </c>
       <c r="R28" t="n">
-        <v>6994667</v>
+        <v>6994684</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,7 +3710,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343229</v>
+        <v>121343018</v>
       </c>
       <c r="B29" t="n">
         <v>78609</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518808</v>
+        <v>518813</v>
       </c>
       <c r="R29" t="n">
-        <v>6994725</v>
+        <v>6994667</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,7 +3822,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121346074</v>
+        <v>121343229</v>
       </c>
       <c r="B30" t="n">
         <v>78609</v>
@@ -3858,17 +3858,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518583</v>
+        <v>518808</v>
       </c>
       <c r="R30" t="n">
-        <v>6995023</v>
+        <v>6994725</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4606,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121344456</v>
+        <v>121343285</v>
       </c>
       <c r="B37" t="n">
         <v>78609</v>
@@ -4642,14 +4642,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518727</v>
+        <v>518804</v>
       </c>
       <c r="R37" t="n">
-        <v>6994987</v>
+        <v>6994760</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,7 +4718,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121343285</v>
+        <v>121344456</v>
       </c>
       <c r="B38" t="n">
         <v>78609</v>
@@ -4754,14 +4754,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518804</v>
+        <v>518727</v>
       </c>
       <c r="R38" t="n">
-        <v>6994760</v>
+        <v>6994987</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6398,7 +6398,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121343797</v>
+        <v>121343178</v>
       </c>
       <c r="B53" t="n">
         <v>78609</v>
@@ -6434,17 +6434,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518812</v>
+        <v>518814</v>
       </c>
       <c r="R53" t="n">
-        <v>6994875</v>
+        <v>6994717</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,7 +6510,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121343178</v>
+        <v>121343797</v>
       </c>
       <c r="B54" t="n">
         <v>78609</v>
@@ -6546,17 +6546,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518814</v>
+        <v>518812</v>
       </c>
       <c r="R54" t="n">
-        <v>6994717</v>
+        <v>6994875</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7406,7 +7406,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121343305</v>
+        <v>121346533</v>
       </c>
       <c r="B62" t="n">
         <v>78609</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518812</v>
+        <v>518703</v>
       </c>
       <c r="R62" t="n">
-        <v>6994779</v>
+        <v>6994800</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,7 +7518,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121346533</v>
+        <v>121343249</v>
       </c>
       <c r="B63" t="n">
         <v>78609</v>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518703</v>
+        <v>518808</v>
       </c>
       <c r="R63" t="n">
-        <v>6994800</v>
+        <v>6994740</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,7 +7630,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343249</v>
+        <v>121343305</v>
       </c>
       <c r="B64" t="n">
         <v>78609</v>
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518808</v>
+        <v>518812</v>
       </c>
       <c r="R64" t="n">
-        <v>6994740</v>
+        <v>6994779</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121344999</v>
+        <v>121343797</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518659</v>
+        <v>518812</v>
       </c>
       <c r="R3" t="n">
-        <v>6995028</v>
+        <v>6994875</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121343137</v>
+        <v>121345116</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +918,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518823</v>
+        <v>518559</v>
       </c>
       <c r="R4" t="n">
-        <v>6994691</v>
+        <v>6994969</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -977,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,6 +999,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346586</v>
+        <v>121344456</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,17 +1054,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518787</v>
+        <v>518727</v>
       </c>
       <c r="R5" t="n">
-        <v>6994738</v>
+        <v>6994987</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343478</v>
+        <v>121344731</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,14 +1166,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518834</v>
+        <v>518652</v>
       </c>
       <c r="R6" t="n">
-        <v>6994815</v>
+        <v>6994988</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121344213</v>
+        <v>121344308</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518792</v>
+        <v>518783</v>
       </c>
       <c r="R7" t="n">
-        <v>6994973</v>
+        <v>6994979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343472</v>
+        <v>121345085</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,14 +1390,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518814</v>
+        <v>518559</v>
       </c>
       <c r="R8" t="n">
-        <v>6994800</v>
+        <v>6995004</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1425,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343092</v>
+        <v>121343959</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,14 +1502,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518811</v>
+        <v>518825</v>
       </c>
       <c r="R9" t="n">
-        <v>6994686</v>
+        <v>6994907</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1537,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343298</v>
+        <v>121346430</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,14 +1614,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518812</v>
+        <v>518614</v>
       </c>
       <c r="R10" t="n">
-        <v>6994775</v>
+        <v>6994902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346289</v>
+        <v>121344193</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518618</v>
+        <v>518808</v>
       </c>
       <c r="R11" t="n">
-        <v>6994929</v>
+        <v>6994956</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1761,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121344796</v>
+        <v>121345972</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,17 +1838,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518665</v>
+        <v>518465</v>
       </c>
       <c r="R12" t="n">
-        <v>6995040</v>
+        <v>6995120</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1887,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121345116</v>
+        <v>121344380</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,40 +1930,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518559</v>
+        <v>518768</v>
       </c>
       <c r="R13" t="n">
-        <v>6994969</v>
+        <v>6994994</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,7 +2008,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121343289</v>
+        <v>121346074</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,17 +2062,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518814</v>
+        <v>518583</v>
       </c>
       <c r="R14" t="n">
-        <v>6994762</v>
+        <v>6995023</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121343468</v>
+        <v>121343472</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         <v>518814</v>
       </c>
       <c r="R15" t="n">
-        <v>6994789</v>
+        <v>6994800</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121345053</v>
+        <v>121343524</v>
       </c>
       <c r="B16" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,34 +2266,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518563</v>
+        <v>518815</v>
       </c>
       <c r="R16" t="n">
-        <v>6995042</v>
+        <v>6994807</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121344818</v>
+        <v>121343468</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,14 +2398,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518624</v>
+        <v>518814</v>
       </c>
       <c r="R17" t="n">
-        <v>6995059</v>
+        <v>6994789</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121343207</v>
+        <v>121346289</v>
       </c>
       <c r="B18" t="n">
-        <v>91282</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,41 +2486,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518808</v>
+        <v>518618</v>
       </c>
       <c r="R18" t="n">
-        <v>6994725</v>
+        <v>6994929</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2552,7 +2549,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2559,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,7 +2568,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2590,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121345960</v>
+        <v>121343018</v>
       </c>
       <c r="B19" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2606,34 +2602,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518444</v>
+        <v>518813</v>
       </c>
       <c r="R19" t="n">
-        <v>6995141</v>
+        <v>6994667</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2665,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,10 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121343303</v>
+        <v>121343920</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,17 +2734,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518809</v>
+        <v>518807</v>
       </c>
       <c r="R20" t="n">
-        <v>6994765</v>
+        <v>6994899</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2777,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121344731</v>
+        <v>121343732</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2854,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518652</v>
+        <v>518817</v>
       </c>
       <c r="R21" t="n">
-        <v>6994988</v>
+        <v>6994855</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2922,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121345938</v>
+        <v>121346053</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,13 +2962,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518387</v>
+        <v>518560</v>
       </c>
       <c r="R22" t="n">
-        <v>6995152</v>
+        <v>6995039</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3034,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346430</v>
+        <v>121343022</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3074,17 +3070,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518614</v>
+        <v>518814</v>
       </c>
       <c r="R23" t="n">
-        <v>6994902</v>
+        <v>6994676</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121345073</v>
+        <v>121346126</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3186,17 +3182,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518555</v>
+        <v>518627</v>
       </c>
       <c r="R24" t="n">
-        <v>6995010</v>
+        <v>6994984</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3225,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,10 +3258,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346074</v>
+        <v>121343207</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>91290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3274,41 +3270,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518583</v>
+        <v>518808</v>
       </c>
       <c r="R25" t="n">
-        <v>6995023</v>
+        <v>6994725</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3337,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,6 +3355,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3374,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346038</v>
+        <v>121343298</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3410,14 +3410,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518544</v>
+        <v>518812</v>
       </c>
       <c r="R26" t="n">
-        <v>6995061</v>
+        <v>6994775</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346620</v>
+        <v>121343249</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518774</v>
+        <v>518808</v>
       </c>
       <c r="R27" t="n">
-        <v>6994685</v>
+        <v>6994740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,10 +3598,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346635</v>
+        <v>121346092</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3634,17 +3634,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518776</v>
+        <v>518610</v>
       </c>
       <c r="R28" t="n">
-        <v>6994684</v>
+        <v>6995000</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121343018</v>
+        <v>121343093</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518813</v>
+        <v>518801</v>
       </c>
       <c r="R29" t="n">
-        <v>6994667</v>
+        <v>6994670</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,10 +3822,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121343229</v>
+        <v>121345946</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,17 +3858,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518808</v>
+        <v>518414</v>
       </c>
       <c r="R30" t="n">
-        <v>6994725</v>
+        <v>6995151</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121345122</v>
+        <v>121346533</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3970,14 +3970,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518552</v>
+        <v>518703</v>
       </c>
       <c r="R31" t="n">
-        <v>6994973</v>
+        <v>6994800</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121343625</v>
+        <v>121343303</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4086,13 +4086,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518819</v>
+        <v>518809</v>
       </c>
       <c r="R32" t="n">
-        <v>6994817</v>
+        <v>6994765</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121344308</v>
+        <v>121343160</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,37 +4174,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518783</v>
+        <v>518815</v>
       </c>
       <c r="R33" t="n">
-        <v>6994979</v>
+        <v>6994704</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,10 +4270,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121343093</v>
+        <v>121343178</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518801</v>
+        <v>518814</v>
       </c>
       <c r="R34" t="n">
-        <v>6994670</v>
+        <v>6994717</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346092</v>
+        <v>121345073</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4418,17 +4418,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518610</v>
+        <v>518555</v>
       </c>
       <c r="R35" t="n">
-        <v>6995000</v>
+        <v>6995010</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121343253</v>
+        <v>121343625</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518799</v>
+        <v>518819</v>
       </c>
       <c r="R36" t="n">
-        <v>6994749</v>
+        <v>6994817</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,10 +4606,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121343285</v>
+        <v>121343289</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518804</v>
+        <v>518814</v>
       </c>
       <c r="R37" t="n">
-        <v>6994760</v>
+        <v>6994762</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,10 +4718,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121344456</v>
+        <v>121346635</v>
       </c>
       <c r="B38" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4754,17 +4754,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518727</v>
+        <v>518776</v>
       </c>
       <c r="R38" t="n">
-        <v>6994987</v>
+        <v>6994684</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,10 +4830,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121345972</v>
+        <v>121343196</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4866,14 +4866,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518465</v>
+        <v>518797</v>
       </c>
       <c r="R39" t="n">
-        <v>6995120</v>
+        <v>6994707</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121343732</v>
+        <v>121346232</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518817</v>
+        <v>518626</v>
       </c>
       <c r="R40" t="n">
-        <v>6994855</v>
+        <v>6994964</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5054,10 +5054,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121343809</v>
+        <v>121343253</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5090,17 +5090,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518808</v>
+        <v>518799</v>
       </c>
       <c r="R41" t="n">
-        <v>6994892</v>
+        <v>6994749</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,10 +5166,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121345954</v>
+        <v>121344213</v>
       </c>
       <c r="B42" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5182,34 +5182,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518428</v>
+        <v>518792</v>
       </c>
       <c r="R42" t="n">
-        <v>6995142</v>
+        <v>6994973</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121346053</v>
+        <v>121343137</v>
       </c>
       <c r="B43" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5314,14 +5314,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518560</v>
+        <v>518823</v>
       </c>
       <c r="R43" t="n">
-        <v>6995039</v>
+        <v>6994691</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121346595</v>
+        <v>121346586</v>
       </c>
       <c r="B44" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518786</v>
+        <v>518787</v>
       </c>
       <c r="R44" t="n">
-        <v>6994717</v>
+        <v>6994738</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121344380</v>
+        <v>121346560</v>
       </c>
       <c r="B45" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5538,17 +5538,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518768</v>
+        <v>518787</v>
       </c>
       <c r="R45" t="n">
-        <v>6994994</v>
+        <v>6994752</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5614,10 +5614,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121346005</v>
+        <v>121346620</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,14 +5650,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518483</v>
+        <v>518774</v>
       </c>
       <c r="R46" t="n">
-        <v>6995124</v>
+        <v>6994685</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,10 +5726,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121343920</v>
+        <v>121344818</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518807</v>
+        <v>518624</v>
       </c>
       <c r="R47" t="n">
-        <v>6994899</v>
+        <v>6995059</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,10 +5838,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121345918</v>
+        <v>121343229</v>
       </c>
       <c r="B48" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5874,14 +5874,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518360</v>
+        <v>518808</v>
       </c>
       <c r="R48" t="n">
-        <v>6995099</v>
+        <v>6994725</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,10 +5950,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121344193</v>
+        <v>121344796</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5990,13 +5990,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518808</v>
+        <v>518665</v>
       </c>
       <c r="R49" t="n">
-        <v>6994956</v>
+        <v>6995040</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6062,10 +6062,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121343196</v>
+        <v>121343478</v>
       </c>
       <c r="B50" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6102,13 +6102,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518797</v>
+        <v>518834</v>
       </c>
       <c r="R50" t="n">
-        <v>6994707</v>
+        <v>6994815</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6174,10 +6174,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121346560</v>
+        <v>121345954</v>
       </c>
       <c r="B51" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6190,34 +6190,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518787</v>
+        <v>518428</v>
       </c>
       <c r="R51" t="n">
-        <v>6994752</v>
+        <v>6995142</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6286,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121346126</v>
+        <v>121344384</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6302,21 +6302,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518627</v>
+        <v>518741</v>
       </c>
       <c r="R52" t="n">
-        <v>6994984</v>
+        <v>6994995</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6398,10 +6398,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121343178</v>
+        <v>121345053</v>
       </c>
       <c r="B53" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6414,37 +6414,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518814</v>
+        <v>518563</v>
       </c>
       <c r="R53" t="n">
-        <v>6994717</v>
+        <v>6995042</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121343797</v>
+        <v>121344999</v>
       </c>
       <c r="B54" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518812</v>
+        <v>518659</v>
       </c>
       <c r="R54" t="n">
-        <v>6994875</v>
+        <v>6995028</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,10 +6622,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121346613</v>
+        <v>121346025</v>
       </c>
       <c r="B55" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6658,17 +6658,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518770</v>
+        <v>518519</v>
       </c>
       <c r="R55" t="n">
-        <v>6994702</v>
+        <v>6995085</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,10 +6734,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121345946</v>
+        <v>121345938</v>
       </c>
       <c r="B56" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518414</v>
+        <v>518387</v>
       </c>
       <c r="R56" t="n">
-        <v>6995151</v>
+        <v>6995152</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121345064</v>
+        <v>121346005</v>
       </c>
       <c r="B57" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518566</v>
+        <v>518483</v>
       </c>
       <c r="R57" t="n">
-        <v>6995030</v>
+        <v>6995124</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6958,10 +6958,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121346232</v>
+        <v>121345960</v>
       </c>
       <c r="B58" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6974,37 +6974,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518626</v>
+        <v>518444</v>
       </c>
       <c r="R58" t="n">
-        <v>6994964</v>
+        <v>6995141</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7070,10 +7070,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121345085</v>
+        <v>121343092</v>
       </c>
       <c r="B59" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7106,14 +7106,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518559</v>
+        <v>518811</v>
       </c>
       <c r="R59" t="n">
-        <v>6995004</v>
+        <v>6994686</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7182,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121343160</v>
+        <v>121346038</v>
       </c>
       <c r="B60" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7198,37 +7198,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518815</v>
+        <v>518544</v>
       </c>
       <c r="R60" t="n">
-        <v>6994704</v>
+        <v>6995061</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7294,10 +7294,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121346025</v>
+        <v>121345918</v>
       </c>
       <c r="B61" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7334,13 +7334,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518519</v>
+        <v>518360</v>
       </c>
       <c r="R61" t="n">
-        <v>6995085</v>
+        <v>6995099</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121346533</v>
+        <v>121343305</v>
       </c>
       <c r="B62" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518703</v>
+        <v>518812</v>
       </c>
       <c r="R62" t="n">
-        <v>6994800</v>
+        <v>6994779</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7518,10 +7518,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121343249</v>
+        <v>121345122</v>
       </c>
       <c r="B63" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7554,14 +7554,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518808</v>
+        <v>518552</v>
       </c>
       <c r="R63" t="n">
-        <v>6994740</v>
+        <v>6994973</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7630,10 +7630,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121343305</v>
+        <v>121346613</v>
       </c>
       <c r="B64" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518812</v>
+        <v>518770</v>
       </c>
       <c r="R64" t="n">
-        <v>6994779</v>
+        <v>6994702</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7742,10 +7742,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121344384</v>
+        <v>121343285</v>
       </c>
       <c r="B65" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7758,34 +7758,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518741</v>
+        <v>518804</v>
       </c>
       <c r="R65" t="n">
-        <v>6994995</v>
+        <v>6994760</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,10 +7854,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121343022</v>
+        <v>121346595</v>
       </c>
       <c r="B66" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7894,13 +7894,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518814</v>
+        <v>518786</v>
       </c>
       <c r="R66" t="n">
-        <v>6994676</v>
+        <v>6994717</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121343959</v>
+        <v>121343809</v>
       </c>
       <c r="B67" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518825</v>
+        <v>518808</v>
       </c>
       <c r="R67" t="n">
-        <v>6994907</v>
+        <v>6994892</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8078,10 +8078,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121343524</v>
+        <v>121345064</v>
       </c>
       <c r="B68" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8114,17 +8114,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518815</v>
+        <v>518566</v>
       </c>
       <c r="R68" t="n">
-        <v>6994807</v>
+        <v>6995030</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8193,7 +8193,7 @@
         <v>121539052</v>
       </c>
       <c r="B69" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -2586,7 +2586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121343018</v>
+        <v>121346053</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2622,14 +2622,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518813</v>
+        <v>518560</v>
       </c>
       <c r="R19" t="n">
-        <v>6994667</v>
+        <v>6995039</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121343920</v>
+        <v>121343018</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2734,14 +2734,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518807</v>
+        <v>518813</v>
       </c>
       <c r="R20" t="n">
-        <v>6994899</v>
+        <v>6994667</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343732</v>
+        <v>121343920</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518817</v>
+        <v>518807</v>
       </c>
       <c r="R21" t="n">
-        <v>6994855</v>
+        <v>6994899</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121346053</v>
+        <v>121343732</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -2958,17 +2958,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518560</v>
+        <v>518817</v>
       </c>
       <c r="R22" t="n">
-        <v>6995039</v>
+        <v>6994855</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -5726,7 +5726,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121344818</v>
+        <v>121344796</v>
       </c>
       <c r="B47" t="n">
         <v>78616</v>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518624</v>
+        <v>518665</v>
       </c>
       <c r="R47" t="n">
-        <v>6995059</v>
+        <v>6995040</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,7 +5838,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121343229</v>
+        <v>121344818</v>
       </c>
       <c r="B48" t="n">
         <v>78616</v>
@@ -5874,17 +5874,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518808</v>
+        <v>518624</v>
       </c>
       <c r="R48" t="n">
-        <v>6994725</v>
+        <v>6995059</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,7 +5950,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121344796</v>
+        <v>121343229</v>
       </c>
       <c r="B49" t="n">
         <v>78616</v>
@@ -5986,17 +5986,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518665</v>
+        <v>518808</v>
       </c>
       <c r="R49" t="n">
-        <v>6995040</v>
+        <v>6994725</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 49768-2024 artfynd.xlsx
+++ b/artfynd/A 49768-2024 artfynd.xlsx
@@ -2586,7 +2586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346053</v>
+        <v>121343018</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2622,14 +2622,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518560</v>
+        <v>518813</v>
       </c>
       <c r="R19" t="n">
-        <v>6995039</v>
+        <v>6994667</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121343018</v>
+        <v>121343920</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2734,14 +2734,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518813</v>
+        <v>518807</v>
       </c>
       <c r="R20" t="n">
-        <v>6994667</v>
+        <v>6994899</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121343920</v>
+        <v>121343732</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518807</v>
+        <v>518817</v>
       </c>
       <c r="R21" t="n">
-        <v>6994899</v>
+        <v>6994855</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121343732</v>
+        <v>121346053</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -2958,17 +2958,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518817</v>
+        <v>518560</v>
       </c>
       <c r="R22" t="n">
-        <v>6994855</v>
+        <v>6995039</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4382,7 +4382,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121345073</v>
+        <v>121343625</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4418,17 +4418,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518555</v>
+        <v>518819</v>
       </c>
       <c r="R35" t="n">
-        <v>6995010</v>
+        <v>6994817</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,7 +4494,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121343625</v>
+        <v>121343289</v>
       </c>
       <c r="B36" t="n">
         <v>78616</v>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518819</v>
+        <v>518814</v>
       </c>
       <c r="R36" t="n">
-        <v>6994817</v>
+        <v>6994762</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121343289</v>
+        <v>121346635</v>
       </c>
       <c r="B37" t="n">
         <v>78616</v>
@@ -4646,13 +4646,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518814</v>
+        <v>518776</v>
       </c>
       <c r="R37" t="n">
-        <v>6994762</v>
+        <v>6994684</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,7 +4718,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121346635</v>
+        <v>121343196</v>
       </c>
       <c r="B38" t="n">
         <v>78616</v>
@@ -4758,13 +4758,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518776</v>
+        <v>518797</v>
       </c>
       <c r="R38" t="n">
-        <v>6994684</v>
+        <v>6994707</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,7 +4830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121343196</v>
+        <v>121345073</v>
       </c>
       <c r="B39" t="n">
         <v>78616</v>
@@ -4866,17 +4866,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518797</v>
+        <v>518555</v>
       </c>
       <c r="R39" t="n">
-        <v>6994707</v>
+        <v>6995010</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5166,7 +5166,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121344213</v>
+        <v>121346560</v>
       </c>
       <c r="B42" t="n">
         <v>78616</v>
@@ -5202,14 +5202,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518792</v>
+        <v>518787</v>
       </c>
       <c r="R42" t="n">
-        <v>6994973</v>
+        <v>6994752</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5278,7 +5278,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121343137</v>
+        <v>121344213</v>
       </c>
       <c r="B43" t="n">
         <v>78616</v>
@@ -5314,17 +5314,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518823</v>
+        <v>518792</v>
       </c>
       <c r="R43" t="n">
-        <v>6994691</v>
+        <v>6994973</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,7 +5390,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121346586</v>
+        <v>121343137</v>
       </c>
       <c r="B44" t="n">
         <v>78616</v>
@@ -5430,13 +5430,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518787</v>
+        <v>518823</v>
       </c>
       <c r="R44" t="n">
-        <v>6994738</v>
+        <v>6994691</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5502,7 +5502,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121346560</v>
+        <v>121346586</v>
       </c>
       <c r="B45" t="n">
         <v>78616</v>
@@ -5545,7 +5545,7 @@
         <v>518787</v>
       </c>
       <c r="R45" t="n">
-        <v>6994752</v>
+        <v>6994738</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5726,7 +5726,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121344796</v>
+        <v>121344818</v>
       </c>
       <c r="B47" t="n">
         <v>78616</v>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518665</v>
+        <v>518624</v>
       </c>
       <c r="R47" t="n">
-        <v>6995040</v>
+        <v>6995059</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,7 +5838,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121344818</v>
+        <v>121343229</v>
       </c>
       <c r="B48" t="n">
         <v>78616</v>
@@ -5874,17 +5874,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Lugnet, Lugnet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518624</v>
+        <v>518808</v>
       </c>
       <c r="R48" t="n">
-        <v>6995059</v>
+        <v>6994725</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,7 +5950,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121343229</v>
+        <v>121344796</v>
       </c>
       <c r="B49" t="n">
         <v>78616</v>
@@ -5986,17 +5986,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lugnet, Lugnet, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518808</v>
+        <v>518665</v>
       </c>
       <c r="R49" t="n">
-        <v>6994725</v>
+        <v>6995040</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6174,10 +6174,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121345954</v>
+        <v>121344384</v>
       </c>
       <c r="B51" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6190,37 +6190,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Linderråken, Linderråken, Jmt</t>
+          <t>Gångspängflon, Gångspängflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518428</v>
+        <v>518741</v>
       </c>
       <c r="R51" t="n">
-        <v>6995142</v>
+        <v>6994995</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6286,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121344384</v>
+        <v>121345954</v>
       </c>
       <c r="B52" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6302,37 +6302,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gångspängflon, Gångspängflon, Jmt</t>
+          <t>Linderråken, Linderråken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518741</v>
+        <v>518428</v>
       </c>
       <c r="R52" t="n">
-        <v>6994995</v>
+        <v>6995142</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6734,7 +6734,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121345938</v>
+        <v>121346005</v>
       </c>
       <c r="B56" t="n">
         <v>78616</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518387</v>
+        <v>518483</v>
       </c>
       <c r="R56" t="n">
-        <v>6995152</v>
+        <v>6995124</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,7 +6846,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121346005</v>
+        <v>121345938</v>
       </c>
       <c r="B57" t="n">
         <v>78616</v>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518483</v>
+        <v>518387</v>
       </c>
       <c r="R57" t="n">
-        <v>6995124</v>
+        <v>6995152</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
